--- a/hall/resources/sample/VisitorLevel.xlsx
+++ b/hall/resources/sample/VisitorLevel.xlsx
@@ -55,12 +55,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+概率_道具ID_数量</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="47">
   <si>
     <t>ID</t>
   </si>
@@ -83,12 +105,18 @@
     <t>固定产出</t>
   </si>
   <si>
+    <t>额外材料掉落</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>Map&lt;int{_}int&gt;{|}</t>
   </si>
   <si>
+    <t>list&lt;list&lt;int&gt;{_}&gt;{|}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -104,19 +132,37 @@
     <t>Reward</t>
   </si>
   <si>
+    <t>BonusRate</t>
+  </si>
+  <si>
     <t>普通路人1</t>
   </si>
   <si>
     <t>1990000_10000</t>
   </si>
   <si>
+    <t>0_1980000_20000</t>
+  </si>
+  <si>
     <t>1990000_11000</t>
   </si>
   <si>
+    <t>5_1980000_20000</t>
+  </si>
+  <si>
     <t>普通路人2</t>
   </si>
   <si>
+    <t>8_1980000_20000</t>
+  </si>
+  <si>
+    <t>10_1980000_20000</t>
+  </si>
+  <si>
     <t>普通路人3</t>
+  </si>
+  <si>
+    <t>15_1980000_20000</t>
   </si>
   <si>
     <t>精英白领1</t>
@@ -189,7 +235,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,6 +251,12 @@
     </font>
     <font>
       <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -723,137 +775,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -870,12 +922,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -887,10 +942,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1209,18 +1267,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G86"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H86"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
     <col min="2" max="2" width="11.625" customWidth="1"/>
     <col min="3" max="4" width="11.75" customWidth="1"/>
     <col min="5" max="5" width="15.625" customWidth="1"/>
     <col min="6" max="6" width="14.75" customWidth="1"/>
-    <col min="7" max="7" width="40.5" customWidth="1"/>
+    <col min="7" max="7" width="29.875" customWidth="1"/>
+    <col min="8" max="8" width="31.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1242,728 +1301,959 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" ht="15.75" spans="1:7">
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" ht="15.75" spans="1:7">
+      <c r="F2" s="6"/>
+      <c r="G2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" spans="1:7">
+      <c r="E3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" spans="1:8">
       <c r="A4" s="1"/>
-      <c r="B4" s="7"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" spans="1:7">
+      <c r="E4" s="8"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:8">
       <c r="A5" s="1">
         <f>B5*1000+C5</f>
-        <v>101001</v>
+        <v>1001001</v>
       </c>
       <c r="B5" s="1">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="F5" s="9"/>
+      <c r="G5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A34" si="0">B6*1000+C6</f>
-        <v>101002</v>
+        <v>1001002</v>
       </c>
       <c r="B6" s="1">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="C6" s="2">
         <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1">
         <v>10</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="F6" s="9"/>
+      <c r="G6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>102001</v>
+        <v>1002001</v>
       </c>
       <c r="B7" s="1">
-        <v>102</v>
+        <v>1002</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="F7" s="9"/>
+      <c r="G7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>102002</v>
+        <v>1002002</v>
       </c>
       <c r="B8" s="1">
-        <v>102</v>
+        <v>1002</v>
       </c>
       <c r="C8" s="2">
         <v>2</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1">
         <v>10</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="F8" s="9"/>
+      <c r="G8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>103001</v>
+        <v>1003001</v>
       </c>
       <c r="B9" s="1">
-        <v>103</v>
+        <v>1003</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="F9" s="9"/>
+      <c r="G9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>103002</v>
+        <v>1003002</v>
       </c>
       <c r="B10" s="1">
-        <v>103</v>
+        <v>1003</v>
       </c>
       <c r="C10" s="2">
         <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E10" s="1">
         <v>10</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="F10" s="9"/>
+      <c r="G10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>201001</v>
+        <v>2001001</v>
       </c>
       <c r="B11" s="1">
-        <v>201</v>
+        <v>2001</v>
       </c>
       <c r="C11" s="2">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="F11" s="9"/>
+      <c r="G11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>201002</v>
+        <v>2001002</v>
       </c>
       <c r="B12" s="1">
-        <v>201</v>
+        <v>2001</v>
       </c>
       <c r="C12" s="2">
         <v>2</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E12" s="1">
         <v>10</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="F12" s="9"/>
+      <c r="G12" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>202001</v>
+        <v>2002001</v>
       </c>
       <c r="B13" s="1">
-        <v>202</v>
+        <v>2002</v>
       </c>
       <c r="C13" s="2">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="F13" s="9"/>
+      <c r="G13" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>202002</v>
+        <v>2002002</v>
       </c>
       <c r="B14" s="1">
-        <v>202</v>
+        <v>2002</v>
       </c>
       <c r="C14" s="2">
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E14" s="1">
         <v>10</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="F14" s="9"/>
+      <c r="G14" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>203001</v>
+        <v>2003001</v>
       </c>
       <c r="B15" s="1">
-        <v>203</v>
+        <v>2003</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="F15" s="9"/>
+      <c r="G15" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>203002</v>
+        <v>2003002</v>
       </c>
       <c r="B16" s="1">
-        <v>203</v>
+        <v>2003</v>
       </c>
       <c r="C16" s="2">
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E16" s="1">
         <v>10</v>
       </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="10" t="s">
+      <c r="F16" s="9"/>
+      <c r="G16" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>301001</v>
+        <v>3001001</v>
       </c>
       <c r="B17" s="1">
-        <v>301</v>
+        <v>3001</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="F17" s="9"/>
+      <c r="G17" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>301002</v>
+        <v>3001002</v>
       </c>
       <c r="B18" s="1">
-        <v>301</v>
+        <v>3001</v>
       </c>
       <c r="C18" s="2">
         <v>2</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E18" s="1">
         <v>10</v>
       </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="F18" s="9"/>
+      <c r="G18" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>302001</v>
+        <v>3002001</v>
       </c>
       <c r="B19" s="1">
-        <v>302</v>
+        <v>3002</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E19" s="1">
         <v>0</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="F19" s="9"/>
+      <c r="G19" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>302002</v>
+        <v>3002002</v>
       </c>
       <c r="B20" s="1">
-        <v>302</v>
+        <v>3002</v>
       </c>
       <c r="C20" s="2">
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E20" s="1">
         <v>10</v>
       </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="F20" s="9"/>
+      <c r="G20" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>303001</v>
+        <v>3003001</v>
       </c>
       <c r="B21" s="1">
-        <v>303</v>
+        <v>3003</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
       </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="F21" s="9"/>
+      <c r="G21" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>303002</v>
+        <v>3003002</v>
       </c>
       <c r="B22" s="1">
-        <v>303</v>
+        <v>3003</v>
       </c>
       <c r="C22" s="2">
         <v>2</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E22" s="1">
         <v>10</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="F22" s="9"/>
+      <c r="G22" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>401001</v>
+        <v>4001001</v>
       </c>
       <c r="B23" s="1">
-        <v>401</v>
+        <v>4001</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="F23" s="9"/>
+      <c r="G23" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>401002</v>
+        <v>4001002</v>
       </c>
       <c r="B24" s="1">
-        <v>401</v>
+        <v>4001</v>
       </c>
       <c r="C24" s="2">
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E24" s="1">
         <v>10</v>
       </c>
-      <c r="F24" s="8"/>
-      <c r="G24" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="F24" s="9"/>
+      <c r="G24" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
-        <v>402001</v>
+        <v>4002001</v>
       </c>
       <c r="B25" s="1">
-        <v>402</v>
+        <v>4002</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="F25" s="9"/>
+      <c r="G25" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
-        <v>402002</v>
+        <v>4002002</v>
       </c>
       <c r="B26" s="1">
-        <v>402</v>
+        <v>4002</v>
       </c>
       <c r="C26" s="2">
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E26" s="1">
         <v>10</v>
       </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="F26" s="9"/>
+      <c r="G26" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
-        <v>403001</v>
+        <v>4003001</v>
       </c>
       <c r="B27" s="1">
-        <v>403</v>
+        <v>4003</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
       </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="F27" s="9"/>
+      <c r="G27" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
-        <v>403002</v>
+        <v>4003002</v>
       </c>
       <c r="B28" s="1">
-        <v>403</v>
+        <v>4003</v>
       </c>
       <c r="C28" s="2">
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E28" s="1">
         <v>10</v>
       </c>
-      <c r="F28" s="8"/>
-      <c r="G28" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="F28" s="9"/>
+      <c r="G28" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
-        <v>501001</v>
+        <v>5001001</v>
       </c>
       <c r="B29" s="1">
-        <v>501</v>
+        <v>5001</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
       </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="F29" s="9"/>
+      <c r="G29" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
-        <v>501002</v>
+        <v>5001002</v>
       </c>
       <c r="B30" s="1">
-        <v>501</v>
+        <v>5001</v>
       </c>
       <c r="C30" s="2">
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E30" s="1">
         <v>10</v>
       </c>
-      <c r="F30" s="8"/>
-      <c r="G30" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="F30" s="9"/>
+      <c r="G30" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
-        <v>502001</v>
+        <v>5002001</v>
       </c>
       <c r="B31" s="1">
-        <v>502</v>
+        <v>5002</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
       </c>
-      <c r="F31" s="8"/>
-      <c r="G31" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="F31" s="9"/>
+      <c r="G31" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
-        <v>502002</v>
+        <v>5002002</v>
       </c>
       <c r="B32" s="1">
-        <v>502</v>
+        <v>5002</v>
       </c>
       <c r="C32" s="2">
         <v>2</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E32" s="1">
         <v>10</v>
       </c>
-      <c r="F32" s="8"/>
-      <c r="G32" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="F32" s="9"/>
+      <c r="G32" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
-        <v>503001</v>
+        <v>5003001</v>
       </c>
       <c r="B33" s="1">
-        <v>503</v>
+        <v>5003</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E33" s="1">
         <v>0</v>
       </c>
-      <c r="F33" s="8"/>
-      <c r="G33" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="F33" s="9"/>
+      <c r="G33" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
-        <v>503002</v>
+        <v>5003002</v>
       </c>
       <c r="B34" s="1">
-        <v>503</v>
+        <v>5003</v>
       </c>
       <c r="C34" s="2">
         <v>2</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E34" s="1">
         <v>10</v>
       </c>
-      <c r="F34" s="8"/>
-      <c r="G34" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="68" ht="17.25" spans="4:5">
-      <c r="D68" s="11"/>
-    </row>
-    <row r="69" ht="14.25" spans="4:5">
-      <c r="E69" s="12"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="H35" s="12"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="H36" s="12"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="H37" s="12"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="H38" s="12"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="H39" s="12"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="H40" s="12"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="H41" s="12"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="H42" s="12"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="H43" s="12"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="H44" s="12"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="H45" s="12"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="H46" s="12"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="H47" s="12"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="H48" s="12"/>
+    </row>
+    <row r="49" spans="8:8">
+      <c r="H49" s="12"/>
+    </row>
+    <row r="50" spans="8:8">
+      <c r="H50" s="12"/>
+    </row>
+    <row r="51" spans="8:8">
+      <c r="H51" s="12"/>
+    </row>
+    <row r="52" spans="8:8">
+      <c r="H52" s="12"/>
+    </row>
+    <row r="53" spans="8:8">
+      <c r="H53" s="12"/>
+    </row>
+    <row r="54" spans="8:8">
+      <c r="H54" s="12"/>
+    </row>
+    <row r="55" spans="8:8">
+      <c r="H55" s="12"/>
+    </row>
+    <row r="56" spans="8:8">
+      <c r="H56" s="12"/>
+    </row>
+    <row r="57" spans="8:8">
+      <c r="H57" s="12"/>
+    </row>
+    <row r="58" spans="8:8">
+      <c r="H58" s="12"/>
+    </row>
+    <row r="59" spans="8:8">
+      <c r="H59" s="12"/>
+    </row>
+    <row r="60" spans="8:8">
+      <c r="H60" s="12"/>
+    </row>
+    <row r="61" spans="8:8">
+      <c r="H61" s="12"/>
+    </row>
+    <row r="62" spans="8:8">
+      <c r="H62" s="12"/>
+    </row>
+    <row r="63" spans="8:8">
+      <c r="H63" s="12"/>
+    </row>
+    <row r="64" spans="8:8">
+      <c r="H64" s="12"/>
+    </row>
+    <row r="65" spans="4:8">
+      <c r="H65" s="12"/>
+    </row>
+    <row r="66" spans="4:8">
+      <c r="H66" s="12"/>
+    </row>
+    <row r="67" spans="4:8">
+      <c r="H67" s="12"/>
+    </row>
+    <row r="68" ht="17.25" spans="4:8">
+      <c r="D68" s="13"/>
+      <c r="H68" s="12"/>
+    </row>
+    <row r="69" ht="14.25" spans="4:8">
+      <c r="E69" s="14"/>
+      <c r="H69" s="12"/>
+    </row>
+    <row r="70" spans="4:8">
+      <c r="H70" s="12"/>
+    </row>
+    <row r="71" spans="4:8">
+      <c r="H71" s="12"/>
+    </row>
+    <row r="72" spans="4:8">
+      <c r="H72" s="12"/>
+    </row>
+    <row r="73" spans="4:8">
+      <c r="H73" s="12"/>
+    </row>
+    <row r="74" spans="4:8">
+      <c r="H74" s="12"/>
+    </row>
+    <row r="75" spans="4:8">
+      <c r="H75" s="12"/>
+    </row>
+    <row r="76" spans="4:8">
+      <c r="H76" s="12"/>
+    </row>
+    <row r="77" spans="4:8">
+      <c r="H77" s="12"/>
+    </row>
+    <row r="78" spans="4:8">
+      <c r="H78" s="12"/>
+    </row>
+    <row r="79" spans="4:8">
+      <c r="H79" s="12"/>
     </row>
     <row r="82" ht="14.25" spans="4:5">
-      <c r="D82" s="12"/>
+      <c r="D82" s="14"/>
     </row>
     <row r="85" ht="14.25" spans="4:5">
-      <c r="E85" s="12"/>
+      <c r="E85" s="14"/>
     </row>
     <row r="86" ht="14.25" spans="4:5">
-      <c r="E86" s="12"/>
+      <c r="E86" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/VisitorLevel.xlsx
+++ b/hall/resources/sample/VisitorLevel.xlsx
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="62">
   <si>
     <t>ID</t>
   </si>
@@ -135,7 +135,7 @@
     <t>BonusRate</t>
   </si>
   <si>
-    <t>普通路人1</t>
+    <t>街头潮人</t>
   </si>
   <si>
     <t>1990000_10000</t>
@@ -150,7 +150,7 @@
     <t>5_1980000_20000</t>
   </si>
   <si>
-    <t>普通路人2</t>
+    <t>复古绅士</t>
   </si>
   <si>
     <t>8_1980000_20000</t>
@@ -159,13 +159,22 @@
     <t>10_1980000_20000</t>
   </si>
   <si>
-    <t>普通路人3</t>
+    <t>酷盖少年</t>
   </si>
   <si>
     <t>15_1980000_20000</t>
   </si>
   <si>
-    <t>精英白领1</t>
+    <t>文艺青年</t>
+  </si>
+  <si>
+    <t>书香少女</t>
+  </si>
+  <si>
+    <t>民谣歌手</t>
+  </si>
+  <si>
+    <t>潮流先锋</t>
   </si>
   <si>
     <t>1990000_20000</t>
@@ -174,13 +183,22 @@
     <t>1990000_21000</t>
   </si>
   <si>
-    <t>精英白领2</t>
-  </si>
-  <si>
-    <t>精英白领3</t>
-  </si>
-  <si>
-    <t>社交名流1</t>
+    <t>时尚教主</t>
+  </si>
+  <si>
+    <t>街拍达人</t>
+  </si>
+  <si>
+    <t>马拉松客</t>
+  </si>
+  <si>
+    <t>极限玩家</t>
+  </si>
+  <si>
+    <t>科技极客</t>
+  </si>
+  <si>
+    <t>运动健将</t>
   </si>
   <si>
     <t>1990000_30000</t>
@@ -189,13 +207,22 @@
     <t>1990000_31000</t>
   </si>
   <si>
-    <t>社交名流2</t>
-  </si>
-  <si>
-    <t>社交名流3</t>
-  </si>
-  <si>
-    <t>富豪商人1</t>
+    <t>跑酷少年</t>
+  </si>
+  <si>
+    <t>滑板高手</t>
+  </si>
+  <si>
+    <t>独立画家</t>
+  </si>
+  <si>
+    <t>浪漫诗人</t>
+  </si>
+  <si>
+    <t>古典乐迷</t>
+  </si>
+  <si>
+    <t>甜心辣妹</t>
   </si>
   <si>
     <t>1990000_40000</t>
@@ -204,13 +231,22 @@
     <t>1990000_41000</t>
   </si>
   <si>
-    <t>富豪商人2</t>
-  </si>
-  <si>
-    <t>富豪商人3</t>
-  </si>
-  <si>
-    <t>达官显贵1</t>
+    <t>活力少女</t>
+  </si>
+  <si>
+    <t>优雅女神</t>
+  </si>
+  <si>
+    <t>创业新贵</t>
+  </si>
+  <si>
+    <t>摸金校尉</t>
+  </si>
+  <si>
+    <t>氪金大佬</t>
+  </si>
+  <si>
+    <t>健身狂魔</t>
   </si>
   <si>
     <t>1990000_50000</t>
@@ -219,10 +255,19 @@
     <t>1990000_51000</t>
   </si>
   <si>
-    <t>达官显贵2</t>
-  </si>
-  <si>
-    <t>达官显贵3</t>
+    <t>单车骑士</t>
+  </si>
+  <si>
+    <t>登山行者</t>
+  </si>
+  <si>
+    <t>穿搭博主</t>
+  </si>
+  <si>
+    <t>美妆新秀</t>
+  </si>
+  <si>
+    <t>高定女王</t>
   </si>
 </sst>
 </file>
@@ -1267,7 +1312,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
@@ -1361,7 +1406,7 @@
     </row>
     <row r="5" ht="16" customHeight="1" spans="1:8">
       <c r="A5" s="1">
-        <f>B5*1000+C5</f>
+        <f t="shared" ref="A5:A10" si="0">B5*1000+C5</f>
         <v>1001001</v>
       </c>
       <c r="B5" s="1">
@@ -1386,7 +1431,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
-        <f t="shared" ref="A6:A34" si="0">B6*1000+C6</f>
+        <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
       <c r="B6" s="1">
@@ -1395,9 +1440,7 @@
       <c r="C6" s="2">
         <v>2</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="D6" s="2"/>
       <c r="E6" s="1">
         <v>10</v>
       </c>
@@ -1445,9 +1488,7 @@
       <c r="C8" s="2">
         <v>2</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="D8" s="2"/>
       <c r="E8" s="1">
         <v>10</v>
       </c>
@@ -1495,9 +1536,7 @@
       <c r="C10" s="2">
         <v>2</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="D10" s="2"/>
       <c r="E10" s="1">
         <v>10</v>
       </c>
@@ -1511,749 +1550,1463 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <f t="shared" si="0"/>
-        <v>2001001</v>
+        <f t="shared" ref="A11:A22" si="1">B11*1000+C11</f>
+        <v>1004001</v>
       </c>
       <c r="B11" s="1">
-        <v>2001</v>
+        <v>1004</v>
       </c>
       <c r="C11" s="2">
         <v>1</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="9"/>
-      <c r="G11" s="11" t="s">
-        <v>28</v>
+      <c r="G11" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <f t="shared" si="0"/>
-        <v>2001002</v>
+        <f t="shared" si="1"/>
+        <v>1004002</v>
       </c>
       <c r="B12" s="1">
-        <v>2001</v>
+        <v>1004</v>
       </c>
       <c r="C12" s="2">
         <v>2</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="D12" s="2"/>
       <c r="E12" s="1">
         <v>10</v>
       </c>
       <c r="F12" s="9"/>
-      <c r="G12" s="11" t="s">
-        <v>29</v>
+      <c r="G12" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <f t="shared" si="0"/>
-        <v>2002001</v>
+        <f t="shared" si="1"/>
+        <v>1005001</v>
       </c>
       <c r="B13" s="1">
-        <v>2002</v>
+        <v>1005</v>
       </c>
       <c r="C13" s="2">
         <v>1</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>30</v>
+      <c r="D13" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
       <c r="F13" s="9"/>
-      <c r="G13" s="11" t="s">
-        <v>28</v>
+      <c r="G13" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <f t="shared" si="0"/>
-        <v>2002002</v>
+        <f t="shared" si="1"/>
+        <v>1005002</v>
       </c>
       <c r="B14" s="1">
-        <v>2002</v>
+        <v>1005</v>
       </c>
       <c r="C14" s="2">
         <v>2</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="D14" s="2"/>
       <c r="E14" s="1">
         <v>10</v>
       </c>
       <c r="F14" s="9"/>
-      <c r="G14" s="11" t="s">
-        <v>29</v>
+      <c r="G14" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <f t="shared" si="0"/>
-        <v>2003001</v>
+        <f t="shared" si="1"/>
+        <v>1006001</v>
       </c>
       <c r="B15" s="1">
-        <v>2003</v>
+        <v>1006</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>31</v>
+      <c r="D15" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
       </c>
       <c r="F15" s="9"/>
-      <c r="G15" s="11" t="s">
-        <v>28</v>
+      <c r="G15" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <f t="shared" si="0"/>
-        <v>2003002</v>
+        <f t="shared" si="1"/>
+        <v>1006002</v>
       </c>
       <c r="B16" s="1">
-        <v>2003</v>
+        <v>1006</v>
       </c>
       <c r="C16" s="2">
         <v>2</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="D16" s="2"/>
       <c r="E16" s="1">
         <v>10</v>
       </c>
       <c r="F16" s="9"/>
-      <c r="G16" s="11" t="s">
-        <v>29</v>
+      <c r="G16" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <f t="shared" si="0"/>
-        <v>3001001</v>
+        <f t="shared" si="1"/>
+        <v>2001001</v>
       </c>
       <c r="B17" s="1">
-        <v>3001</v>
+        <v>2001</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>32</v>
+      <c r="D17" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <f t="shared" si="0"/>
-        <v>3001002</v>
+        <f t="shared" si="1"/>
+        <v>2001002</v>
       </c>
       <c r="B18" s="1">
-        <v>3001</v>
+        <v>2001</v>
       </c>
       <c r="C18" s="2">
         <v>2</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="D18" s="2"/>
       <c r="E18" s="1">
         <v>10</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <f t="shared" si="0"/>
-        <v>3002001</v>
+        <f t="shared" si="1"/>
+        <v>2002001</v>
       </c>
       <c r="B19" s="1">
-        <v>3002</v>
+        <v>2002</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>35</v>
+      <c r="D19" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="E19" s="1">
         <v>0</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <f t="shared" si="0"/>
-        <v>3002002</v>
+        <f t="shared" si="1"/>
+        <v>2002002</v>
       </c>
       <c r="B20" s="1">
-        <v>3002</v>
+        <v>2002</v>
       </c>
       <c r="C20" s="2">
         <v>2</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="D20" s="2"/>
       <c r="E20" s="1">
         <v>10</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <f t="shared" si="0"/>
-        <v>3003001</v>
+        <f t="shared" si="1"/>
+        <v>2003001</v>
       </c>
       <c r="B21" s="1">
-        <v>3003</v>
+        <v>2003</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>36</v>
+      <c r="D21" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <f t="shared" si="0"/>
-        <v>3003002</v>
+        <f t="shared" si="1"/>
+        <v>2003002</v>
       </c>
       <c r="B22" s="1">
-        <v>3003</v>
+        <v>2003</v>
       </c>
       <c r="C22" s="2">
         <v>2</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="D22" s="2"/>
       <c r="E22" s="1">
         <v>10</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <f t="shared" si="0"/>
-        <v>4001001</v>
+        <f t="shared" ref="A23:A34" si="2">B23*1000+C23</f>
+        <v>2004001</v>
       </c>
       <c r="B23" s="1">
-        <v>4001</v>
+        <v>2004</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>37</v>
+      <c r="D23" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="11" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <f t="shared" si="0"/>
-        <v>4001002</v>
+        <f t="shared" si="2"/>
+        <v>2004002</v>
       </c>
       <c r="B24" s="1">
-        <v>4001</v>
+        <v>2004</v>
       </c>
       <c r="C24" s="2">
         <v>2</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="D24" s="1"/>
       <c r="E24" s="1">
         <v>10</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="11" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <f t="shared" si="0"/>
-        <v>4002001</v>
+        <f t="shared" si="2"/>
+        <v>2005001</v>
       </c>
       <c r="B25" s="1">
-        <v>4002</v>
+        <v>2005</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>40</v>
+      <c r="D25" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="11" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <f t="shared" si="0"/>
-        <v>4002002</v>
+        <f t="shared" si="2"/>
+        <v>2005002</v>
       </c>
       <c r="B26" s="1">
-        <v>4002</v>
+        <v>2005</v>
       </c>
       <c r="C26" s="2">
         <v>2</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="D26" s="1"/>
       <c r="E26" s="1">
         <v>10</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="11" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <f t="shared" si="0"/>
-        <v>4003001</v>
+        <f t="shared" si="2"/>
+        <v>2006001</v>
       </c>
       <c r="B27" s="1">
-        <v>4003</v>
+        <v>2006</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>41</v>
+      <c r="D27" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="11" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <f t="shared" si="0"/>
-        <v>4003002</v>
+        <f t="shared" si="2"/>
+        <v>2006002</v>
       </c>
       <c r="B28" s="1">
-        <v>4003</v>
+        <v>2006</v>
       </c>
       <c r="C28" s="2">
         <v>2</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="D28" s="1"/>
       <c r="E28" s="1">
         <v>10</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="11" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <f t="shared" si="0"/>
-        <v>5001001</v>
+        <f t="shared" si="2"/>
+        <v>3001001</v>
       </c>
       <c r="B29" s="1">
-        <v>5001</v>
+        <v>3001</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>42</v>
+      <c r="D29" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <f t="shared" si="0"/>
-        <v>5001002</v>
+        <f t="shared" si="2"/>
+        <v>3001002</v>
       </c>
       <c r="B30" s="1">
-        <v>5001</v>
+        <v>3001</v>
       </c>
       <c r="C30" s="2">
         <v>2</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="D30" s="1"/>
       <c r="E30" s="1">
         <v>10</v>
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <f t="shared" si="0"/>
-        <v>5002001</v>
+        <f t="shared" si="2"/>
+        <v>3002001</v>
       </c>
       <c r="B31" s="1">
-        <v>5002</v>
+        <v>3002</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>45</v>
+      <c r="D31" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <f t="shared" si="0"/>
-        <v>5002002</v>
+        <f t="shared" si="2"/>
+        <v>3002002</v>
       </c>
       <c r="B32" s="1">
-        <v>5002</v>
+        <v>3002</v>
       </c>
       <c r="C32" s="2">
         <v>2</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="D32" s="1"/>
       <c r="E32" s="1">
         <v>10</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <f t="shared" si="0"/>
-        <v>5003001</v>
+        <f t="shared" si="2"/>
+        <v>3003001</v>
       </c>
       <c r="B33" s="1">
-        <v>5003</v>
+        <v>3003</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>46</v>
+      <c r="D33" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E33" s="1">
         <v>0</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <f t="shared" si="0"/>
-        <v>5003002</v>
+        <f t="shared" si="2"/>
+        <v>3003002</v>
       </c>
       <c r="B34" s="1">
-        <v>5003</v>
+        <v>3003</v>
       </c>
       <c r="C34" s="2">
         <v>2</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="D34" s="1"/>
       <c r="E34" s="1">
         <v>10</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="1">
+        <f t="shared" ref="A35:A40" si="3">B35*1000+C35</f>
+        <v>3004001</v>
+      </c>
+      <c r="B35" s="1">
+        <v>3004</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0</v>
+      </c>
+      <c r="F35" s="9"/>
+      <c r="G35" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="1">
+        <f t="shared" si="3"/>
+        <v>3004002</v>
+      </c>
+      <c r="B36" s="1">
+        <v>3004</v>
+      </c>
+      <c r="C36" s="2">
+        <v>2</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1">
+        <v>10</v>
+      </c>
+      <c r="F36" s="9"/>
+      <c r="G36" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="1">
+        <f t="shared" si="3"/>
+        <v>3005001</v>
+      </c>
+      <c r="B37" s="1">
+        <v>3005</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="E37" s="1">
+        <v>0</v>
+      </c>
+      <c r="F37" s="9"/>
+      <c r="G37" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
-      <c r="H35" s="12"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="H36" s="12"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="H37" s="12"/>
-    </row>
     <row r="38" spans="1:8">
-      <c r="H38" s="12"/>
+      <c r="A38" s="1">
+        <f t="shared" si="3"/>
+        <v>3005002</v>
+      </c>
+      <c r="B38" s="1">
+        <v>3005</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1">
+        <v>10</v>
+      </c>
+      <c r="F38" s="9"/>
+      <c r="G38" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="H39" s="12"/>
+      <c r="A39" s="1">
+        <f t="shared" si="3"/>
+        <v>3006001</v>
+      </c>
+      <c r="B39" s="1">
+        <v>3006</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0</v>
+      </c>
+      <c r="F39" s="9"/>
+      <c r="G39" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="40" spans="1:8">
-      <c r="H40" s="12"/>
+      <c r="A40" s="1">
+        <f t="shared" si="3"/>
+        <v>3006002</v>
+      </c>
+      <c r="B40" s="1">
+        <v>3006</v>
+      </c>
+      <c r="C40" s="2">
+        <v>2</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1">
+        <v>10</v>
+      </c>
+      <c r="F40" s="9"/>
+      <c r="G40" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="41" spans="1:8">
-      <c r="H41" s="12"/>
+      <c r="A41" s="1">
+        <f t="shared" ref="A41:A52" si="4">B41*1000+C41</f>
+        <v>4001001</v>
+      </c>
+      <c r="B41" s="1">
+        <v>4001</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0</v>
+      </c>
+      <c r="F41" s="9"/>
+      <c r="G41" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="H42" s="12"/>
+      <c r="A42" s="1">
+        <f t="shared" si="4"/>
+        <v>4001002</v>
+      </c>
+      <c r="B42" s="1">
+        <v>4001</v>
+      </c>
+      <c r="C42" s="2">
+        <v>2</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1">
+        <v>10</v>
+      </c>
+      <c r="F42" s="9"/>
+      <c r="G42" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="H43" s="12"/>
+      <c r="A43" s="1">
+        <f t="shared" si="4"/>
+        <v>4002001</v>
+      </c>
+      <c r="B43" s="1">
+        <v>4002</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0</v>
+      </c>
+      <c r="F43" s="9"/>
+      <c r="G43" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="H44" s="12"/>
+      <c r="A44" s="1">
+        <f t="shared" si="4"/>
+        <v>4002002</v>
+      </c>
+      <c r="B44" s="1">
+        <v>4002</v>
+      </c>
+      <c r="C44" s="2">
+        <v>2</v>
+      </c>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1">
+        <v>10</v>
+      </c>
+      <c r="F44" s="9"/>
+      <c r="G44" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="H45" s="12"/>
+      <c r="A45" s="1">
+        <f t="shared" si="4"/>
+        <v>4003001</v>
+      </c>
+      <c r="B45" s="1">
+        <v>4003</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0</v>
+      </c>
+      <c r="F45" s="9"/>
+      <c r="G45" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="H46" s="12"/>
+      <c r="A46" s="1">
+        <f t="shared" si="4"/>
+        <v>4003002</v>
+      </c>
+      <c r="B46" s="1">
+        <v>4003</v>
+      </c>
+      <c r="C46" s="2">
+        <v>2</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1">
+        <v>10</v>
+      </c>
+      <c r="F46" s="9"/>
+      <c r="G46" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="H47" s="12"/>
+      <c r="A47" s="1">
+        <f t="shared" ref="A47:A58" si="5">B47*1000+C47</f>
+        <v>4004001</v>
+      </c>
+      <c r="B47" s="1">
+        <v>4004</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0</v>
+      </c>
+      <c r="F47" s="9"/>
+      <c r="G47" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="48" spans="1:8">
-      <c r="H48" s="12"/>
-    </row>
-    <row r="49" spans="8:8">
-      <c r="H49" s="12"/>
-    </row>
-    <row r="50" spans="8:8">
-      <c r="H50" s="12"/>
-    </row>
-    <row r="51" spans="8:8">
-      <c r="H51" s="12"/>
-    </row>
-    <row r="52" spans="8:8">
-      <c r="H52" s="12"/>
-    </row>
-    <row r="53" spans="8:8">
-      <c r="H53" s="12"/>
-    </row>
-    <row r="54" spans="8:8">
-      <c r="H54" s="12"/>
-    </row>
-    <row r="55" spans="8:8">
-      <c r="H55" s="12"/>
-    </row>
-    <row r="56" spans="8:8">
-      <c r="H56" s="12"/>
-    </row>
-    <row r="57" spans="8:8">
-      <c r="H57" s="12"/>
-    </row>
-    <row r="58" spans="8:8">
-      <c r="H58" s="12"/>
-    </row>
-    <row r="59" spans="8:8">
-      <c r="H59" s="12"/>
-    </row>
-    <row r="60" spans="8:8">
-      <c r="H60" s="12"/>
-    </row>
-    <row r="61" spans="8:8">
-      <c r="H61" s="12"/>
-    </row>
-    <row r="62" spans="8:8">
-      <c r="H62" s="12"/>
-    </row>
-    <row r="63" spans="8:8">
-      <c r="H63" s="12"/>
-    </row>
-    <row r="64" spans="8:8">
-      <c r="H64" s="12"/>
-    </row>
-    <row r="65" spans="4:8">
+      <c r="A48" s="1">
+        <f t="shared" si="5"/>
+        <v>4004002</v>
+      </c>
+      <c r="B48" s="1">
+        <v>4004</v>
+      </c>
+      <c r="C48" s="2">
+        <v>2</v>
+      </c>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1">
+        <v>10</v>
+      </c>
+      <c r="F48" s="9"/>
+      <c r="G48" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1">
+        <f t="shared" si="5"/>
+        <v>4005001</v>
+      </c>
+      <c r="B49" s="1">
+        <v>4005</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0</v>
+      </c>
+      <c r="F49" s="9"/>
+      <c r="G49" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1">
+        <f t="shared" si="5"/>
+        <v>4005002</v>
+      </c>
+      <c r="B50" s="1">
+        <v>4005</v>
+      </c>
+      <c r="C50" s="2">
+        <v>2</v>
+      </c>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1">
+        <v>10</v>
+      </c>
+      <c r="F50" s="9"/>
+      <c r="G50" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1">
+        <f t="shared" si="5"/>
+        <v>4006001</v>
+      </c>
+      <c r="B51" s="1">
+        <v>4006</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" s="1">
+        <v>0</v>
+      </c>
+      <c r="F51" s="9"/>
+      <c r="G51" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1">
+        <f t="shared" si="5"/>
+        <v>4006002</v>
+      </c>
+      <c r="B52" s="1">
+        <v>4006</v>
+      </c>
+      <c r="C52" s="2">
+        <v>2</v>
+      </c>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1">
+        <v>10</v>
+      </c>
+      <c r="F52" s="9"/>
+      <c r="G52" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="1">
+        <f t="shared" si="5"/>
+        <v>5001001</v>
+      </c>
+      <c r="B53" s="1">
+        <v>5001</v>
+      </c>
+      <c r="C53" s="2">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0</v>
+      </c>
+      <c r="F53" s="9"/>
+      <c r="G53" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="1">
+        <f t="shared" si="5"/>
+        <v>5001002</v>
+      </c>
+      <c r="B54" s="1">
+        <v>5001</v>
+      </c>
+      <c r="C54" s="2">
+        <v>2</v>
+      </c>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1">
+        <v>10</v>
+      </c>
+      <c r="F54" s="9"/>
+      <c r="G54" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="1">
+        <f t="shared" si="5"/>
+        <v>5002001</v>
+      </c>
+      <c r="B55" s="1">
+        <v>5002</v>
+      </c>
+      <c r="C55" s="2">
+        <v>1</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0</v>
+      </c>
+      <c r="F55" s="9"/>
+      <c r="G55" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="1">
+        <f t="shared" si="5"/>
+        <v>5002002</v>
+      </c>
+      <c r="B56" s="1">
+        <v>5002</v>
+      </c>
+      <c r="C56" s="2">
+        <v>2</v>
+      </c>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1">
+        <v>10</v>
+      </c>
+      <c r="F56" s="9"/>
+      <c r="G56" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="1">
+        <f t="shared" si="5"/>
+        <v>5003001</v>
+      </c>
+      <c r="B57" s="1">
+        <v>5003</v>
+      </c>
+      <c r="C57" s="2">
+        <v>1</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E57" s="1">
+        <v>0</v>
+      </c>
+      <c r="F57" s="9"/>
+      <c r="G57" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="1">
+        <f t="shared" si="5"/>
+        <v>5003002</v>
+      </c>
+      <c r="B58" s="1">
+        <v>5003</v>
+      </c>
+      <c r="C58" s="2">
+        <v>2</v>
+      </c>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1">
+        <v>10</v>
+      </c>
+      <c r="F58" s="9"/>
+      <c r="G58" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="1">
+        <f t="shared" ref="A59:A64" si="6">B59*1000+C59</f>
+        <v>5004001</v>
+      </c>
+      <c r="B59" s="1">
+        <v>5004</v>
+      </c>
+      <c r="C59" s="2">
+        <v>1</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E59" s="1">
+        <v>0</v>
+      </c>
+      <c r="F59" s="9"/>
+      <c r="G59" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="1">
+        <f t="shared" si="6"/>
+        <v>5004002</v>
+      </c>
+      <c r="B60" s="1">
+        <v>5004</v>
+      </c>
+      <c r="C60" s="2">
+        <v>2</v>
+      </c>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1">
+        <v>10</v>
+      </c>
+      <c r="F60" s="9"/>
+      <c r="G60" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="1">
+        <f t="shared" si="6"/>
+        <v>5005001</v>
+      </c>
+      <c r="B61" s="1">
+        <v>5005</v>
+      </c>
+      <c r="C61" s="2">
+        <v>1</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E61" s="1">
+        <v>0</v>
+      </c>
+      <c r="F61" s="9"/>
+      <c r="G61" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="1">
+        <f t="shared" si="6"/>
+        <v>5005002</v>
+      </c>
+      <c r="B62" s="1">
+        <v>5005</v>
+      </c>
+      <c r="C62" s="2">
+        <v>2</v>
+      </c>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1">
+        <v>10</v>
+      </c>
+      <c r="F62" s="9"/>
+      <c r="G62" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="1">
+        <f t="shared" si="6"/>
+        <v>5006001</v>
+      </c>
+      <c r="B63" s="1">
+        <v>5006</v>
+      </c>
+      <c r="C63" s="2">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E63" s="1">
+        <v>0</v>
+      </c>
+      <c r="F63" s="9"/>
+      <c r="G63" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="1">
+        <f t="shared" si="6"/>
+        <v>5006002</v>
+      </c>
+      <c r="B64" s="1">
+        <v>5006</v>
+      </c>
+      <c r="C64" s="2">
+        <v>2</v>
+      </c>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1">
+        <v>10</v>
+      </c>
+      <c r="F64" s="9"/>
+      <c r="G64" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" spans="8:8">
       <c r="H65" s="12"/>
     </row>
-    <row r="66" spans="4:8">
+    <row r="66" spans="8:8">
       <c r="H66" s="12"/>
     </row>
-    <row r="67" spans="4:8">
+    <row r="67" spans="8:8">
       <c r="H67" s="12"/>
     </row>
-    <row r="68" ht="17.25" spans="4:8">
-      <c r="D68" s="13"/>
+    <row r="68" spans="8:8">
       <c r="H68" s="12"/>
     </row>
-    <row r="69" ht="14.25" spans="4:8">
-      <c r="E69" s="14"/>
+    <row r="69" spans="8:8">
       <c r="H69" s="12"/>
     </row>
-    <row r="70" spans="4:8">
+    <row r="70" spans="8:8">
       <c r="H70" s="12"/>
     </row>
-    <row r="71" spans="4:8">
+    <row r="71" spans="8:8">
       <c r="H71" s="12"/>
     </row>
-    <row r="72" spans="4:8">
+    <row r="72" spans="8:8">
       <c r="H72" s="12"/>
     </row>
-    <row r="73" spans="4:8">
+    <row r="73" spans="8:8">
       <c r="H73" s="12"/>
     </row>
-    <row r="74" spans="4:8">
+    <row r="74" spans="8:8">
       <c r="H74" s="12"/>
     </row>
-    <row r="75" spans="4:8">
+    <row r="75" spans="8:8">
       <c r="H75" s="12"/>
     </row>
-    <row r="76" spans="4:8">
+    <row r="76" spans="8:8">
       <c r="H76" s="12"/>
     </row>
-    <row r="77" spans="4:8">
+    <row r="77" spans="8:8">
       <c r="H77" s="12"/>
     </row>
-    <row r="78" spans="4:8">
+    <row r="78" spans="8:8">
       <c r="H78" s="12"/>
     </row>
-    <row r="79" spans="4:8">
+    <row r="79" spans="8:8">
       <c r="H79" s="12"/>
     </row>
-    <row r="82" ht="14.25" spans="4:5">
-      <c r="D82" s="14"/>
-    </row>
-    <row r="85" ht="14.25" spans="4:5">
-      <c r="E85" s="14"/>
-    </row>
-    <row r="86" ht="14.25" spans="4:5">
-      <c r="E86" s="14"/>
+    <row r="80" spans="8:8">
+      <c r="H80" s="12"/>
+    </row>
+    <row r="81" spans="8:8">
+      <c r="H81" s="12"/>
+    </row>
+    <row r="82" spans="8:8">
+      <c r="H82" s="12"/>
+    </row>
+    <row r="83" spans="8:8">
+      <c r="H83" s="12"/>
+    </row>
+    <row r="84" spans="8:8">
+      <c r="H84" s="12"/>
+    </row>
+    <row r="85" spans="8:8">
+      <c r="H85" s="12"/>
+    </row>
+    <row r="86" spans="8:8">
+      <c r="H86" s="12"/>
+    </row>
+    <row r="87" spans="8:8">
+      <c r="H87" s="12"/>
+    </row>
+    <row r="88" spans="8:8">
+      <c r="H88" s="12"/>
+    </row>
+    <row r="89" spans="8:8">
+      <c r="H89" s="12"/>
+    </row>
+    <row r="90" spans="8:8">
+      <c r="H90" s="12"/>
+    </row>
+    <row r="91" spans="8:8">
+      <c r="H91" s="12"/>
+    </row>
+    <row r="92" spans="8:8">
+      <c r="H92" s="12"/>
+    </row>
+    <row r="93" spans="8:8">
+      <c r="H93" s="12"/>
+    </row>
+    <row r="94" spans="8:8">
+      <c r="H94" s="12"/>
+    </row>
+    <row r="95" spans="8:8">
+      <c r="H95" s="12"/>
+    </row>
+    <row r="96" spans="8:8">
+      <c r="H96" s="12"/>
+    </row>
+    <row r="97" spans="4:8">
+      <c r="H97" s="12"/>
+    </row>
+    <row r="98" spans="4:8">
+      <c r="H98" s="12"/>
+    </row>
+    <row r="99" spans="4:8">
+      <c r="H99" s="12"/>
+    </row>
+    <row r="100" spans="4:8">
+      <c r="H100" s="12"/>
+    </row>
+    <row r="101" spans="4:8">
+      <c r="H101" s="12"/>
+    </row>
+    <row r="102" spans="4:8">
+      <c r="H102" s="12"/>
+    </row>
+    <row r="103" spans="4:8">
+      <c r="H103" s="12"/>
+    </row>
+    <row r="104" ht="17.25" spans="4:8">
+      <c r="D104" s="13"/>
+      <c r="H104" s="12"/>
+    </row>
+    <row r="105" ht="14.25" spans="4:8">
+      <c r="E105" s="14"/>
+      <c r="H105" s="12"/>
+    </row>
+    <row r="106" spans="4:8">
+      <c r="H106" s="12"/>
+    </row>
+    <row r="107" spans="4:8">
+      <c r="H107" s="12"/>
+    </row>
+    <row r="108" spans="4:8">
+      <c r="H108" s="12"/>
+    </row>
+    <row r="109" spans="4:8">
+      <c r="H109" s="12"/>
+    </row>
+    <row r="110" spans="4:8">
+      <c r="H110" s="12"/>
+    </row>
+    <row r="111" spans="4:8">
+      <c r="H111" s="12"/>
+    </row>
+    <row r="112" spans="4:8">
+      <c r="H112" s="12"/>
+    </row>
+    <row r="113" spans="4:8">
+      <c r="H113" s="12"/>
+    </row>
+    <row r="114" spans="4:8">
+      <c r="H114" s="12"/>
+    </row>
+    <row r="115" spans="4:8">
+      <c r="H115" s="12"/>
+    </row>
+    <row r="118" ht="14.25" spans="4:8">
+      <c r="D118" s="14"/>
+    </row>
+    <row r="121" ht="14.25" spans="4:8">
+      <c r="E121" s="14"/>
+    </row>
+    <row r="122" ht="14.25" spans="4:8">
+      <c r="E122" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/VisitorLevel.xlsx
+++ b/hall/resources/sample/VisitorLevel.xlsx
@@ -165,6 +165,54 @@
     <t>15_1980000_20000</t>
   </si>
   <si>
+    <t>潮流先锋</t>
+  </si>
+  <si>
+    <t>时尚教主</t>
+  </si>
+  <si>
+    <t>街拍达人</t>
+  </si>
+  <si>
+    <t>运动健将</t>
+  </si>
+  <si>
+    <t>1990000_20000</t>
+  </si>
+  <si>
+    <t>1990000_21000</t>
+  </si>
+  <si>
+    <t>跑酷少年</t>
+  </si>
+  <si>
+    <t>滑板高手</t>
+  </si>
+  <si>
+    <t>甜心辣妹</t>
+  </si>
+  <si>
+    <t>活力少女</t>
+  </si>
+  <si>
+    <t>优雅女神</t>
+  </si>
+  <si>
+    <t>健身狂魔</t>
+  </si>
+  <si>
+    <t>1990000_30000</t>
+  </si>
+  <si>
+    <t>1990000_31000</t>
+  </si>
+  <si>
+    <t>单车骑士</t>
+  </si>
+  <si>
+    <t>登山行者</t>
+  </si>
+  <si>
     <t>文艺青年</t>
   </si>
   <si>
@@ -174,45 +222,21 @@
     <t>民谣歌手</t>
   </si>
   <si>
-    <t>潮流先锋</t>
-  </si>
-  <si>
-    <t>1990000_20000</t>
-  </si>
-  <si>
-    <t>1990000_21000</t>
-  </si>
-  <si>
-    <t>时尚教主</t>
-  </si>
-  <si>
-    <t>街拍达人</t>
-  </si>
-  <si>
     <t>马拉松客</t>
   </si>
   <si>
+    <t>1990000_40000</t>
+  </si>
+  <si>
+    <t>1990000_41000</t>
+  </si>
+  <si>
     <t>极限玩家</t>
   </si>
   <si>
     <t>科技极客</t>
   </si>
   <si>
-    <t>运动健将</t>
-  </si>
-  <si>
-    <t>1990000_30000</t>
-  </si>
-  <si>
-    <t>1990000_31000</t>
-  </si>
-  <si>
-    <t>跑酷少年</t>
-  </si>
-  <si>
-    <t>滑板高手</t>
-  </si>
-  <si>
     <t>独立画家</t>
   </si>
   <si>
@@ -222,43 +246,19 @@
     <t>古典乐迷</t>
   </si>
   <si>
-    <t>甜心辣妹</t>
-  </si>
-  <si>
-    <t>1990000_40000</t>
-  </si>
-  <si>
-    <t>1990000_41000</t>
-  </si>
-  <si>
-    <t>活力少女</t>
-  </si>
-  <si>
-    <t>优雅女神</t>
-  </si>
-  <si>
     <t>创业新贵</t>
   </si>
   <si>
+    <t>1990000_50000</t>
+  </si>
+  <si>
+    <t>1990000_51000</t>
+  </si>
+  <si>
     <t>摸金校尉</t>
   </si>
   <si>
     <t>氪金大佬</t>
-  </si>
-  <si>
-    <t>健身狂魔</t>
-  </si>
-  <si>
-    <t>1990000_50000</t>
-  </si>
-  <si>
-    <t>1990000_51000</t>
-  </si>
-  <si>
-    <t>单车骑士</t>
-  </si>
-  <si>
-    <t>登山行者</t>
   </si>
   <si>
     <t>穿搭博主</t>
@@ -1872,7 +1872,7 @@
       <c r="C24" s="2">
         <v>2</v>
       </c>
-      <c r="D24" s="1"/>
+      <c r="D24" s="2"/>
       <c r="E24" s="1">
         <v>10</v>
       </c>
@@ -1920,7 +1920,7 @@
       <c r="C26" s="2">
         <v>2</v>
       </c>
-      <c r="D26" s="1"/>
+      <c r="D26" s="2"/>
       <c r="E26" s="1">
         <v>10</v>
       </c>
@@ -1968,7 +1968,7 @@
       <c r="C28" s="2">
         <v>2</v>
       </c>
-      <c r="D28" s="1"/>
+      <c r="D28" s="2"/>
       <c r="E28" s="1">
         <v>10</v>
       </c>
@@ -2016,7 +2016,7 @@
       <c r="C30" s="2">
         <v>2</v>
       </c>
-      <c r="D30" s="1"/>
+      <c r="D30" s="2"/>
       <c r="E30" s="1">
         <v>10</v>
       </c>
@@ -2064,7 +2064,7 @@
       <c r="C32" s="2">
         <v>2</v>
       </c>
-      <c r="D32" s="1"/>
+      <c r="D32" s="2"/>
       <c r="E32" s="1">
         <v>10</v>
       </c>
@@ -2112,7 +2112,7 @@
       <c r="C34" s="2">
         <v>2</v>
       </c>
-      <c r="D34" s="1"/>
+      <c r="D34" s="2"/>
       <c r="E34" s="1">
         <v>10</v>
       </c>
@@ -2160,7 +2160,7 @@
       <c r="C36" s="2">
         <v>2</v>
       </c>
-      <c r="D36" s="1"/>
+      <c r="D36" s="2"/>
       <c r="E36" s="1">
         <v>10</v>
       </c>
@@ -2208,7 +2208,7 @@
       <c r="C38" s="2">
         <v>2</v>
       </c>
-      <c r="D38" s="1"/>
+      <c r="D38" s="2"/>
       <c r="E38" s="1">
         <v>10</v>
       </c>
@@ -2256,7 +2256,7 @@
       <c r="C40" s="2">
         <v>2</v>
       </c>
-      <c r="D40" s="1"/>
+      <c r="D40" s="2"/>
       <c r="E40" s="1">
         <v>10</v>
       </c>
@@ -2304,7 +2304,7 @@
       <c r="C42" s="2">
         <v>2</v>
       </c>
-      <c r="D42" s="1"/>
+      <c r="D42" s="2"/>
       <c r="E42" s="1">
         <v>10</v>
       </c>
@@ -2352,7 +2352,7 @@
       <c r="C44" s="2">
         <v>2</v>
       </c>
-      <c r="D44" s="1"/>
+      <c r="D44" s="2"/>
       <c r="E44" s="1">
         <v>10</v>
       </c>
@@ -2400,7 +2400,7 @@
       <c r="C46" s="2">
         <v>2</v>
       </c>
-      <c r="D46" s="1"/>
+      <c r="D46" s="2"/>
       <c r="E46" s="1">
         <v>10</v>
       </c>
@@ -2448,7 +2448,7 @@
       <c r="C48" s="2">
         <v>2</v>
       </c>
-      <c r="D48" s="1"/>
+      <c r="D48" s="2"/>
       <c r="E48" s="1">
         <v>10</v>
       </c>
@@ -2496,7 +2496,7 @@
       <c r="C50" s="2">
         <v>2</v>
       </c>
-      <c r="D50" s="1"/>
+      <c r="D50" s="2"/>
       <c r="E50" s="1">
         <v>10</v>
       </c>
@@ -2544,7 +2544,7 @@
       <c r="C52" s="2">
         <v>2</v>
       </c>
-      <c r="D52" s="1"/>
+      <c r="D52" s="2"/>
       <c r="E52" s="1">
         <v>10</v>
       </c>
@@ -2592,7 +2592,7 @@
       <c r="C54" s="2">
         <v>2</v>
       </c>
-      <c r="D54" s="1"/>
+      <c r="D54" s="2"/>
       <c r="E54" s="1">
         <v>10</v>
       </c>
@@ -2640,7 +2640,7 @@
       <c r="C56" s="2">
         <v>2</v>
       </c>
-      <c r="D56" s="1"/>
+      <c r="D56" s="2"/>
       <c r="E56" s="1">
         <v>10</v>
       </c>
@@ -2688,7 +2688,7 @@
       <c r="C58" s="2">
         <v>2</v>
       </c>
-      <c r="D58" s="1"/>
+      <c r="D58" s="2"/>
       <c r="E58" s="1">
         <v>10</v>
       </c>
@@ -2736,7 +2736,7 @@
       <c r="C60" s="2">
         <v>2</v>
       </c>
-      <c r="D60" s="1"/>
+      <c r="D60" s="2"/>
       <c r="E60" s="1">
         <v>10</v>
       </c>
@@ -2784,7 +2784,7 @@
       <c r="C62" s="2">
         <v>2</v>
       </c>
-      <c r="D62" s="1"/>
+      <c r="D62" s="2"/>
       <c r="E62" s="1">
         <v>10</v>
       </c>
@@ -2832,7 +2832,7 @@
       <c r="C64" s="2">
         <v>2</v>
       </c>
-      <c r="D64" s="1"/>
+      <c r="D64" s="2"/>
       <c r="E64" s="1">
         <v>10</v>
       </c>

--- a/hall/resources/sample/VisitorLevel.xlsx
+++ b/hall/resources/sample/VisitorLevel.xlsx
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="87">
   <si>
     <t>ID</t>
   </si>
@@ -141,28 +141,25 @@
     <t>1990000_10000</t>
   </si>
   <si>
-    <t>0_1980000_20000</t>
+    <t>10_1024008_10</t>
   </si>
   <si>
     <t>1990000_11000</t>
   </si>
   <si>
-    <t>5_1980000_20000</t>
+    <t>11_1024008_10</t>
   </si>
   <si>
     <t>复古绅士</t>
   </si>
   <si>
-    <t>8_1980000_20000</t>
-  </si>
-  <si>
-    <t>10_1980000_20000</t>
-  </si>
-  <si>
     <t>酷盖少年</t>
   </si>
   <si>
-    <t>15_1980000_20000</t>
+    <t>10_1024009_10</t>
+  </si>
+  <si>
+    <t>11_1024009_10</t>
   </si>
   <si>
     <t>潮流先锋</t>
@@ -171,6 +168,12 @@
     <t>时尚教主</t>
   </si>
   <si>
+    <t>10_1024010_10</t>
+  </si>
+  <si>
+    <t>11_1024010_10</t>
+  </si>
+  <si>
     <t>街拍达人</t>
   </si>
   <si>
@@ -180,21 +183,39 @@
     <t>1990000_20000</t>
   </si>
   <si>
+    <t>15_1024008_10</t>
+  </si>
+  <si>
     <t>1990000_21000</t>
   </si>
   <si>
+    <t>16_1024008_10</t>
+  </si>
+  <si>
     <t>跑酷少年</t>
   </si>
   <si>
     <t>滑板高手</t>
   </si>
   <si>
+    <t>15_1024009_10</t>
+  </si>
+  <si>
+    <t>16_1024009_10</t>
+  </si>
+  <si>
     <t>甜心辣妹</t>
   </si>
   <si>
     <t>活力少女</t>
   </si>
   <si>
+    <t>15_1024010_10</t>
+  </si>
+  <si>
+    <t>16_1024010_10</t>
+  </si>
+  <si>
     <t>优雅女神</t>
   </si>
   <si>
@@ -204,21 +225,39 @@
     <t>1990000_30000</t>
   </si>
   <si>
+    <t>20_1024008_10</t>
+  </si>
+  <si>
     <t>1990000_31000</t>
   </si>
   <si>
+    <t>21_1024008_10</t>
+  </si>
+  <si>
     <t>单车骑士</t>
   </si>
   <si>
     <t>登山行者</t>
   </si>
   <si>
+    <t>20_1024009_10</t>
+  </si>
+  <si>
+    <t>21_1024009_10</t>
+  </si>
+  <si>
     <t>文艺青年</t>
   </si>
   <si>
     <t>书香少女</t>
   </si>
   <si>
+    <t>20_1024010_10</t>
+  </si>
+  <si>
+    <t>21_1024010_10</t>
+  </si>
+  <si>
     <t>民谣歌手</t>
   </si>
   <si>
@@ -228,21 +267,39 @@
     <t>1990000_40000</t>
   </si>
   <si>
+    <t>25_1024008_10</t>
+  </si>
+  <si>
     <t>1990000_41000</t>
   </si>
   <si>
+    <t>26_1024008_10</t>
+  </si>
+  <si>
     <t>极限玩家</t>
   </si>
   <si>
     <t>科技极客</t>
   </si>
   <si>
+    <t>25_1024009_10</t>
+  </si>
+  <si>
+    <t>26_1024009_10</t>
+  </si>
+  <si>
     <t>独立画家</t>
   </si>
   <si>
     <t>浪漫诗人</t>
   </si>
   <si>
+    <t>25_1024010_10</t>
+  </si>
+  <si>
+    <t>26_1024010_10</t>
+  </si>
+  <si>
     <t>古典乐迷</t>
   </si>
   <si>
@@ -252,19 +309,37 @@
     <t>1990000_50000</t>
   </si>
   <si>
+    <t>30_1024008_10</t>
+  </si>
+  <si>
     <t>1990000_51000</t>
   </si>
   <si>
+    <t>31_1024008_10</t>
+  </si>
+  <si>
     <t>摸金校尉</t>
   </si>
   <si>
     <t>氪金大佬</t>
   </si>
   <si>
+    <t>30_1024009_10</t>
+  </si>
+  <si>
+    <t>31_1024009_10</t>
+  </si>
+  <si>
     <t>穿搭博主</t>
   </si>
   <si>
     <t>美妆新秀</t>
+  </si>
+  <si>
+    <t>30_1024010_10</t>
+  </si>
+  <si>
+    <t>31_1024010_10</t>
   </si>
   <si>
     <t>高定女王</t>
@@ -1474,7 +1549,7 @@
         <v>18</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1497,7 +1572,7 @@
         <v>20</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1512,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -1522,7 +1597,7 @@
         <v>18</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1545,7 +1620,7 @@
         <v>20</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1560,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -1570,7 +1645,7 @@
         <v>18</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1593,7 +1668,7 @@
         <v>20</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1608,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -1618,7 +1693,7 @@
         <v>18</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1641,7 +1716,7 @@
         <v>20</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1656,7 +1731,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
@@ -1666,7 +1741,7 @@
         <v>18</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1689,7 +1764,7 @@
         <v>20</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1704,17 +1779,17 @@
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1734,10 +1809,10 @@
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1752,17 +1827,17 @@
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E19" s="1">
         <v>0</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1782,10 +1857,10 @@
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1800,17 +1875,17 @@
         <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1830,10 +1905,10 @@
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1848,17 +1923,17 @@
         <v>1</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1878,10 +1953,10 @@
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1896,17 +1971,17 @@
         <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1926,10 +2001,10 @@
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1944,17 +2019,17 @@
         <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1974,10 +2049,10 @@
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1992,17 +2067,17 @@
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="11" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -2022,10 +2097,10 @@
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="11" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2040,17 +2115,17 @@
         <v>1</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="11" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2070,10 +2145,10 @@
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="11" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2088,17 +2163,17 @@
         <v>1</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E33" s="1">
         <v>0</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="11" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2118,10 +2193,10 @@
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="11" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2136,17 +2211,17 @@
         <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E35" s="1">
         <v>0</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="11" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2166,10 +2241,10 @@
       </c>
       <c r="F36" s="9"/>
       <c r="G36" s="11" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2184,17 +2259,17 @@
         <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E37" s="1">
         <v>0</v>
       </c>
       <c r="F37" s="9"/>
       <c r="G37" s="11" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -2214,10 +2289,10 @@
       </c>
       <c r="F38" s="9"/>
       <c r="G38" s="11" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2232,17 +2307,17 @@
         <v>1</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E39" s="1">
         <v>0</v>
       </c>
       <c r="F39" s="9"/>
       <c r="G39" s="11" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -2262,10 +2337,10 @@
       </c>
       <c r="F40" s="9"/>
       <c r="G40" s="11" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2280,17 +2355,17 @@
         <v>1</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E41" s="1">
         <v>0</v>
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="11" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2310,10 +2385,10 @@
       </c>
       <c r="F42" s="9"/>
       <c r="G42" s="11" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2328,17 +2403,17 @@
         <v>1</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E43" s="1">
         <v>0</v>
       </c>
       <c r="F43" s="9"/>
       <c r="G43" s="11" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2358,10 +2433,10 @@
       </c>
       <c r="F44" s="9"/>
       <c r="G44" s="11" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -2376,17 +2451,17 @@
         <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E45" s="1">
         <v>0</v>
       </c>
       <c r="F45" s="9"/>
       <c r="G45" s="11" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2406,10 +2481,10 @@
       </c>
       <c r="F46" s="9"/>
       <c r="G46" s="11" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -2424,17 +2499,17 @@
         <v>1</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E47" s="1">
         <v>0</v>
       </c>
       <c r="F47" s="9"/>
       <c r="G47" s="11" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2454,10 +2529,10 @@
       </c>
       <c r="F48" s="9"/>
       <c r="G48" s="11" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2472,17 +2547,17 @@
         <v>1</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E49" s="1">
         <v>0</v>
       </c>
       <c r="F49" s="9"/>
       <c r="G49" s="11" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -2502,10 +2577,10 @@
       </c>
       <c r="F50" s="9"/>
       <c r="G50" s="11" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2520,17 +2595,17 @@
         <v>1</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E51" s="1">
         <v>0</v>
       </c>
       <c r="F51" s="9"/>
       <c r="G51" s="11" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2550,10 +2625,10 @@
       </c>
       <c r="F52" s="9"/>
       <c r="G52" s="11" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2568,17 +2643,17 @@
         <v>1</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
       </c>
       <c r="F53" s="9"/>
       <c r="G53" s="11" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2598,10 +2673,10 @@
       </c>
       <c r="F54" s="9"/>
       <c r="G54" s="11" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2616,17 +2691,17 @@
         <v>1</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="E55" s="1">
         <v>0</v>
       </c>
       <c r="F55" s="9"/>
       <c r="G55" s="11" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2646,10 +2721,10 @@
       </c>
       <c r="F56" s="9"/>
       <c r="G56" s="11" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2664,17 +2739,17 @@
         <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="E57" s="1">
         <v>0</v>
       </c>
       <c r="F57" s="9"/>
       <c r="G57" s="11" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2694,10 +2769,10 @@
       </c>
       <c r="F58" s="9"/>
       <c r="G58" s="11" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2712,17 +2787,17 @@
         <v>1</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
       </c>
       <c r="F59" s="9"/>
       <c r="G59" s="11" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2742,10 +2817,10 @@
       </c>
       <c r="F60" s="9"/>
       <c r="G60" s="11" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2760,17 +2835,17 @@
         <v>1</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
       </c>
       <c r="F61" s="9"/>
       <c r="G61" s="11" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2790,10 +2865,10 @@
       </c>
       <c r="F62" s="9"/>
       <c r="G62" s="11" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2808,17 +2883,17 @@
         <v>1</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
       </c>
       <c r="F63" s="9"/>
       <c r="G63" s="11" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2838,10 +2913,10 @@
       </c>
       <c r="F64" s="9"/>
       <c r="G64" s="11" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="8:8">

--- a/hall/resources/sample/VisitorLevel.xlsx
+++ b/hall/resources/sample/VisitorLevel.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -82,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="324">
   <si>
     <t>ID</t>
   </si>
@@ -1025,6 +1030,36 @@
   <si>
     <t>高定女王</t>
   </si>
+  <si>
+    <t>独立女士</t>
+  </si>
+  <si>
+    <t>1022505_10</t>
+  </si>
+  <si>
+    <t>夜色女神</t>
+  </si>
+  <si>
+    <t>1022505_15</t>
+  </si>
+  <si>
+    <t>优雅名媛</t>
+  </si>
+  <si>
+    <t>1022505_20</t>
+  </si>
+  <si>
+    <t>时尚先锋</t>
+  </si>
+  <si>
+    <t>1022505_25</t>
+  </si>
+  <si>
+    <t>商务精英</t>
+  </si>
+  <si>
+    <t>1022505_30</t>
+  </si>
 </sst>
 </file>
 
@@ -1237,18 +1272,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1276,6 +1311,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.15"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1613,7 +1654,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
@@ -1637,16 +1678,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="6">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="5">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="7">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
@@ -1655,89 +1696,89 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1829,6 +1870,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -49840,7 +49893,7 @@
       </c>
       <c r="F1757" s="29"/>
       <c r="G1757" s="30" t="str">
-        <f t="shared" ref="G1757:G1804" si="229">G1697</f>
+        <f t="shared" ref="G1757:G1805" si="229">G1697</f>
         <v>1990000_16300</v>
       </c>
       <c r="H1757" s="27" t="str">
@@ -49863,7 +49916,7 @@
       </c>
       <c r="D1758" s="29"/>
       <c r="E1758" s="27">
-        <f t="shared" ref="E1758:E1804" si="230">E1698</f>
+        <f t="shared" ref="E1758:E1805" si="230">E1698</f>
         <v>74</v>
       </c>
       <c r="F1758" s="29"/>
@@ -50026,7 +50079,7 @@
         <v>5006</v>
       </c>
       <c r="C1764" s="28">
-        <f t="shared" ref="C1764:C1804" si="231">C1704</f>
+        <f t="shared" ref="C1764:C1809" si="231">C1704</f>
         <v>20</v>
       </c>
       <c r="D1764" s="29"/>
@@ -50404,7 +50457,7 @@
         <v>1990000_34300</v>
       </c>
       <c r="H1777" s="27" t="str">
-        <f t="shared" ref="H1777:H1804" si="232">H1775</f>
+        <f t="shared" ref="H1777:H1805" si="232">H1775</f>
         <v>30_1024010_2</v>
       </c>
     </row>
@@ -50438,7 +50491,7 @@
     </row>
     <row r="1779" spans="1:8">
       <c r="A1779" s="27">
-        <f t="shared" ref="A1779:A1804" si="233">B1779*1000+C1779</f>
+        <f t="shared" ref="A1779:A1805" si="233">B1779*1000+C1779</f>
         <v>5006035</v>
       </c>
       <c r="B1779" s="27">
@@ -51165,168 +51218,273 @@
       </c>
     </row>
     <row r="1805" spans="1:8">
+      <c r="A1805" s="31">
+        <f t="shared" si="233"/>
+        <v>9001001</v>
+      </c>
+      <c r="B1805" s="31">
+        <v>9001</v>
+      </c>
+      <c r="C1805" s="32">
+        <f t="shared" si="231"/>
+        <v>1</v>
+      </c>
+      <c r="D1805" s="31" t="s">
+        <v>314</v>
+      </c>
+      <c r="E1805" s="31">
+        <v>9999999</v>
+      </c>
+      <c r="F1805" s="33"/>
+      <c r="G1805" s="34" t="s">
+        <v>315</v>
+      </c>
       <c r="H1805" s="31"/>
     </row>
     <row r="1806" spans="1:8">
+      <c r="A1806" s="31">
+        <f>B1806*1000+C1806</f>
+        <v>9002002</v>
+      </c>
+      <c r="B1806" s="31">
+        <v>9002</v>
+      </c>
+      <c r="C1806" s="32">
+        <f t="shared" si="231"/>
+        <v>2</v>
+      </c>
+      <c r="D1806" s="31" t="s">
+        <v>316</v>
+      </c>
+      <c r="E1806" s="31">
+        <v>9999999</v>
+      </c>
+      <c r="F1806" s="33"/>
+      <c r="G1806" s="34" t="s">
+        <v>317</v>
+      </c>
       <c r="H1806" s="31"/>
     </row>
     <row r="1807" spans="1:8">
+      <c r="A1807" s="31">
+        <f>B1807*1000+C1807</f>
+        <v>9003003</v>
+      </c>
+      <c r="B1807" s="31">
+        <v>9003</v>
+      </c>
+      <c r="C1807" s="32">
+        <f t="shared" si="231"/>
+        <v>3</v>
+      </c>
+      <c r="D1807" s="31" t="s">
+        <v>318</v>
+      </c>
+      <c r="E1807" s="31">
+        <v>9999999</v>
+      </c>
+      <c r="F1807" s="33"/>
+      <c r="G1807" s="34" t="s">
+        <v>319</v>
+      </c>
       <c r="H1807" s="31"/>
     </row>
     <row r="1808" spans="1:8">
+      <c r="A1808" s="31">
+        <f>B1808*1000+C1808</f>
+        <v>9004004</v>
+      </c>
+      <c r="B1808" s="31">
+        <v>9004</v>
+      </c>
+      <c r="C1808" s="32">
+        <f t="shared" si="231"/>
+        <v>4</v>
+      </c>
+      <c r="D1808" s="31" t="s">
+        <v>320</v>
+      </c>
+      <c r="E1808" s="31">
+        <v>9999999</v>
+      </c>
+      <c r="F1808" s="33"/>
+      <c r="G1808" s="34" t="s">
+        <v>321</v>
+      </c>
       <c r="H1808" s="31"/>
     </row>
-    <row r="1809" spans="8:8">
+    <row r="1809" spans="1:8">
+      <c r="A1809" s="31">
+        <f>B1809*1000+C1809</f>
+        <v>9005005</v>
+      </c>
+      <c r="B1809" s="31">
+        <v>9005</v>
+      </c>
+      <c r="C1809" s="32">
+        <f t="shared" si="231"/>
+        <v>5</v>
+      </c>
+      <c r="D1809" s="31" t="s">
+        <v>322</v>
+      </c>
+      <c r="E1809" s="31">
+        <v>9999999</v>
+      </c>
+      <c r="F1809" s="33"/>
+      <c r="G1809" s="34" t="s">
+        <v>323</v>
+      </c>
       <c r="H1809" s="31"/>
     </row>
-    <row r="1810" spans="8:8">
-      <c r="H1810" s="31"/>
-    </row>
-    <row r="1811" spans="8:8">
-      <c r="H1811" s="31"/>
-    </row>
-    <row r="1812" spans="8:8">
-      <c r="H1812" s="31"/>
-    </row>
-    <row r="1813" spans="8:8">
-      <c r="H1813" s="31"/>
-    </row>
-    <row r="1814" spans="8:8">
-      <c r="H1814" s="31"/>
-    </row>
-    <row r="1815" spans="8:8">
-      <c r="H1815" s="31"/>
-    </row>
-    <row r="1816" spans="8:8">
-      <c r="H1816" s="31"/>
-    </row>
-    <row r="1817" spans="8:8">
-      <c r="H1817" s="31"/>
-    </row>
-    <row r="1818" spans="8:8">
-      <c r="H1818" s="31"/>
-    </row>
-    <row r="1819" spans="8:8">
-      <c r="H1819" s="31"/>
-    </row>
-    <row r="1820" spans="8:8">
-      <c r="H1820" s="31"/>
-    </row>
-    <row r="1821" spans="8:8">
-      <c r="H1821" s="31"/>
-    </row>
-    <row r="1822" spans="8:8">
-      <c r="H1822" s="31"/>
-    </row>
-    <row r="1823" spans="8:8">
-      <c r="H1823" s="31"/>
-    </row>
-    <row r="1824" spans="8:8">
-      <c r="H1824" s="31"/>
+    <row r="1810" spans="1:8">
+      <c r="H1810" s="35"/>
+    </row>
+    <row r="1811" spans="1:8">
+      <c r="H1811" s="35"/>
+    </row>
+    <row r="1812" spans="1:8">
+      <c r="H1812" s="35"/>
+    </row>
+    <row r="1813" spans="1:8">
+      <c r="H1813" s="35"/>
+    </row>
+    <row r="1814" spans="1:8">
+      <c r="H1814" s="35"/>
+    </row>
+    <row r="1815" spans="1:8">
+      <c r="H1815" s="35"/>
+    </row>
+    <row r="1816" spans="1:8">
+      <c r="H1816" s="35"/>
+    </row>
+    <row r="1817" spans="1:8">
+      <c r="H1817" s="35"/>
+    </row>
+    <row r="1818" spans="1:8">
+      <c r="H1818" s="35"/>
+    </row>
+    <row r="1819" spans="1:8">
+      <c r="H1819" s="35"/>
+    </row>
+    <row r="1820" spans="1:8">
+      <c r="H1820" s="35"/>
+    </row>
+    <row r="1821" spans="1:8">
+      <c r="H1821" s="35"/>
+    </row>
+    <row r="1822" spans="1:8">
+      <c r="H1822" s="35"/>
+    </row>
+    <row r="1823" spans="1:8">
+      <c r="H1823" s="35"/>
+    </row>
+    <row r="1824" spans="1:8">
+      <c r="H1824" s="35"/>
     </row>
     <row r="1825" spans="8:8">
-      <c r="H1825" s="31"/>
+      <c r="H1825" s="35"/>
     </row>
     <row r="1826" spans="8:8">
-      <c r="H1826" s="31"/>
+      <c r="H1826" s="35"/>
     </row>
     <row r="1827" spans="8:8">
-      <c r="H1827" s="31"/>
+      <c r="H1827" s="35"/>
     </row>
     <row r="1828" spans="8:8">
-      <c r="H1828" s="31"/>
+      <c r="H1828" s="35"/>
     </row>
     <row r="1829" spans="8:8">
-      <c r="H1829" s="31"/>
+      <c r="H1829" s="35"/>
     </row>
     <row r="1830" spans="8:8">
-      <c r="H1830" s="31"/>
+      <c r="H1830" s="35"/>
     </row>
     <row r="1831" spans="8:8">
-      <c r="H1831" s="31"/>
+      <c r="H1831" s="35"/>
     </row>
     <row r="1832" spans="8:8">
-      <c r="H1832" s="31"/>
+      <c r="H1832" s="35"/>
     </row>
     <row r="1833" spans="8:8">
-      <c r="H1833" s="31"/>
+      <c r="H1833" s="35"/>
     </row>
     <row r="1834" spans="8:8">
-      <c r="H1834" s="31"/>
+      <c r="H1834" s="35"/>
     </row>
     <row r="1835" spans="8:8">
-      <c r="H1835" s="31"/>
+      <c r="H1835" s="35"/>
     </row>
     <row r="1836" spans="8:8">
-      <c r="H1836" s="31"/>
+      <c r="H1836" s="35"/>
     </row>
     <row r="1837" spans="8:8">
-      <c r="H1837" s="31"/>
+      <c r="H1837" s="35"/>
     </row>
     <row r="1838" spans="8:8">
-      <c r="H1838" s="31"/>
+      <c r="H1838" s="35"/>
     </row>
     <row r="1839" spans="8:8">
-      <c r="H1839" s="31"/>
+      <c r="H1839" s="35"/>
     </row>
     <row r="1840" spans="8:8">
-      <c r="H1840" s="31"/>
+      <c r="H1840" s="35"/>
     </row>
     <row r="1841" spans="4:8">
-      <c r="H1841" s="31"/>
+      <c r="H1841" s="35"/>
     </row>
     <row r="1842" spans="4:8">
-      <c r="H1842" s="31"/>
+      <c r="H1842" s="35"/>
     </row>
     <row r="1843" spans="4:8">
-      <c r="H1843" s="31"/>
+      <c r="H1843" s="35"/>
     </row>
     <row r="1844" ht="17.25" spans="4:8">
-      <c r="D1844" s="32"/>
-      <c r="H1844" s="31"/>
+      <c r="D1844" s="36"/>
+      <c r="H1844" s="35"/>
     </row>
     <row r="1845" ht="14.25" spans="4:8">
-      <c r="E1845" s="33"/>
-      <c r="H1845" s="31"/>
+      <c r="E1845" s="37"/>
+      <c r="H1845" s="35"/>
     </row>
     <row r="1846" spans="4:8">
-      <c r="H1846" s="31"/>
+      <c r="H1846" s="35"/>
     </row>
     <row r="1847" spans="4:8">
-      <c r="H1847" s="31"/>
+      <c r="H1847" s="35"/>
     </row>
     <row r="1848" spans="4:8">
-      <c r="H1848" s="31"/>
+      <c r="H1848" s="35"/>
     </row>
     <row r="1849" spans="4:8">
-      <c r="H1849" s="31"/>
+      <c r="H1849" s="35"/>
     </row>
     <row r="1850" spans="4:8">
-      <c r="H1850" s="31"/>
+      <c r="H1850" s="35"/>
     </row>
     <row r="1851" spans="4:8">
-      <c r="H1851" s="31"/>
+      <c r="H1851" s="35"/>
     </row>
     <row r="1852" spans="4:8">
-      <c r="H1852" s="31"/>
+      <c r="H1852" s="35"/>
     </row>
     <row r="1853" spans="4:8">
-      <c r="H1853" s="31"/>
+      <c r="H1853" s="35"/>
     </row>
     <row r="1854" spans="4:8">
-      <c r="H1854" s="31"/>
+      <c r="H1854" s="35"/>
     </row>
     <row r="1855" spans="4:8">
-      <c r="H1855" s="31"/>
+      <c r="H1855" s="35"/>
     </row>
     <row r="1858" ht="14.25" spans="4:5">
-      <c r="D1858" s="33"/>
+      <c r="D1858" s="37"/>
     </row>
     <row r="1861" ht="14.25" spans="4:5">
-      <c r="E1861" s="33"/>
+      <c r="E1861" s="37"/>
     </row>
     <row r="1862" ht="14.25" spans="4:5">
-      <c r="E1862" s="33"/>
+      <c r="E1862" s="37"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/VisitorLevel.xlsx
+++ b/hall/resources/sample/VisitorLevel.xlsx
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="276">
   <si>
     <t>ID</t>
   </si>
@@ -704,10 +704,10 @@
     <t>创业新贵</t>
   </si>
   <si>
-    <t>30_1024008_2</t>
+    <t>30_1024008_2|30_1022505_10</t>
   </si>
   <si>
-    <t>31_1024008_2</t>
+    <t>31_1024008_2|30_1022505_10</t>
   </si>
   <si>
     <t>1990000_700</t>
@@ -855,6 +855,12 @@
   </si>
   <si>
     <t>摸金校尉</t>
+  </si>
+  <si>
+    <t>30_1024008_2</t>
+  </si>
+  <si>
+    <t>31_1024008_2</t>
   </si>
   <si>
     <t>氪金大佬</t>
@@ -41238,7 +41244,7 @@
       </c>
       <c r="H1447" s="27" t="str">
         <f>H1445</f>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1448" spans="1:8">
@@ -41263,7 +41269,7 @@
       </c>
       <c r="H1448" s="27" t="str">
         <f t="shared" ref="H1448:H1456" si="187">H1446</f>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1449" spans="1:8">
@@ -41288,7 +41294,7 @@
       </c>
       <c r="H1449" s="27" t="str">
         <f t="shared" si="187"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1450" spans="1:8">
@@ -41313,7 +41319,7 @@
       </c>
       <c r="H1450" s="27" t="str">
         <f t="shared" si="187"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1451" spans="1:8">
@@ -41338,7 +41344,7 @@
       </c>
       <c r="H1451" s="27" t="str">
         <f t="shared" si="187"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1452" spans="1:8">
@@ -41363,7 +41369,7 @@
       </c>
       <c r="H1452" s="27" t="str">
         <f t="shared" si="187"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1453" spans="1:8">
@@ -41388,7 +41394,7 @@
       </c>
       <c r="H1453" s="27" t="str">
         <f t="shared" si="187"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1454" spans="1:8">
@@ -41413,7 +41419,7 @@
       </c>
       <c r="H1454" s="27" t="str">
         <f t="shared" si="187"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1455" spans="1:8">
@@ -41438,7 +41444,7 @@
       </c>
       <c r="H1455" s="27" t="str">
         <f t="shared" si="187"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1456" spans="1:8">
@@ -41463,7 +41469,7 @@
       </c>
       <c r="H1456" s="27" t="str">
         <f t="shared" si="187"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1457" spans="1:8">
@@ -41488,7 +41494,7 @@
       </c>
       <c r="H1457" s="27" t="str">
         <f t="shared" ref="H1457:H1520" si="188">H1455</f>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1458" spans="1:8">
@@ -41513,7 +41519,7 @@
       </c>
       <c r="H1458" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1459" spans="1:8">
@@ -41538,7 +41544,7 @@
       </c>
       <c r="H1459" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1460" spans="1:8">
@@ -41563,7 +41569,7 @@
       </c>
       <c r="H1460" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1461" spans="1:8">
@@ -41588,7 +41594,7 @@
       </c>
       <c r="H1461" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1462" spans="1:8">
@@ -41613,7 +41619,7 @@
       </c>
       <c r="H1462" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1463" spans="1:8">
@@ -41638,7 +41644,7 @@
       </c>
       <c r="H1463" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1464" spans="1:8">
@@ -41663,7 +41669,7 @@
       </c>
       <c r="H1464" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1465" spans="1:8">
@@ -41688,7 +41694,7 @@
       </c>
       <c r="H1465" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1466" spans="1:8">
@@ -41713,7 +41719,7 @@
       </c>
       <c r="H1466" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1467" spans="1:8">
@@ -41738,7 +41744,7 @@
       </c>
       <c r="H1467" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1468" spans="1:8">
@@ -41763,7 +41769,7 @@
       </c>
       <c r="H1468" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1469" spans="1:8">
@@ -41788,7 +41794,7 @@
       </c>
       <c r="H1469" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1470" spans="1:8">
@@ -41813,7 +41819,7 @@
       </c>
       <c r="H1470" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1471" spans="1:8">
@@ -41838,7 +41844,7 @@
       </c>
       <c r="H1471" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1472" spans="1:8">
@@ -41863,7 +41869,7 @@
       </c>
       <c r="H1472" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1473" spans="1:8">
@@ -41888,7 +41894,7 @@
       </c>
       <c r="H1473" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1474" spans="1:8">
@@ -41913,7 +41919,7 @@
       </c>
       <c r="H1474" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1475" spans="1:8">
@@ -41938,7 +41944,7 @@
       </c>
       <c r="H1475" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1476" spans="1:8">
@@ -41963,7 +41969,7 @@
       </c>
       <c r="H1476" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1477" spans="1:8">
@@ -41988,7 +41994,7 @@
       </c>
       <c r="H1477" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1478" spans="1:8">
@@ -42013,7 +42019,7 @@
       </c>
       <c r="H1478" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1479" spans="1:8">
@@ -42038,7 +42044,7 @@
       </c>
       <c r="H1479" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1480" spans="1:8">
@@ -42063,7 +42069,7 @@
       </c>
       <c r="H1480" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1481" spans="1:8">
@@ -42088,7 +42094,7 @@
       </c>
       <c r="H1481" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1482" spans="1:8">
@@ -42113,7 +42119,7 @@
       </c>
       <c r="H1482" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1483" spans="1:8">
@@ -42138,7 +42144,7 @@
       </c>
       <c r="H1483" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1484" spans="1:8">
@@ -42163,7 +42169,7 @@
       </c>
       <c r="H1484" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1485" spans="1:8">
@@ -42188,7 +42194,7 @@
       </c>
       <c r="H1485" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1486" spans="1:8">
@@ -42213,7 +42219,7 @@
       </c>
       <c r="H1486" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1487" spans="1:8">
@@ -42238,7 +42244,7 @@
       </c>
       <c r="H1487" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1488" spans="1:8">
@@ -42263,7 +42269,7 @@
       </c>
       <c r="H1488" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1489" spans="1:8">
@@ -42288,7 +42294,7 @@
       </c>
       <c r="H1489" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1490" spans="1:8">
@@ -42313,7 +42319,7 @@
       </c>
       <c r="H1490" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1491" spans="1:8">
@@ -42338,7 +42344,7 @@
       </c>
       <c r="H1491" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1492" spans="1:8">
@@ -42363,7 +42369,7 @@
       </c>
       <c r="H1492" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1493" spans="1:8">
@@ -42388,7 +42394,7 @@
       </c>
       <c r="H1493" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1494" spans="1:8">
@@ -42413,7 +42419,7 @@
       </c>
       <c r="H1494" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1495" spans="1:8">
@@ -42438,7 +42444,7 @@
       </c>
       <c r="H1495" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1496" spans="1:8">
@@ -42463,7 +42469,7 @@
       </c>
       <c r="H1496" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1497" spans="1:8">
@@ -42488,7 +42494,7 @@
       </c>
       <c r="H1497" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1498" spans="1:8">
@@ -42513,7 +42519,7 @@
       </c>
       <c r="H1498" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1499" spans="1:8">
@@ -42538,7 +42544,7 @@
       </c>
       <c r="H1499" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1500" spans="1:8">
@@ -42563,7 +42569,7 @@
       </c>
       <c r="H1500" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1501" spans="1:8">
@@ -42588,7 +42594,7 @@
       </c>
       <c r="H1501" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1502" spans="1:8">
@@ -42613,7 +42619,7 @@
       </c>
       <c r="H1502" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1503" spans="1:8">
@@ -42638,7 +42644,7 @@
       </c>
       <c r="H1503" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1504" spans="1:8">
@@ -42663,7 +42669,7 @@
       </c>
       <c r="H1504" s="27" t="str">
         <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1505" spans="1:8">
@@ -42690,9 +42696,8 @@
         <f>G1445</f>
         <v>1990000_200</v>
       </c>
-      <c r="H1505" s="27" t="str">
-        <f t="shared" si="188"/>
-        <v>30_1024008_2</v>
+      <c r="H1505" s="27" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="1506" spans="1:8">
@@ -42718,9 +42723,8 @@
         <f t="shared" ref="G1506:G1537" si="193">G1446</f>
         <v>1990000_250</v>
       </c>
-      <c r="H1506" s="27" t="str">
-        <f t="shared" si="188"/>
-        <v>31_1024008_2</v>
+      <c r="H1506" s="27" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="1507" spans="1:8">
@@ -44360,7 +44364,7 @@
         <v>1</v>
       </c>
       <c r="D1565" s="28" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E1565" s="27">
         <f t="shared" si="198"/>
@@ -44372,7 +44376,7 @@
         <v>1990000_200</v>
       </c>
       <c r="H1565" s="27" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="1566" spans="1:8">
@@ -44399,7 +44403,7 @@
         <v>1990000_250</v>
       </c>
       <c r="H1566" s="27" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="1567" spans="1:8">
@@ -46039,7 +46043,7 @@
         <v>1</v>
       </c>
       <c r="D1625" s="28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E1625" s="27">
         <f t="shared" si="204"/>
@@ -47720,7 +47724,7 @@
         <v>1</v>
       </c>
       <c r="D1685" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E1685" s="27">
         <f t="shared" si="214"/>
@@ -47732,7 +47736,7 @@
         <v>1990000_200</v>
       </c>
       <c r="H1685" s="27" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="1686" spans="1:8">
@@ -47759,7 +47763,7 @@
         <v>1990000_250</v>
       </c>
       <c r="H1686" s="27" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="1687" spans="1:8">
@@ -49399,7 +49403,7 @@
         <v>1</v>
       </c>
       <c r="D1745" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E1745" s="27">
         <f t="shared" si="222"/>
@@ -51080,14 +51084,14 @@
         <v>1</v>
       </c>
       <c r="D1805" s="31" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E1805" s="31">
         <v>9999999</v>
       </c>
       <c r="F1805" s="33"/>
       <c r="G1805" s="34" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H1805" s="31"/>
     </row>
@@ -51104,14 +51108,14 @@
         <v>2</v>
       </c>
       <c r="D1806" s="31" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E1806" s="31">
         <v>9999999</v>
       </c>
       <c r="F1806" s="33"/>
       <c r="G1806" s="34" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H1806" s="31"/>
     </row>
@@ -51128,14 +51132,14 @@
         <v>3</v>
       </c>
       <c r="D1807" s="31" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1807" s="31">
         <v>9999999</v>
       </c>
       <c r="F1807" s="33"/>
       <c r="G1807" s="34" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H1807" s="31"/>
     </row>
@@ -51152,14 +51156,14 @@
         <v>4</v>
       </c>
       <c r="D1808" s="31" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E1808" s="31">
         <v>9999999</v>
       </c>
       <c r="F1808" s="33"/>
       <c r="G1808" s="34" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H1808" s="31"/>
     </row>
@@ -51176,14 +51180,14 @@
         <v>5</v>
       </c>
       <c r="D1809" s="31" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E1809" s="31">
         <v>9999999</v>
       </c>
       <c r="F1809" s="33"/>
       <c r="G1809" s="34" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H1809" s="31"/>
     </row>

--- a/hall/resources/sample/VisitorLevel.xlsx
+++ b/hall/resources/sample/VisitorLevel.xlsx
@@ -419,10 +419,10 @@
     <t>健身狂魔</t>
   </si>
   <si>
-    <t>20_1024008_2|20_1022502_1</t>
+    <t>20_1024008_2</t>
   </si>
   <si>
-    <t>21_1024008_2|21_1022502_1</t>
+    <t>21_1024008_2</t>
   </si>
   <si>
     <t>1990000_350</t>
@@ -536,10 +536,10 @@
     <t>登山行者</t>
   </si>
   <si>
-    <t>20_1024009_2|20_1022502_1</t>
+    <t>20_1024009_2</t>
   </si>
   <si>
-    <t>21_1024009_2|21_1022502_1</t>
+    <t>21_1024009_2</t>
   </si>
   <si>
     <t>文艺青年</t>
@@ -548,10 +548,10 @@
     <t>书香少女</t>
   </si>
   <si>
-    <t>20_1024010_2|20_1022502_1</t>
+    <t>20_1024010_2</t>
   </si>
   <si>
-    <t>21_1024010_2|21_1022502_1</t>
+    <t>21_1024010_2</t>
   </si>
   <si>
     <t>民谣歌手</t>
@@ -560,10 +560,10 @@
     <t>马拉松客</t>
   </si>
   <si>
-    <t>25_1024008_2|25_1022502_1</t>
+    <t>25_1024008_2</t>
   </si>
   <si>
-    <t>26_1024008_2|26_1022502_1</t>
+    <t>26_1024008_2</t>
   </si>
   <si>
     <t>1990000_375</t>
@@ -674,10 +674,10 @@
     <t>科技极客</t>
   </si>
   <si>
-    <t>25_1024009_2|25_1022502_1</t>
+    <t>25_1024009_2</t>
   </si>
   <si>
-    <t>26_1024009_2|26_1022502_1</t>
+    <t>26_1024009_2</t>
   </si>
   <si>
     <t>独立画家</t>
@@ -686,28 +686,28 @@
     <t>浪漫诗人</t>
   </si>
   <si>
-    <t>25_1024010_2|25_1022502_1</t>
+    <t>25_1024010_2</t>
   </si>
   <si>
-    <t>26_1024010_2|26_1022502_1</t>
+    <t>26_1024010_2</t>
   </si>
   <si>
     <t>古典乐迷</t>
   </si>
   <si>
-    <t>25_1024010_2|30_1024001_1|25_1022502_1</t>
+    <t>25_1024010_2|30_1024001_1</t>
   </si>
   <si>
-    <t>26_1024010_2|30_1024001_1|26_1022502_1</t>
+    <t>26_1024010_2|30_1024001_1</t>
   </si>
   <si>
     <t>创业新贵</t>
   </si>
   <si>
-    <t>30_1024008_2|30_1022505_10|30_1022502_1</t>
+    <t>30_1024008_2|30_1022505_10</t>
   </si>
   <si>
-    <t>31_1024008_2|30_1022505_10|30_1022502_1</t>
+    <t>31_1024008_2|30_1022505_10</t>
   </si>
   <si>
     <t>1990000_700</t>
@@ -857,19 +857,19 @@
     <t>摸金校尉</t>
   </si>
   <si>
-    <t>30_1024008_2|30_1022502_1</t>
+    <t>30_1024008_2</t>
   </si>
   <si>
-    <t>31_1024008_2|30_1022502_1</t>
+    <t>31_1024008_2</t>
   </si>
   <si>
     <t>氪金大佬</t>
   </si>
   <si>
-    <t>30_1024009_2|30_1022502_1</t>
+    <t>30_1024009_2</t>
   </si>
   <si>
-    <t>31_1024009_2|30_1022502_1</t>
+    <t>31_1024009_2</t>
   </si>
   <si>
     <t>穿搭博主</t>
@@ -878,10 +878,10 @@
     <t>美妆新秀</t>
   </si>
   <si>
-    <t>30_1024010_2|30_1022502_1</t>
+    <t>30_1024010_2</t>
   </si>
   <si>
-    <t>31_1024010_2|30_1022502_1</t>
+    <t>31_1024010_2</t>
   </si>
   <si>
     <t>高定女王</t>
@@ -21858,7 +21858,7 @@
       </c>
       <c r="H727" s="23" t="str">
         <f>H725</f>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="728" spans="1:8">
@@ -21883,7 +21883,7 @@
       </c>
       <c r="H728" s="23" t="str">
         <f>H726</f>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="729" spans="1:8">
@@ -21908,7 +21908,7 @@
       </c>
       <c r="H729" s="23" t="str">
         <f t="shared" ref="H729:H760" si="97">H727</f>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="730" spans="1:8">
@@ -21933,7 +21933,7 @@
       </c>
       <c r="H730" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="731" spans="1:8">
@@ -21958,7 +21958,7 @@
       </c>
       <c r="H731" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="732" spans="1:8">
@@ -21983,7 +21983,7 @@
       </c>
       <c r="H732" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="733" spans="1:8">
@@ -22008,7 +22008,7 @@
       </c>
       <c r="H733" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="734" spans="1:8">
@@ -22033,7 +22033,7 @@
       </c>
       <c r="H734" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="735" spans="1:8">
@@ -22058,7 +22058,7 @@
       </c>
       <c r="H735" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="736" spans="1:8">
@@ -22083,7 +22083,7 @@
       </c>
       <c r="H736" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="737" spans="1:8">
@@ -22108,7 +22108,7 @@
       </c>
       <c r="H737" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="738" spans="1:8">
@@ -22133,7 +22133,7 @@
       </c>
       <c r="H738" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="739" spans="1:8">
@@ -22158,7 +22158,7 @@
       </c>
       <c r="H739" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="740" spans="1:8">
@@ -22183,7 +22183,7 @@
       </c>
       <c r="H740" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="741" spans="1:8">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="H741" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="742" spans="1:8">
@@ -22233,7 +22233,7 @@
       </c>
       <c r="H742" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="743" spans="1:8">
@@ -22258,7 +22258,7 @@
       </c>
       <c r="H743" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="744" spans="1:8">
@@ -22283,7 +22283,7 @@
       </c>
       <c r="H744" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="745" spans="1:8">
@@ -22308,7 +22308,7 @@
       </c>
       <c r="H745" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="746" spans="1:8">
@@ -22333,7 +22333,7 @@
       </c>
       <c r="H746" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="747" spans="1:8">
@@ -22358,7 +22358,7 @@
       </c>
       <c r="H747" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="748" spans="1:8">
@@ -22383,7 +22383,7 @@
       </c>
       <c r="H748" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="749" spans="1:8">
@@ -22408,7 +22408,7 @@
       </c>
       <c r="H749" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="750" spans="1:8">
@@ -22433,7 +22433,7 @@
       </c>
       <c r="H750" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="751" spans="1:8">
@@ -22458,7 +22458,7 @@
       </c>
       <c r="H751" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="752" spans="1:8">
@@ -22483,7 +22483,7 @@
       </c>
       <c r="H752" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="753" spans="1:8">
@@ -22508,7 +22508,7 @@
       </c>
       <c r="H753" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="754" spans="1:8">
@@ -22533,7 +22533,7 @@
       </c>
       <c r="H754" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="755" spans="1:8">
@@ -22558,7 +22558,7 @@
       </c>
       <c r="H755" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="756" spans="1:8">
@@ -22583,7 +22583,7 @@
       </c>
       <c r="H756" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="757" spans="1:8">
@@ -22608,7 +22608,7 @@
       </c>
       <c r="H757" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="758" spans="1:8">
@@ -22633,7 +22633,7 @@
       </c>
       <c r="H758" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="759" spans="1:8">
@@ -22658,7 +22658,7 @@
       </c>
       <c r="H759" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="760" spans="1:8">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="H760" s="23" t="str">
         <f t="shared" si="97"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="761" spans="1:8">
@@ -22708,7 +22708,7 @@
       </c>
       <c r="H761" s="23" t="str">
         <f t="shared" ref="H761:H784" si="100">H759</f>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="762" spans="1:8">
@@ -22733,7 +22733,7 @@
       </c>
       <c r="H762" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="763" spans="1:8">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="H763" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="764" spans="1:8">
@@ -22783,7 +22783,7 @@
       </c>
       <c r="H764" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="765" spans="1:8">
@@ -22808,7 +22808,7 @@
       </c>
       <c r="H765" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="766" spans="1:8">
@@ -22833,7 +22833,7 @@
       </c>
       <c r="H766" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="767" spans="1:8">
@@ -22858,7 +22858,7 @@
       </c>
       <c r="H767" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="768" spans="1:8">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="H768" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="769" spans="1:8">
@@ -22908,7 +22908,7 @@
       </c>
       <c r="H769" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="770" spans="1:8">
@@ -22933,7 +22933,7 @@
       </c>
       <c r="H770" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="771" spans="1:8">
@@ -22958,7 +22958,7 @@
       </c>
       <c r="H771" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="772" spans="1:8">
@@ -22983,7 +22983,7 @@
       </c>
       <c r="H772" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="773" spans="1:8">
@@ -23008,7 +23008,7 @@
       </c>
       <c r="H773" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="774" spans="1:8">
@@ -23033,7 +23033,7 @@
       </c>
       <c r="H774" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="775" spans="1:8">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="H775" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="776" spans="1:8">
@@ -23083,7 +23083,7 @@
       </c>
       <c r="H776" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="777" spans="1:8">
@@ -23108,7 +23108,7 @@
       </c>
       <c r="H777" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="778" spans="1:8">
@@ -23133,7 +23133,7 @@
       </c>
       <c r="H778" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="779" spans="1:8">
@@ -23158,7 +23158,7 @@
       </c>
       <c r="H779" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="780" spans="1:8">
@@ -23183,7 +23183,7 @@
       </c>
       <c r="H780" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="781" spans="1:8">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="H781" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="782" spans="1:8">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="H782" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="783" spans="1:8">
@@ -23258,7 +23258,7 @@
       </c>
       <c r="H783" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="784" spans="1:8">
@@ -23283,7 +23283,7 @@
       </c>
       <c r="H784" s="23" t="str">
         <f t="shared" si="100"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="785" spans="1:8">
@@ -23312,7 +23312,7 @@
       </c>
       <c r="H785" s="23" t="str">
         <f>H725</f>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="786" spans="1:8">
@@ -23340,7 +23340,7 @@
       </c>
       <c r="H786" s="23" t="str">
         <f>H726</f>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="787" spans="1:8">
@@ -23368,7 +23368,7 @@
       </c>
       <c r="H787" s="23" t="str">
         <f>H727</f>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="788" spans="1:8">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="H788" s="23" t="str">
         <f>H728</f>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="789" spans="1:8">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="H789" s="23" t="str">
         <f t="shared" ref="H789:H820" si="106">H729</f>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="790" spans="1:8">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="H790" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="791" spans="1:8">
@@ -23480,7 +23480,7 @@
       </c>
       <c r="H791" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="792" spans="1:8">
@@ -23508,7 +23508,7 @@
       </c>
       <c r="H792" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="793" spans="1:8">
@@ -23536,7 +23536,7 @@
       </c>
       <c r="H793" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="794" spans="1:8">
@@ -23564,7 +23564,7 @@
       </c>
       <c r="H794" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="795" spans="1:8">
@@ -23592,7 +23592,7 @@
       </c>
       <c r="H795" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="796" spans="1:8">
@@ -23620,7 +23620,7 @@
       </c>
       <c r="H796" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="797" spans="1:8">
@@ -23648,7 +23648,7 @@
       </c>
       <c r="H797" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="798" spans="1:8">
@@ -23676,7 +23676,7 @@
       </c>
       <c r="H798" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="799" spans="1:8">
@@ -23704,7 +23704,7 @@
       </c>
       <c r="H799" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="800" spans="1:8">
@@ -23732,7 +23732,7 @@
       </c>
       <c r="H800" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="801" spans="1:8">
@@ -23760,7 +23760,7 @@
       </c>
       <c r="H801" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="802" spans="1:8">
@@ -23788,7 +23788,7 @@
       </c>
       <c r="H802" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="803" spans="1:8">
@@ -23816,7 +23816,7 @@
       </c>
       <c r="H803" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="804" spans="1:8">
@@ -23844,7 +23844,7 @@
       </c>
       <c r="H804" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="805" spans="1:8">
@@ -23872,7 +23872,7 @@
       </c>
       <c r="H805" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="806" spans="1:8">
@@ -23900,7 +23900,7 @@
       </c>
       <c r="H806" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="807" spans="1:8">
@@ -23928,7 +23928,7 @@
       </c>
       <c r="H807" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="808" spans="1:8">
@@ -23956,7 +23956,7 @@
       </c>
       <c r="H808" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="809" spans="1:8">
@@ -23984,7 +23984,7 @@
       </c>
       <c r="H809" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="810" spans="1:8">
@@ -24012,7 +24012,7 @@
       </c>
       <c r="H810" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="811" spans="1:8">
@@ -24040,7 +24040,7 @@
       </c>
       <c r="H811" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="812" spans="1:8">
@@ -24068,7 +24068,7 @@
       </c>
       <c r="H812" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="813" spans="1:8">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="H813" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="814" spans="1:8">
@@ -24124,7 +24124,7 @@
       </c>
       <c r="H814" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="815" spans="1:8">
@@ -24152,7 +24152,7 @@
       </c>
       <c r="H815" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="816" spans="1:8">
@@ -24180,7 +24180,7 @@
       </c>
       <c r="H816" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="817" spans="1:8">
@@ -24208,7 +24208,7 @@
       </c>
       <c r="H817" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="818" spans="1:8">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="H818" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="819" spans="1:8">
@@ -24264,7 +24264,7 @@
       </c>
       <c r="H819" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="820" spans="1:8">
@@ -24292,7 +24292,7 @@
       </c>
       <c r="H820" s="23" t="str">
         <f t="shared" si="106"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="821" spans="1:8">
@@ -24320,7 +24320,7 @@
       </c>
       <c r="H821" s="23" t="str">
         <f t="shared" ref="H821:H844" si="112">H761</f>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="822" spans="1:8">
@@ -24348,7 +24348,7 @@
       </c>
       <c r="H822" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="823" spans="1:8">
@@ -24376,7 +24376,7 @@
       </c>
       <c r="H823" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="824" spans="1:8">
@@ -24404,7 +24404,7 @@
       </c>
       <c r="H824" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="825" spans="1:8">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="H825" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="826" spans="1:8">
@@ -24460,7 +24460,7 @@
       </c>
       <c r="H826" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="827" spans="1:8">
@@ -24488,7 +24488,7 @@
       </c>
       <c r="H827" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="828" spans="1:8">
@@ -24516,7 +24516,7 @@
       </c>
       <c r="H828" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="829" spans="1:8">
@@ -24544,7 +24544,7 @@
       </c>
       <c r="H829" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="830" spans="1:8">
@@ -24572,7 +24572,7 @@
       </c>
       <c r="H830" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="831" spans="1:8">
@@ -24600,7 +24600,7 @@
       </c>
       <c r="H831" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="832" spans="1:8">
@@ -24628,7 +24628,7 @@
       </c>
       <c r="H832" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="833" spans="1:8">
@@ -24656,7 +24656,7 @@
       </c>
       <c r="H833" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="834" spans="1:8">
@@ -24684,7 +24684,7 @@
       </c>
       <c r="H834" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="835" spans="1:8">
@@ -24712,7 +24712,7 @@
       </c>
       <c r="H835" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="836" spans="1:8">
@@ -24740,7 +24740,7 @@
       </c>
       <c r="H836" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="837" spans="1:8">
@@ -24768,7 +24768,7 @@
       </c>
       <c r="H837" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="838" spans="1:8">
@@ -24796,7 +24796,7 @@
       </c>
       <c r="H838" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="839" spans="1:8">
@@ -24824,7 +24824,7 @@
       </c>
       <c r="H839" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="840" spans="1:8">
@@ -24852,7 +24852,7 @@
       </c>
       <c r="H840" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="841" spans="1:8">
@@ -24880,7 +24880,7 @@
       </c>
       <c r="H841" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="842" spans="1:8">
@@ -24908,7 +24908,7 @@
       </c>
       <c r="H842" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="843" spans="1:8">
@@ -24936,7 +24936,7 @@
       </c>
       <c r="H843" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>20_1024008_2|20_1022502_1</v>
+        <v>20_1024008_2</v>
       </c>
     </row>
     <row r="844" spans="1:8">
@@ -24964,7 +24964,7 @@
       </c>
       <c r="H844" s="23" t="str">
         <f t="shared" si="112"/>
-        <v>21_1024008_2|21_1022502_1</v>
+        <v>21_1024008_2</v>
       </c>
     </row>
     <row r="845" spans="1:8">
@@ -25047,7 +25047,7 @@
       </c>
       <c r="H847" s="23" t="str">
         <f>H845</f>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="848" spans="1:8">
@@ -25075,7 +25075,7 @@
       </c>
       <c r="H848" s="23" t="str">
         <f>H846</f>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="849" spans="1:8">
@@ -25103,7 +25103,7 @@
       </c>
       <c r="H849" s="23" t="str">
         <f t="shared" ref="H849:H880" si="118">H847</f>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="850" spans="1:8">
@@ -25131,7 +25131,7 @@
       </c>
       <c r="H850" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="851" spans="1:8">
@@ -25159,7 +25159,7 @@
       </c>
       <c r="H851" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="852" spans="1:8">
@@ -25187,7 +25187,7 @@
       </c>
       <c r="H852" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="853" spans="1:8">
@@ -25215,7 +25215,7 @@
       </c>
       <c r="H853" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="854" spans="1:8">
@@ -25243,7 +25243,7 @@
       </c>
       <c r="H854" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="855" spans="1:8">
@@ -25271,7 +25271,7 @@
       </c>
       <c r="H855" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="856" spans="1:8">
@@ -25299,7 +25299,7 @@
       </c>
       <c r="H856" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="857" spans="1:8">
@@ -25327,7 +25327,7 @@
       </c>
       <c r="H857" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="858" spans="1:8">
@@ -25355,7 +25355,7 @@
       </c>
       <c r="H858" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="859" spans="1:8">
@@ -25383,7 +25383,7 @@
       </c>
       <c r="H859" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="860" spans="1:8">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="H860" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="861" spans="1:8">
@@ -25439,7 +25439,7 @@
       </c>
       <c r="H861" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="862" spans="1:8">
@@ -25467,7 +25467,7 @@
       </c>
       <c r="H862" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="863" spans="1:8">
@@ -25495,7 +25495,7 @@
       </c>
       <c r="H863" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="864" spans="1:8">
@@ -25523,7 +25523,7 @@
       </c>
       <c r="H864" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="865" spans="1:8">
@@ -25551,7 +25551,7 @@
       </c>
       <c r="H865" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="866" spans="1:8">
@@ -25579,7 +25579,7 @@
       </c>
       <c r="H866" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="867" spans="1:8">
@@ -25607,7 +25607,7 @@
       </c>
       <c r="H867" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="868" spans="1:8">
@@ -25635,7 +25635,7 @@
       </c>
       <c r="H868" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="869" spans="1:8">
@@ -25663,7 +25663,7 @@
       </c>
       <c r="H869" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="870" spans="1:8">
@@ -25691,7 +25691,7 @@
       </c>
       <c r="H870" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="871" spans="1:8">
@@ -25719,7 +25719,7 @@
       </c>
       <c r="H871" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="872" spans="1:8">
@@ -25747,7 +25747,7 @@
       </c>
       <c r="H872" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="873" spans="1:8">
@@ -25775,7 +25775,7 @@
       </c>
       <c r="H873" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="874" spans="1:8">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="H874" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="875" spans="1:8">
@@ -25831,7 +25831,7 @@
       </c>
       <c r="H875" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="876" spans="1:8">
@@ -25859,7 +25859,7 @@
       </c>
       <c r="H876" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="877" spans="1:8">
@@ -25887,7 +25887,7 @@
       </c>
       <c r="H877" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="878" spans="1:8">
@@ -25915,7 +25915,7 @@
       </c>
       <c r="H878" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="879" spans="1:8">
@@ -25943,7 +25943,7 @@
       </c>
       <c r="H879" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="880" spans="1:8">
@@ -25971,7 +25971,7 @@
       </c>
       <c r="H880" s="23" t="str">
         <f t="shared" si="118"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="881" spans="1:8">
@@ -25999,7 +25999,7 @@
       </c>
       <c r="H881" s="23" t="str">
         <f t="shared" ref="H881:H904" si="121">H879</f>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="882" spans="1:8">
@@ -26027,7 +26027,7 @@
       </c>
       <c r="H882" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="883" spans="1:8">
@@ -26055,7 +26055,7 @@
       </c>
       <c r="H883" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="884" spans="1:8">
@@ -26083,7 +26083,7 @@
       </c>
       <c r="H884" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="885" spans="1:8">
@@ -26111,7 +26111,7 @@
       </c>
       <c r="H885" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="886" spans="1:8">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="H886" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="887" spans="1:8">
@@ -26167,7 +26167,7 @@
       </c>
       <c r="H887" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="888" spans="1:8">
@@ -26195,7 +26195,7 @@
       </c>
       <c r="H888" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="889" spans="1:8">
@@ -26223,7 +26223,7 @@
       </c>
       <c r="H889" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="890" spans="1:8">
@@ -26251,7 +26251,7 @@
       </c>
       <c r="H890" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="891" spans="1:8">
@@ -26279,7 +26279,7 @@
       </c>
       <c r="H891" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="892" spans="1:8">
@@ -26307,7 +26307,7 @@
       </c>
       <c r="H892" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="893" spans="1:8">
@@ -26335,7 +26335,7 @@
       </c>
       <c r="H893" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="894" spans="1:8">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="H894" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="895" spans="1:8">
@@ -26391,7 +26391,7 @@
       </c>
       <c r="H895" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="896" spans="1:8">
@@ -26419,7 +26419,7 @@
       </c>
       <c r="H896" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="897" spans="1:8">
@@ -26447,7 +26447,7 @@
       </c>
       <c r="H897" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="898" spans="1:8">
@@ -26475,7 +26475,7 @@
       </c>
       <c r="H898" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="899" spans="1:8">
@@ -26503,7 +26503,7 @@
       </c>
       <c r="H899" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="900" spans="1:8">
@@ -26531,7 +26531,7 @@
       </c>
       <c r="H900" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="901" spans="1:8">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="H901" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="902" spans="1:8">
@@ -26587,7 +26587,7 @@
       </c>
       <c r="H902" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="903" spans="1:8">
@@ -26615,7 +26615,7 @@
       </c>
       <c r="H903" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="904" spans="1:8">
@@ -26643,7 +26643,7 @@
       </c>
       <c r="H904" s="23" t="str">
         <f t="shared" si="121"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="905" spans="1:8">
@@ -26672,7 +26672,7 @@
       </c>
       <c r="H905" s="23" t="str">
         <f>H845</f>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="906" spans="1:8">
@@ -26700,7 +26700,7 @@
       </c>
       <c r="H906" s="23" t="str">
         <f t="shared" ref="H906:H937" si="122">H846</f>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="907" spans="1:8">
@@ -26728,7 +26728,7 @@
       </c>
       <c r="H907" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="908" spans="1:8">
@@ -26756,7 +26756,7 @@
       </c>
       <c r="H908" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="909" spans="1:8">
@@ -26784,7 +26784,7 @@
       </c>
       <c r="H909" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="910" spans="1:8">
@@ -26812,7 +26812,7 @@
       </c>
       <c r="H910" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="911" spans="1:8">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="H911" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="912" spans="1:8">
@@ -26868,7 +26868,7 @@
       </c>
       <c r="H912" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="913" spans="1:8">
@@ -26896,7 +26896,7 @@
       </c>
       <c r="H913" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="914" spans="1:8">
@@ -26924,7 +26924,7 @@
       </c>
       <c r="H914" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="915" spans="1:8">
@@ -26952,7 +26952,7 @@
       </c>
       <c r="H915" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="916" spans="1:8">
@@ -26980,7 +26980,7 @@
       </c>
       <c r="H916" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="917" spans="1:8">
@@ -27008,7 +27008,7 @@
       </c>
       <c r="H917" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="918" spans="1:8">
@@ -27036,7 +27036,7 @@
       </c>
       <c r="H918" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="919" spans="1:8">
@@ -27064,7 +27064,7 @@
       </c>
       <c r="H919" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="920" spans="1:8">
@@ -27092,7 +27092,7 @@
       </c>
       <c r="H920" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="921" spans="1:8">
@@ -27120,7 +27120,7 @@
       </c>
       <c r="H921" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="922" spans="1:8">
@@ -27148,7 +27148,7 @@
       </c>
       <c r="H922" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="923" spans="1:8">
@@ -27176,7 +27176,7 @@
       </c>
       <c r="H923" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="924" spans="1:8">
@@ -27204,7 +27204,7 @@
       </c>
       <c r="H924" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="925" spans="1:8">
@@ -27232,7 +27232,7 @@
       </c>
       <c r="H925" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="926" spans="1:8">
@@ -27260,7 +27260,7 @@
       </c>
       <c r="H926" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="927" spans="1:8">
@@ -27288,7 +27288,7 @@
       </c>
       <c r="H927" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="928" spans="1:8">
@@ -27316,7 +27316,7 @@
       </c>
       <c r="H928" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="929" spans="1:8">
@@ -27344,7 +27344,7 @@
       </c>
       <c r="H929" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="930" spans="1:8">
@@ -27372,7 +27372,7 @@
       </c>
       <c r="H930" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="931" spans="1:8">
@@ -27400,7 +27400,7 @@
       </c>
       <c r="H931" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="932" spans="1:8">
@@ -27428,7 +27428,7 @@
       </c>
       <c r="H932" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="933" spans="1:8">
@@ -27456,7 +27456,7 @@
       </c>
       <c r="H933" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="934" spans="1:8">
@@ -27484,7 +27484,7 @@
       </c>
       <c r="H934" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="935" spans="1:8">
@@ -27512,7 +27512,7 @@
       </c>
       <c r="H935" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="936" spans="1:8">
@@ -27540,7 +27540,7 @@
       </c>
       <c r="H936" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="937" spans="1:8">
@@ -27568,7 +27568,7 @@
       </c>
       <c r="H937" s="23" t="str">
         <f t="shared" si="122"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="938" spans="1:8">
@@ -27596,7 +27596,7 @@
       </c>
       <c r="H938" s="23" t="str">
         <f t="shared" ref="H938:H964" si="128">H878</f>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="939" spans="1:8">
@@ -27624,7 +27624,7 @@
       </c>
       <c r="H939" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="940" spans="1:8">
@@ -27652,7 +27652,7 @@
       </c>
       <c r="H940" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="941" spans="1:8">
@@ -27680,7 +27680,7 @@
       </c>
       <c r="H941" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="942" spans="1:8">
@@ -27708,7 +27708,7 @@
       </c>
       <c r="H942" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="943" spans="1:8">
@@ -27736,7 +27736,7 @@
       </c>
       <c r="H943" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="944" spans="1:8">
@@ -27764,7 +27764,7 @@
       </c>
       <c r="H944" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="945" spans="1:8">
@@ -27792,7 +27792,7 @@
       </c>
       <c r="H945" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="946" spans="1:8">
@@ -27820,7 +27820,7 @@
       </c>
       <c r="H946" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="947" spans="1:8">
@@ -27848,7 +27848,7 @@
       </c>
       <c r="H947" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="948" spans="1:8">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="H948" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="949" spans="1:8">
@@ -27904,7 +27904,7 @@
       </c>
       <c r="H949" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="950" spans="1:8">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="H950" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="951" spans="1:8">
@@ -27960,7 +27960,7 @@
       </c>
       <c r="H951" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="952" spans="1:8">
@@ -27988,7 +27988,7 @@
       </c>
       <c r="H952" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="953" spans="1:8">
@@ -28016,7 +28016,7 @@
       </c>
       <c r="H953" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="954" spans="1:8">
@@ -28044,7 +28044,7 @@
       </c>
       <c r="H954" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="955" spans="1:8">
@@ -28072,7 +28072,7 @@
       </c>
       <c r="H955" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="956" spans="1:8">
@@ -28100,7 +28100,7 @@
       </c>
       <c r="H956" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="957" spans="1:8">
@@ -28128,7 +28128,7 @@
       </c>
       <c r="H957" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="958" spans="1:8">
@@ -28156,7 +28156,7 @@
       </c>
       <c r="H958" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="959" spans="1:8">
@@ -28184,7 +28184,7 @@
       </c>
       <c r="H959" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="960" spans="1:8">
@@ -28212,7 +28212,7 @@
       </c>
       <c r="H960" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="961" spans="1:8">
@@ -28240,7 +28240,7 @@
       </c>
       <c r="H961" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="962" spans="1:8">
@@ -28268,7 +28268,7 @@
       </c>
       <c r="H962" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="963" spans="1:8">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="H963" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>20_1024009_2|20_1022502_1</v>
+        <v>20_1024009_2</v>
       </c>
     </row>
     <row r="964" spans="1:8">
@@ -28324,7 +28324,7 @@
       </c>
       <c r="H964" s="23" t="str">
         <f t="shared" si="128"/>
-        <v>21_1024009_2|21_1022502_1</v>
+        <v>21_1024009_2</v>
       </c>
     </row>
     <row r="965" spans="1:8">
@@ -28407,7 +28407,7 @@
       </c>
       <c r="H967" s="23" t="str">
         <f>H965</f>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="968" spans="1:8">
@@ -28435,7 +28435,7 @@
       </c>
       <c r="H968" s="23" t="str">
         <f>H966</f>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="969" spans="1:8">
@@ -28463,7 +28463,7 @@
       </c>
       <c r="H969" s="23" t="str">
         <f t="shared" ref="H969:H1000" si="133">H967</f>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="970" spans="1:8">
@@ -28491,7 +28491,7 @@
       </c>
       <c r="H970" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="971" spans="1:8">
@@ -28519,7 +28519,7 @@
       </c>
       <c r="H971" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="972" spans="1:8">
@@ -28547,7 +28547,7 @@
       </c>
       <c r="H972" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="973" spans="1:8">
@@ -28575,7 +28575,7 @@
       </c>
       <c r="H973" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="974" spans="1:8">
@@ -28603,7 +28603,7 @@
       </c>
       <c r="H974" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="975" spans="1:8">
@@ -28631,7 +28631,7 @@
       </c>
       <c r="H975" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="976" spans="1:8">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="H976" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="977" spans="1:8">
@@ -28687,7 +28687,7 @@
       </c>
       <c r="H977" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="978" spans="1:8">
@@ -28715,7 +28715,7 @@
       </c>
       <c r="H978" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="979" spans="1:8">
@@ -28743,7 +28743,7 @@
       </c>
       <c r="H979" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="980" spans="1:8">
@@ -28771,7 +28771,7 @@
       </c>
       <c r="H980" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="981" spans="1:8">
@@ -28799,7 +28799,7 @@
       </c>
       <c r="H981" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="982" spans="1:8">
@@ -28827,7 +28827,7 @@
       </c>
       <c r="H982" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="983" spans="1:8">
@@ -28855,7 +28855,7 @@
       </c>
       <c r="H983" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="984" spans="1:8">
@@ -28883,7 +28883,7 @@
       </c>
       <c r="H984" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="985" spans="1:8">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="H985" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="986" spans="1:8">
@@ -28939,7 +28939,7 @@
       </c>
       <c r="H986" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="987" spans="1:8">
@@ -28967,7 +28967,7 @@
       </c>
       <c r="H987" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="988" spans="1:8">
@@ -28995,7 +28995,7 @@
       </c>
       <c r="H988" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="989" spans="1:8">
@@ -29023,7 +29023,7 @@
       </c>
       <c r="H989" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="990" spans="1:8">
@@ -29051,7 +29051,7 @@
       </c>
       <c r="H990" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="991" spans="1:8">
@@ -29079,7 +29079,7 @@
       </c>
       <c r="H991" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="992" spans="1:8">
@@ -29107,7 +29107,7 @@
       </c>
       <c r="H992" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="993" spans="1:8">
@@ -29135,7 +29135,7 @@
       </c>
       <c r="H993" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="994" spans="1:8">
@@ -29163,7 +29163,7 @@
       </c>
       <c r="H994" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="995" spans="1:8">
@@ -29191,7 +29191,7 @@
       </c>
       <c r="H995" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="996" spans="1:8">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="H996" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="997" spans="1:8">
@@ -29247,7 +29247,7 @@
       </c>
       <c r="H997" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="998" spans="1:8">
@@ -29275,7 +29275,7 @@
       </c>
       <c r="H998" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="999" spans="1:8">
@@ -29303,7 +29303,7 @@
       </c>
       <c r="H999" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1000" spans="1:8">
@@ -29331,7 +29331,7 @@
       </c>
       <c r="H1000" s="23" t="str">
         <f t="shared" si="133"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1001" spans="1:8">
@@ -29359,7 +29359,7 @@
       </c>
       <c r="H1001" s="23" t="str">
         <f t="shared" ref="H1001:H1024" si="139">H999</f>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1002" spans="1:8">
@@ -29387,7 +29387,7 @@
       </c>
       <c r="H1002" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1003" spans="1:8">
@@ -29415,7 +29415,7 @@
       </c>
       <c r="H1003" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1004" spans="1:8">
@@ -29443,7 +29443,7 @@
       </c>
       <c r="H1004" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1005" spans="1:8">
@@ -29471,7 +29471,7 @@
       </c>
       <c r="H1005" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1006" spans="1:8">
@@ -29499,7 +29499,7 @@
       </c>
       <c r="H1006" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1007" spans="1:8">
@@ -29527,7 +29527,7 @@
       </c>
       <c r="H1007" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1008" spans="1:8">
@@ -29555,7 +29555,7 @@
       </c>
       <c r="H1008" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1009" spans="1:8">
@@ -29583,7 +29583,7 @@
       </c>
       <c r="H1009" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1010" spans="1:8">
@@ -29611,7 +29611,7 @@
       </c>
       <c r="H1010" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1011" spans="1:8">
@@ -29639,7 +29639,7 @@
       </c>
       <c r="H1011" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1012" spans="1:8">
@@ -29667,7 +29667,7 @@
       </c>
       <c r="H1012" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1013" spans="1:8">
@@ -29695,7 +29695,7 @@
       </c>
       <c r="H1013" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1014" spans="1:8">
@@ -29723,7 +29723,7 @@
       </c>
       <c r="H1014" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1015" spans="1:8">
@@ -29751,7 +29751,7 @@
       </c>
       <c r="H1015" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1016" spans="1:8">
@@ -29779,7 +29779,7 @@
       </c>
       <c r="H1016" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1017" spans="1:8">
@@ -29807,7 +29807,7 @@
       </c>
       <c r="H1017" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1018" spans="1:8">
@@ -29835,7 +29835,7 @@
       </c>
       <c r="H1018" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1019" spans="1:8">
@@ -29863,7 +29863,7 @@
       </c>
       <c r="H1019" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1020" spans="1:8">
@@ -29891,7 +29891,7 @@
       </c>
       <c r="H1020" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1021" spans="1:8">
@@ -29919,7 +29919,7 @@
       </c>
       <c r="H1021" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1022" spans="1:8">
@@ -29947,7 +29947,7 @@
       </c>
       <c r="H1022" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1023" spans="1:8">
@@ -29975,7 +29975,7 @@
       </c>
       <c r="H1023" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1024" spans="1:8">
@@ -30003,7 +30003,7 @@
       </c>
       <c r="H1024" s="23" t="str">
         <f t="shared" si="139"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1025" spans="1:8">
@@ -30032,7 +30032,7 @@
       </c>
       <c r="H1025" s="23" t="str">
         <f>H965</f>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1026" spans="1:8">
@@ -30060,7 +30060,7 @@
       </c>
       <c r="H1026" s="23" t="str">
         <f t="shared" ref="H1026:H1057" si="140">H966</f>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1027" spans="1:8">
@@ -30088,7 +30088,7 @@
       </c>
       <c r="H1027" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1028" spans="1:8">
@@ -30116,7 +30116,7 @@
       </c>
       <c r="H1028" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1029" spans="1:8">
@@ -30144,7 +30144,7 @@
       </c>
       <c r="H1029" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1030" spans="1:8">
@@ -30172,7 +30172,7 @@
       </c>
       <c r="H1030" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1031" spans="1:8">
@@ -30200,7 +30200,7 @@
       </c>
       <c r="H1031" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1032" spans="1:8">
@@ -30228,7 +30228,7 @@
       </c>
       <c r="H1032" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1033" spans="1:8">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="H1033" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1034" spans="1:8">
@@ -30284,7 +30284,7 @@
       </c>
       <c r="H1034" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1035" spans="1:8">
@@ -30312,7 +30312,7 @@
       </c>
       <c r="H1035" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1036" spans="1:8">
@@ -30340,7 +30340,7 @@
       </c>
       <c r="H1036" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1037" spans="1:8">
@@ -30368,7 +30368,7 @@
       </c>
       <c r="H1037" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1038" spans="1:8">
@@ -30396,7 +30396,7 @@
       </c>
       <c r="H1038" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1039" spans="1:8">
@@ -30424,7 +30424,7 @@
       </c>
       <c r="H1039" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1040" spans="1:8">
@@ -30452,7 +30452,7 @@
       </c>
       <c r="H1040" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1041" spans="1:8">
@@ -30480,7 +30480,7 @@
       </c>
       <c r="H1041" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1042" spans="1:8">
@@ -30508,7 +30508,7 @@
       </c>
       <c r="H1042" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1043" spans="1:8">
@@ -30536,7 +30536,7 @@
       </c>
       <c r="H1043" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1044" spans="1:8">
@@ -30564,7 +30564,7 @@
       </c>
       <c r="H1044" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1045" spans="1:8">
@@ -30592,7 +30592,7 @@
       </c>
       <c r="H1045" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1046" spans="1:8">
@@ -30620,7 +30620,7 @@
       </c>
       <c r="H1046" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1047" spans="1:8">
@@ -30648,7 +30648,7 @@
       </c>
       <c r="H1047" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1048" spans="1:8">
@@ -30676,7 +30676,7 @@
       </c>
       <c r="H1048" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1049" spans="1:8">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="H1049" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1050" spans="1:8">
@@ -30732,7 +30732,7 @@
       </c>
       <c r="H1050" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1051" spans="1:8">
@@ -30760,7 +30760,7 @@
       </c>
       <c r="H1051" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1052" spans="1:8">
@@ -30788,7 +30788,7 @@
       </c>
       <c r="H1052" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1053" spans="1:8">
@@ -30816,7 +30816,7 @@
       </c>
       <c r="H1053" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1054" spans="1:8">
@@ -30844,7 +30844,7 @@
       </c>
       <c r="H1054" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1055" spans="1:8">
@@ -30872,7 +30872,7 @@
       </c>
       <c r="H1055" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1056" spans="1:8">
@@ -30900,7 +30900,7 @@
       </c>
       <c r="H1056" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1057" spans="1:8">
@@ -30928,7 +30928,7 @@
       </c>
       <c r="H1057" s="23" t="str">
         <f t="shared" si="140"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1058" spans="1:8">
@@ -30956,7 +30956,7 @@
       </c>
       <c r="H1058" s="23" t="str">
         <f t="shared" ref="H1058:H1084" si="146">H998</f>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1059" spans="1:8">
@@ -30984,7 +30984,7 @@
       </c>
       <c r="H1059" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1060" spans="1:8">
@@ -31012,7 +31012,7 @@
       </c>
       <c r="H1060" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1061" spans="1:8">
@@ -31040,7 +31040,7 @@
       </c>
       <c r="H1061" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1062" spans="1:8">
@@ -31068,7 +31068,7 @@
       </c>
       <c r="H1062" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1063" spans="1:8">
@@ -31096,7 +31096,7 @@
       </c>
       <c r="H1063" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1064" spans="1:8">
@@ -31124,7 +31124,7 @@
       </c>
       <c r="H1064" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1065" spans="1:8">
@@ -31152,7 +31152,7 @@
       </c>
       <c r="H1065" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1066" spans="1:8">
@@ -31180,7 +31180,7 @@
       </c>
       <c r="H1066" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1067" spans="1:8">
@@ -31208,7 +31208,7 @@
       </c>
       <c r="H1067" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1068" spans="1:8">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="H1068" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1069" spans="1:8">
@@ -31264,7 +31264,7 @@
       </c>
       <c r="H1069" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1070" spans="1:8">
@@ -31292,7 +31292,7 @@
       </c>
       <c r="H1070" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1071" spans="1:8">
@@ -31320,7 +31320,7 @@
       </c>
       <c r="H1071" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1072" spans="1:8">
@@ -31348,7 +31348,7 @@
       </c>
       <c r="H1072" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1073" spans="1:8">
@@ -31376,7 +31376,7 @@
       </c>
       <c r="H1073" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1074" spans="1:8">
@@ -31404,7 +31404,7 @@
       </c>
       <c r="H1074" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1075" spans="1:8">
@@ -31432,7 +31432,7 @@
       </c>
       <c r="H1075" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1076" spans="1:8">
@@ -31460,7 +31460,7 @@
       </c>
       <c r="H1076" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1077" spans="1:8">
@@ -31488,7 +31488,7 @@
       </c>
       <c r="H1077" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1078" spans="1:8">
@@ -31516,7 +31516,7 @@
       </c>
       <c r="H1078" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1079" spans="1:8">
@@ -31544,7 +31544,7 @@
       </c>
       <c r="H1079" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1080" spans="1:8">
@@ -31572,7 +31572,7 @@
       </c>
       <c r="H1080" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1081" spans="1:8">
@@ -31600,7 +31600,7 @@
       </c>
       <c r="H1081" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1082" spans="1:8">
@@ -31628,7 +31628,7 @@
       </c>
       <c r="H1082" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1083" spans="1:8">
@@ -31656,7 +31656,7 @@
       </c>
       <c r="H1083" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>20_1024010_2|20_1022502_1</v>
+        <v>20_1024010_2</v>
       </c>
     </row>
     <row r="1084" spans="1:8">
@@ -31684,7 +31684,7 @@
       </c>
       <c r="H1084" s="23" t="str">
         <f t="shared" si="146"/>
-        <v>21_1024010_2|21_1022502_1</v>
+        <v>21_1024010_2</v>
       </c>
     </row>
     <row r="1085" spans="1:8">
@@ -31758,7 +31758,7 @@
       </c>
       <c r="H1087" s="1" t="str">
         <f>H1085</f>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1088" spans="1:8">
@@ -31783,7 +31783,7 @@
       </c>
       <c r="H1088" s="1" t="str">
         <f>H1086</f>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1089" spans="1:8">
@@ -31808,7 +31808,7 @@
       </c>
       <c r="H1089" s="1" t="str">
         <f t="shared" ref="H1089:H1120" si="151">H1087</f>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1090" spans="1:8">
@@ -31833,7 +31833,7 @@
       </c>
       <c r="H1090" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1091" spans="1:8">
@@ -31858,7 +31858,7 @@
       </c>
       <c r="H1091" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1092" spans="1:8">
@@ -31883,7 +31883,7 @@
       </c>
       <c r="H1092" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1093" spans="1:8">
@@ -31908,7 +31908,7 @@
       </c>
       <c r="H1093" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1094" spans="1:8">
@@ -31933,7 +31933,7 @@
       </c>
       <c r="H1094" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1095" spans="1:8">
@@ -31958,7 +31958,7 @@
       </c>
       <c r="H1095" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1096" spans="1:8">
@@ -31983,7 +31983,7 @@
       </c>
       <c r="H1096" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1097" spans="1:8">
@@ -32008,7 +32008,7 @@
       </c>
       <c r="H1097" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1098" spans="1:8">
@@ -32033,7 +32033,7 @@
       </c>
       <c r="H1098" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1099" spans="1:8">
@@ -32058,7 +32058,7 @@
       </c>
       <c r="H1099" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1100" spans="1:8">
@@ -32083,7 +32083,7 @@
       </c>
       <c r="H1100" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1101" spans="1:8">
@@ -32108,7 +32108,7 @@
       </c>
       <c r="H1101" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1102" spans="1:8">
@@ -32133,7 +32133,7 @@
       </c>
       <c r="H1102" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1103" spans="1:8">
@@ -32158,7 +32158,7 @@
       </c>
       <c r="H1103" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1104" spans="1:8">
@@ -32183,7 +32183,7 @@
       </c>
       <c r="H1104" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1105" spans="1:8">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="H1105" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1106" spans="1:8">
@@ -32233,7 +32233,7 @@
       </c>
       <c r="H1106" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1107" spans="1:8">
@@ -32258,7 +32258,7 @@
       </c>
       <c r="H1107" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1108" spans="1:8">
@@ -32283,7 +32283,7 @@
       </c>
       <c r="H1108" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1109" spans="1:8">
@@ -32308,7 +32308,7 @@
       </c>
       <c r="H1109" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1110" spans="1:8">
@@ -32333,7 +32333,7 @@
       </c>
       <c r="H1110" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1111" spans="1:8">
@@ -32358,7 +32358,7 @@
       </c>
       <c r="H1111" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1112" spans="1:8">
@@ -32383,7 +32383,7 @@
       </c>
       <c r="H1112" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1113" spans="1:8">
@@ -32408,7 +32408,7 @@
       </c>
       <c r="H1113" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1114" spans="1:8">
@@ -32433,7 +32433,7 @@
       </c>
       <c r="H1114" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1115" spans="1:8">
@@ -32458,7 +32458,7 @@
       </c>
       <c r="H1115" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1116" spans="1:8">
@@ -32483,7 +32483,7 @@
       </c>
       <c r="H1116" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1117" spans="1:8">
@@ -32508,7 +32508,7 @@
       </c>
       <c r="H1117" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1118" spans="1:8">
@@ -32533,7 +32533,7 @@
       </c>
       <c r="H1118" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1119" spans="1:8">
@@ -32558,7 +32558,7 @@
       </c>
       <c r="H1119" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1120" spans="1:8">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="H1120" s="1" t="str">
         <f t="shared" si="151"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1121" spans="1:8">
@@ -32608,7 +32608,7 @@
       </c>
       <c r="H1121" s="1" t="str">
         <f t="shared" ref="H1121:H1144" si="154">H1119</f>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1122" spans="1:8">
@@ -32633,7 +32633,7 @@
       </c>
       <c r="H1122" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1123" spans="1:8">
@@ -32658,7 +32658,7 @@
       </c>
       <c r="H1123" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1124" spans="1:8">
@@ -32683,7 +32683,7 @@
       </c>
       <c r="H1124" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1125" spans="1:8">
@@ -32708,7 +32708,7 @@
       </c>
       <c r="H1125" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1126" spans="1:8">
@@ -32733,7 +32733,7 @@
       </c>
       <c r="H1126" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1127" spans="1:8">
@@ -32758,7 +32758,7 @@
       </c>
       <c r="H1127" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1128" spans="1:8">
@@ -32783,7 +32783,7 @@
       </c>
       <c r="H1128" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1129" spans="1:8">
@@ -32808,7 +32808,7 @@
       </c>
       <c r="H1129" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1130" spans="1:8">
@@ -32833,7 +32833,7 @@
       </c>
       <c r="H1130" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1131" spans="1:8">
@@ -32858,7 +32858,7 @@
       </c>
       <c r="H1131" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1132" spans="1:8">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="H1132" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1133" spans="1:8">
@@ -32908,7 +32908,7 @@
       </c>
       <c r="H1133" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1134" spans="1:8">
@@ -32933,7 +32933,7 @@
       </c>
       <c r="H1134" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1135" spans="1:8">
@@ -32958,7 +32958,7 @@
       </c>
       <c r="H1135" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1136" spans="1:8">
@@ -32983,7 +32983,7 @@
       </c>
       <c r="H1136" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1137" spans="1:8">
@@ -33008,7 +33008,7 @@
       </c>
       <c r="H1137" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1138" spans="1:8">
@@ -33033,7 +33033,7 @@
       </c>
       <c r="H1138" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1139" spans="1:8">
@@ -33058,7 +33058,7 @@
       </c>
       <c r="H1139" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1140" spans="1:8">
@@ -33083,7 +33083,7 @@
       </c>
       <c r="H1140" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1141" spans="1:8">
@@ -33108,7 +33108,7 @@
       </c>
       <c r="H1141" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1142" spans="1:8">
@@ -33133,7 +33133,7 @@
       </c>
       <c r="H1142" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1143" spans="1:8">
@@ -33158,7 +33158,7 @@
       </c>
       <c r="H1143" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1144" spans="1:8">
@@ -33183,7 +33183,7 @@
       </c>
       <c r="H1144" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1145" spans="1:8">
@@ -33212,7 +33212,7 @@
       </c>
       <c r="H1145" s="1" t="str">
         <f>H1085</f>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1146" spans="1:8">
@@ -33240,7 +33240,7 @@
       </c>
       <c r="H1146" s="1" t="str">
         <f t="shared" ref="H1146:H1209" si="158">H1086</f>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1147" spans="1:8">
@@ -33268,7 +33268,7 @@
       </c>
       <c r="H1147" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1148" spans="1:8">
@@ -33296,7 +33296,7 @@
       </c>
       <c r="H1148" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1149" spans="1:8">
@@ -33324,7 +33324,7 @@
       </c>
       <c r="H1149" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1150" spans="1:8">
@@ -33352,7 +33352,7 @@
       </c>
       <c r="H1150" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1151" spans="1:8">
@@ -33380,7 +33380,7 @@
       </c>
       <c r="H1151" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1152" spans="1:8">
@@ -33408,7 +33408,7 @@
       </c>
       <c r="H1152" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1153" spans="1:8">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="H1153" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1154" spans="1:8">
@@ -33464,7 +33464,7 @@
       </c>
       <c r="H1154" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1155" spans="1:8">
@@ -33492,7 +33492,7 @@
       </c>
       <c r="H1155" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1156" spans="1:8">
@@ -33520,7 +33520,7 @@
       </c>
       <c r="H1156" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1157" spans="1:8">
@@ -33548,7 +33548,7 @@
       </c>
       <c r="H1157" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1158" spans="1:8">
@@ -33576,7 +33576,7 @@
       </c>
       <c r="H1158" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1159" spans="1:8">
@@ -33604,7 +33604,7 @@
       </c>
       <c r="H1159" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1160" spans="1:8">
@@ -33632,7 +33632,7 @@
       </c>
       <c r="H1160" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1161" spans="1:8">
@@ -33660,7 +33660,7 @@
       </c>
       <c r="H1161" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1162" spans="1:8">
@@ -33688,7 +33688,7 @@
       </c>
       <c r="H1162" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1163" spans="1:8">
@@ -33716,7 +33716,7 @@
       </c>
       <c r="H1163" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1164" spans="1:8">
@@ -33744,7 +33744,7 @@
       </c>
       <c r="H1164" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1165" spans="1:8">
@@ -33772,7 +33772,7 @@
       </c>
       <c r="H1165" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1166" spans="1:8">
@@ -33800,7 +33800,7 @@
       </c>
       <c r="H1166" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1167" spans="1:8">
@@ -33828,7 +33828,7 @@
       </c>
       <c r="H1167" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1168" spans="1:8">
@@ -33856,7 +33856,7 @@
       </c>
       <c r="H1168" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1169" spans="1:8">
@@ -33884,7 +33884,7 @@
       </c>
       <c r="H1169" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1170" spans="1:8">
@@ -33912,7 +33912,7 @@
       </c>
       <c r="H1170" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1171" spans="1:8">
@@ -33940,7 +33940,7 @@
       </c>
       <c r="H1171" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1172" spans="1:8">
@@ -33968,7 +33968,7 @@
       </c>
       <c r="H1172" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1173" spans="1:8">
@@ -33996,7 +33996,7 @@
       </c>
       <c r="H1173" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1174" spans="1:8">
@@ -34024,7 +34024,7 @@
       </c>
       <c r="H1174" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1175" spans="1:8">
@@ -34052,7 +34052,7 @@
       </c>
       <c r="H1175" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1176" spans="1:8">
@@ -34080,7 +34080,7 @@
       </c>
       <c r="H1176" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1177" spans="1:8">
@@ -34108,7 +34108,7 @@
       </c>
       <c r="H1177" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1178" spans="1:8">
@@ -34136,7 +34136,7 @@
       </c>
       <c r="H1178" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1179" spans="1:8">
@@ -34164,7 +34164,7 @@
       </c>
       <c r="H1179" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1180" spans="1:8">
@@ -34192,7 +34192,7 @@
       </c>
       <c r="H1180" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1181" spans="1:8">
@@ -34220,7 +34220,7 @@
       </c>
       <c r="H1181" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1182" spans="1:8">
@@ -34248,7 +34248,7 @@
       </c>
       <c r="H1182" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1183" spans="1:8">
@@ -34276,7 +34276,7 @@
       </c>
       <c r="H1183" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1184" spans="1:8">
@@ -34304,7 +34304,7 @@
       </c>
       <c r="H1184" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1185" spans="1:8">
@@ -34332,7 +34332,7 @@
       </c>
       <c r="H1185" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1186" spans="1:8">
@@ -34360,7 +34360,7 @@
       </c>
       <c r="H1186" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1187" spans="1:8">
@@ -34388,7 +34388,7 @@
       </c>
       <c r="H1187" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1188" spans="1:8">
@@ -34416,7 +34416,7 @@
       </c>
       <c r="H1188" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1189" spans="1:8">
@@ -34444,7 +34444,7 @@
       </c>
       <c r="H1189" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1190" spans="1:8">
@@ -34472,7 +34472,7 @@
       </c>
       <c r="H1190" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1191" spans="1:8">
@@ -34500,7 +34500,7 @@
       </c>
       <c r="H1191" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1192" spans="1:8">
@@ -34528,7 +34528,7 @@
       </c>
       <c r="H1192" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1193" spans="1:8">
@@ -34556,7 +34556,7 @@
       </c>
       <c r="H1193" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1194" spans="1:8">
@@ -34584,7 +34584,7 @@
       </c>
       <c r="H1194" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1195" spans="1:8">
@@ -34612,7 +34612,7 @@
       </c>
       <c r="H1195" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1196" spans="1:8">
@@ -34640,7 +34640,7 @@
       </c>
       <c r="H1196" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1197" spans="1:8">
@@ -34668,7 +34668,7 @@
       </c>
       <c r="H1197" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1198" spans="1:8">
@@ -34696,7 +34696,7 @@
       </c>
       <c r="H1198" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1199" spans="1:8">
@@ -34724,7 +34724,7 @@
       </c>
       <c r="H1199" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1200" spans="1:8">
@@ -34752,7 +34752,7 @@
       </c>
       <c r="H1200" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1201" spans="1:8">
@@ -34780,7 +34780,7 @@
       </c>
       <c r="H1201" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1202" spans="1:8">
@@ -34808,7 +34808,7 @@
       </c>
       <c r="H1202" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1203" spans="1:8">
@@ -34836,7 +34836,7 @@
       </c>
       <c r="H1203" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>25_1024008_2|25_1022502_1</v>
+        <v>25_1024008_2</v>
       </c>
     </row>
     <row r="1204" spans="1:8">
@@ -34864,7 +34864,7 @@
       </c>
       <c r="H1204" s="1" t="str">
         <f t="shared" si="158"/>
-        <v>26_1024008_2|26_1022502_1</v>
+        <v>26_1024008_2</v>
       </c>
     </row>
     <row r="1205" spans="1:8">
@@ -34947,7 +34947,7 @@
       </c>
       <c r="H1207" s="1" t="str">
         <f>H1205</f>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1208" spans="1:8">
@@ -34975,7 +34975,7 @@
       </c>
       <c r="H1208" s="1" t="str">
         <f>H1206</f>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1209" spans="1:8">
@@ -35003,7 +35003,7 @@
       </c>
       <c r="H1209" s="1" t="str">
         <f t="shared" ref="H1209:H1240" si="165">H1207</f>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1210" spans="1:8">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="H1210" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1211" spans="1:8">
@@ -35059,7 +35059,7 @@
       </c>
       <c r="H1211" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1212" spans="1:8">
@@ -35087,7 +35087,7 @@
       </c>
       <c r="H1212" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1213" spans="1:8">
@@ -35115,7 +35115,7 @@
       </c>
       <c r="H1213" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1214" spans="1:8">
@@ -35143,7 +35143,7 @@
       </c>
       <c r="H1214" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1215" spans="1:8">
@@ -35171,7 +35171,7 @@
       </c>
       <c r="H1215" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1216" spans="1:8">
@@ -35199,7 +35199,7 @@
       </c>
       <c r="H1216" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1217" spans="1:8">
@@ -35227,7 +35227,7 @@
       </c>
       <c r="H1217" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1218" spans="1:8">
@@ -35255,7 +35255,7 @@
       </c>
       <c r="H1218" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1219" spans="1:8">
@@ -35283,7 +35283,7 @@
       </c>
       <c r="H1219" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1220" spans="1:8">
@@ -35311,7 +35311,7 @@
       </c>
       <c r="H1220" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1221" spans="1:8">
@@ -35339,7 +35339,7 @@
       </c>
       <c r="H1221" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1222" spans="1:8">
@@ -35367,7 +35367,7 @@
       </c>
       <c r="H1222" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1223" spans="1:8">
@@ -35395,7 +35395,7 @@
       </c>
       <c r="H1223" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1224" spans="1:8">
@@ -35423,7 +35423,7 @@
       </c>
       <c r="H1224" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1225" spans="1:8">
@@ -35451,7 +35451,7 @@
       </c>
       <c r="H1225" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1226" spans="1:8">
@@ -35479,7 +35479,7 @@
       </c>
       <c r="H1226" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1227" spans="1:8">
@@ -35507,7 +35507,7 @@
       </c>
       <c r="H1227" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1228" spans="1:8">
@@ -35535,7 +35535,7 @@
       </c>
       <c r="H1228" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1229" spans="1:8">
@@ -35563,7 +35563,7 @@
       </c>
       <c r="H1229" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1230" spans="1:8">
@@ -35591,7 +35591,7 @@
       </c>
       <c r="H1230" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1231" spans="1:8">
@@ -35619,7 +35619,7 @@
       </c>
       <c r="H1231" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1232" spans="1:8">
@@ -35647,7 +35647,7 @@
       </c>
       <c r="H1232" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1233" spans="1:8">
@@ -35675,7 +35675,7 @@
       </c>
       <c r="H1233" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1234" spans="1:8">
@@ -35703,7 +35703,7 @@
       </c>
       <c r="H1234" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1235" spans="1:8">
@@ -35731,7 +35731,7 @@
       </c>
       <c r="H1235" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1236" spans="1:8">
@@ -35759,7 +35759,7 @@
       </c>
       <c r="H1236" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1237" spans="1:8">
@@ -35787,7 +35787,7 @@
       </c>
       <c r="H1237" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1238" spans="1:8">
@@ -35815,7 +35815,7 @@
       </c>
       <c r="H1238" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1239" spans="1:8">
@@ -35843,7 +35843,7 @@
       </c>
       <c r="H1239" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1240" spans="1:8">
@@ -35871,7 +35871,7 @@
       </c>
       <c r="H1240" s="1" t="str">
         <f t="shared" si="165"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1241" spans="1:8">
@@ -35899,7 +35899,7 @@
       </c>
       <c r="H1241" s="1" t="str">
         <f t="shared" ref="H1241:H1264" si="171">H1239</f>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1242" spans="1:8">
@@ -35927,7 +35927,7 @@
       </c>
       <c r="H1242" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1243" spans="1:8">
@@ -35955,7 +35955,7 @@
       </c>
       <c r="H1243" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1244" spans="1:8">
@@ -35983,7 +35983,7 @@
       </c>
       <c r="H1244" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1245" spans="1:8">
@@ -36011,7 +36011,7 @@
       </c>
       <c r="H1245" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1246" spans="1:8">
@@ -36039,7 +36039,7 @@
       </c>
       <c r="H1246" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1247" spans="1:8">
@@ -36067,7 +36067,7 @@
       </c>
       <c r="H1247" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1248" spans="1:8">
@@ -36095,7 +36095,7 @@
       </c>
       <c r="H1248" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1249" spans="1:8">
@@ -36123,7 +36123,7 @@
       </c>
       <c r="H1249" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1250" spans="1:8">
@@ -36151,7 +36151,7 @@
       </c>
       <c r="H1250" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1251" spans="1:8">
@@ -36179,7 +36179,7 @@
       </c>
       <c r="H1251" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1252" spans="1:8">
@@ -36207,7 +36207,7 @@
       </c>
       <c r="H1252" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1253" spans="1:8">
@@ -36235,7 +36235,7 @@
       </c>
       <c r="H1253" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1254" spans="1:8">
@@ -36263,7 +36263,7 @@
       </c>
       <c r="H1254" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1255" spans="1:8">
@@ -36291,7 +36291,7 @@
       </c>
       <c r="H1255" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1256" spans="1:8">
@@ -36319,7 +36319,7 @@
       </c>
       <c r="H1256" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1257" spans="1:8">
@@ -36347,7 +36347,7 @@
       </c>
       <c r="H1257" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1258" spans="1:8">
@@ -36375,7 +36375,7 @@
       </c>
       <c r="H1258" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1259" spans="1:8">
@@ -36403,7 +36403,7 @@
       </c>
       <c r="H1259" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1260" spans="1:8">
@@ -36431,7 +36431,7 @@
       </c>
       <c r="H1260" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1261" spans="1:8">
@@ -36459,7 +36459,7 @@
       </c>
       <c r="H1261" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1262" spans="1:8">
@@ -36487,7 +36487,7 @@
       </c>
       <c r="H1262" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1263" spans="1:8">
@@ -36515,7 +36515,7 @@
       </c>
       <c r="H1263" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1264" spans="1:8">
@@ -36543,7 +36543,7 @@
       </c>
       <c r="H1264" s="1" t="str">
         <f t="shared" si="171"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1265" spans="1:8">
@@ -36572,7 +36572,7 @@
       </c>
       <c r="H1265" s="1" t="str">
         <f>H1205</f>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1266" spans="1:8">
@@ -36600,7 +36600,7 @@
       </c>
       <c r="H1266" s="1" t="str">
         <f t="shared" ref="H1266:H1297" si="172">H1206</f>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1267" spans="1:8">
@@ -36628,7 +36628,7 @@
       </c>
       <c r="H1267" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1268" spans="1:8">
@@ -36656,7 +36656,7 @@
       </c>
       <c r="H1268" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1269" spans="1:8">
@@ -36684,7 +36684,7 @@
       </c>
       <c r="H1269" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1270" spans="1:8">
@@ -36712,7 +36712,7 @@
       </c>
       <c r="H1270" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1271" spans="1:8">
@@ -36740,7 +36740,7 @@
       </c>
       <c r="H1271" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1272" spans="1:8">
@@ -36768,7 +36768,7 @@
       </c>
       <c r="H1272" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1273" spans="1:8">
@@ -36796,7 +36796,7 @@
       </c>
       <c r="H1273" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1274" spans="1:8">
@@ -36824,7 +36824,7 @@
       </c>
       <c r="H1274" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1275" spans="1:8">
@@ -36852,7 +36852,7 @@
       </c>
       <c r="H1275" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1276" spans="1:8">
@@ -36880,7 +36880,7 @@
       </c>
       <c r="H1276" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1277" spans="1:8">
@@ -36908,7 +36908,7 @@
       </c>
       <c r="H1277" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1278" spans="1:8">
@@ -36936,7 +36936,7 @@
       </c>
       <c r="H1278" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1279" spans="1:8">
@@ -36964,7 +36964,7 @@
       </c>
       <c r="H1279" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1280" spans="1:8">
@@ -36992,7 +36992,7 @@
       </c>
       <c r="H1280" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1281" spans="1:8">
@@ -37020,7 +37020,7 @@
       </c>
       <c r="H1281" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1282" spans="1:8">
@@ -37048,7 +37048,7 @@
       </c>
       <c r="H1282" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1283" spans="1:8">
@@ -37076,7 +37076,7 @@
       </c>
       <c r="H1283" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1284" spans="1:8">
@@ -37104,7 +37104,7 @@
       </c>
       <c r="H1284" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1285" spans="1:8">
@@ -37132,7 +37132,7 @@
       </c>
       <c r="H1285" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1286" spans="1:8">
@@ -37160,7 +37160,7 @@
       </c>
       <c r="H1286" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1287" spans="1:8">
@@ -37188,7 +37188,7 @@
       </c>
       <c r="H1287" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1288" spans="1:8">
@@ -37216,7 +37216,7 @@
       </c>
       <c r="H1288" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1289" spans="1:8">
@@ -37244,7 +37244,7 @@
       </c>
       <c r="H1289" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1290" spans="1:8">
@@ -37272,7 +37272,7 @@
       </c>
       <c r="H1290" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1291" spans="1:8">
@@ -37300,7 +37300,7 @@
       </c>
       <c r="H1291" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1292" spans="1:8">
@@ -37328,7 +37328,7 @@
       </c>
       <c r="H1292" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1293" spans="1:8">
@@ -37356,7 +37356,7 @@
       </c>
       <c r="H1293" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1294" spans="1:8">
@@ -37384,7 +37384,7 @@
       </c>
       <c r="H1294" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1295" spans="1:8">
@@ -37412,7 +37412,7 @@
       </c>
       <c r="H1295" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1296" spans="1:8">
@@ -37440,7 +37440,7 @@
       </c>
       <c r="H1296" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1297" spans="1:8">
@@ -37468,7 +37468,7 @@
       </c>
       <c r="H1297" s="1" t="str">
         <f t="shared" si="172"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1298" spans="1:8">
@@ -37496,7 +37496,7 @@
       </c>
       <c r="H1298" s="1" t="str">
         <f t="shared" ref="H1298:H1324" si="178">H1238</f>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1299" spans="1:8">
@@ -37524,7 +37524,7 @@
       </c>
       <c r="H1299" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1300" spans="1:8">
@@ -37552,7 +37552,7 @@
       </c>
       <c r="H1300" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1301" spans="1:8">
@@ -37580,7 +37580,7 @@
       </c>
       <c r="H1301" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1302" spans="1:8">
@@ -37608,7 +37608,7 @@
       </c>
       <c r="H1302" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1303" spans="1:8">
@@ -37636,7 +37636,7 @@
       </c>
       <c r="H1303" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1304" spans="1:8">
@@ -37664,7 +37664,7 @@
       </c>
       <c r="H1304" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1305" spans="1:8">
@@ -37692,7 +37692,7 @@
       </c>
       <c r="H1305" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1306" spans="1:8">
@@ -37720,7 +37720,7 @@
       </c>
       <c r="H1306" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1307" spans="1:8">
@@ -37748,7 +37748,7 @@
       </c>
       <c r="H1307" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1308" spans="1:8">
@@ -37776,7 +37776,7 @@
       </c>
       <c r="H1308" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1309" spans="1:8">
@@ -37804,7 +37804,7 @@
       </c>
       <c r="H1309" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1310" spans="1:8">
@@ -37832,7 +37832,7 @@
       </c>
       <c r="H1310" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1311" spans="1:8">
@@ -37860,7 +37860,7 @@
       </c>
       <c r="H1311" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1312" spans="1:8">
@@ -37888,7 +37888,7 @@
       </c>
       <c r="H1312" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1313" spans="1:8">
@@ -37916,7 +37916,7 @@
       </c>
       <c r="H1313" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1314" spans="1:8">
@@ -37944,7 +37944,7 @@
       </c>
       <c r="H1314" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1315" spans="1:8">
@@ -37972,7 +37972,7 @@
       </c>
       <c r="H1315" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1316" spans="1:8">
@@ -38000,7 +38000,7 @@
       </c>
       <c r="H1316" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1317" spans="1:8">
@@ -38028,7 +38028,7 @@
       </c>
       <c r="H1317" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1318" spans="1:8">
@@ -38056,7 +38056,7 @@
       </c>
       <c r="H1318" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1319" spans="1:8">
@@ -38084,7 +38084,7 @@
       </c>
       <c r="H1319" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1320" spans="1:8">
@@ -38112,7 +38112,7 @@
       </c>
       <c r="H1320" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1321" spans="1:8">
@@ -38140,7 +38140,7 @@
       </c>
       <c r="H1321" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1322" spans="1:8">
@@ -38168,7 +38168,7 @@
       </c>
       <c r="H1322" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1323" spans="1:8">
@@ -38196,7 +38196,7 @@
       </c>
       <c r="H1323" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>25_1024009_2|25_1022502_1</v>
+        <v>25_1024009_2</v>
       </c>
     </row>
     <row r="1324" spans="1:8">
@@ -38224,7 +38224,7 @@
       </c>
       <c r="H1324" s="1" t="str">
         <f t="shared" si="178"/>
-        <v>26_1024009_2|26_1022502_1</v>
+        <v>26_1024009_2</v>
       </c>
     </row>
     <row r="1325" spans="1:8">
@@ -38307,7 +38307,7 @@
       </c>
       <c r="H1327" s="1" t="str">
         <f>H1325</f>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1328" spans="1:8">
@@ -38335,7 +38335,7 @@
       </c>
       <c r="H1328" s="1" t="str">
         <f>H1326</f>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1329" spans="1:8">
@@ -38363,7 +38363,7 @@
       </c>
       <c r="H1329" s="1" t="str">
         <f t="shared" ref="H1329:H1360" si="183">H1327</f>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1330" spans="1:8">
@@ -38391,7 +38391,7 @@
       </c>
       <c r="H1330" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1331" spans="1:8">
@@ -38419,7 +38419,7 @@
       </c>
       <c r="H1331" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1332" spans="1:8">
@@ -38447,7 +38447,7 @@
       </c>
       <c r="H1332" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1333" spans="1:8">
@@ -38475,7 +38475,7 @@
       </c>
       <c r="H1333" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1334" spans="1:8">
@@ -38503,7 +38503,7 @@
       </c>
       <c r="H1334" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1335" spans="1:8">
@@ -38531,7 +38531,7 @@
       </c>
       <c r="H1335" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1336" spans="1:8">
@@ -38559,7 +38559,7 @@
       </c>
       <c r="H1336" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1337" spans="1:8">
@@ -38587,7 +38587,7 @@
       </c>
       <c r="H1337" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1338" spans="1:8">
@@ -38615,7 +38615,7 @@
       </c>
       <c r="H1338" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1339" spans="1:8">
@@ -38643,7 +38643,7 @@
       </c>
       <c r="H1339" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1340" spans="1:8">
@@ -38671,7 +38671,7 @@
       </c>
       <c r="H1340" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1341" spans="1:8">
@@ -38699,7 +38699,7 @@
       </c>
       <c r="H1341" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1342" spans="1:8">
@@ -38727,7 +38727,7 @@
       </c>
       <c r="H1342" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1343" spans="1:8">
@@ -38755,7 +38755,7 @@
       </c>
       <c r="H1343" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1344" spans="1:8">
@@ -38783,7 +38783,7 @@
       </c>
       <c r="H1344" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1345" spans="1:8">
@@ -38811,7 +38811,7 @@
       </c>
       <c r="H1345" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1346" spans="1:8">
@@ -38839,7 +38839,7 @@
       </c>
       <c r="H1346" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1347" spans="1:8">
@@ -38867,7 +38867,7 @@
       </c>
       <c r="H1347" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1348" spans="1:8">
@@ -38895,7 +38895,7 @@
       </c>
       <c r="H1348" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1349" spans="1:8">
@@ -38923,7 +38923,7 @@
       </c>
       <c r="H1349" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1350" spans="1:8">
@@ -38951,7 +38951,7 @@
       </c>
       <c r="H1350" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1351" spans="1:8">
@@ -38979,7 +38979,7 @@
       </c>
       <c r="H1351" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1352" spans="1:8">
@@ -39007,7 +39007,7 @@
       </c>
       <c r="H1352" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1353" spans="1:8">
@@ -39035,7 +39035,7 @@
       </c>
       <c r="H1353" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1354" spans="1:8">
@@ -39063,7 +39063,7 @@
       </c>
       <c r="H1354" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1355" spans="1:8">
@@ -39091,7 +39091,7 @@
       </c>
       <c r="H1355" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1356" spans="1:8">
@@ -39119,7 +39119,7 @@
       </c>
       <c r="H1356" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1357" spans="1:8">
@@ -39147,7 +39147,7 @@
       </c>
       <c r="H1357" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1358" spans="1:8">
@@ -39175,7 +39175,7 @@
       </c>
       <c r="H1358" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1359" spans="1:8">
@@ -39203,7 +39203,7 @@
       </c>
       <c r="H1359" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1360" spans="1:8">
@@ -39231,7 +39231,7 @@
       </c>
       <c r="H1360" s="1" t="str">
         <f t="shared" si="183"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1361" spans="1:8">
@@ -39259,7 +39259,7 @@
       </c>
       <c r="H1361" s="1" t="str">
         <f t="shared" ref="H1361:H1384" si="189">H1359</f>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1362" spans="1:8">
@@ -39287,7 +39287,7 @@
       </c>
       <c r="H1362" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1363" spans="1:8">
@@ -39315,7 +39315,7 @@
       </c>
       <c r="H1363" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1364" spans="1:8">
@@ -39343,7 +39343,7 @@
       </c>
       <c r="H1364" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1365" spans="1:8">
@@ -39371,7 +39371,7 @@
       </c>
       <c r="H1365" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1366" spans="1:8">
@@ -39399,7 +39399,7 @@
       </c>
       <c r="H1366" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1367" spans="1:8">
@@ -39427,7 +39427,7 @@
       </c>
       <c r="H1367" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1368" spans="1:8">
@@ -39455,7 +39455,7 @@
       </c>
       <c r="H1368" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1369" spans="1:8">
@@ -39483,7 +39483,7 @@
       </c>
       <c r="H1369" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1370" spans="1:8">
@@ -39511,7 +39511,7 @@
       </c>
       <c r="H1370" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1371" spans="1:8">
@@ -39539,7 +39539,7 @@
       </c>
       <c r="H1371" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1372" spans="1:8">
@@ -39567,7 +39567,7 @@
       </c>
       <c r="H1372" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1373" spans="1:8">
@@ -39595,7 +39595,7 @@
       </c>
       <c r="H1373" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1374" spans="1:8">
@@ -39623,7 +39623,7 @@
       </c>
       <c r="H1374" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1375" spans="1:8">
@@ -39651,7 +39651,7 @@
       </c>
       <c r="H1375" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1376" spans="1:8">
@@ -39679,7 +39679,7 @@
       </c>
       <c r="H1376" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1377" spans="1:8">
@@ -39707,7 +39707,7 @@
       </c>
       <c r="H1377" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1378" spans="1:8">
@@ -39735,7 +39735,7 @@
       </c>
       <c r="H1378" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1379" spans="1:8">
@@ -39763,7 +39763,7 @@
       </c>
       <c r="H1379" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1380" spans="1:8">
@@ -39791,7 +39791,7 @@
       </c>
       <c r="H1380" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1381" spans="1:8">
@@ -39819,7 +39819,7 @@
       </c>
       <c r="H1381" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1382" spans="1:8">
@@ -39847,7 +39847,7 @@
       </c>
       <c r="H1382" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1383" spans="1:8">
@@ -39875,7 +39875,7 @@
       </c>
       <c r="H1383" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>25_1024010_2|25_1022502_1</v>
+        <v>25_1024010_2</v>
       </c>
     </row>
     <row r="1384" spans="1:8">
@@ -39903,7 +39903,7 @@
       </c>
       <c r="H1384" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>26_1024010_2|26_1022502_1</v>
+        <v>26_1024010_2</v>
       </c>
     </row>
     <row r="1385" spans="1:8">
@@ -39986,7 +39986,7 @@
       </c>
       <c r="H1387" s="27" t="str">
         <f>H1385</f>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1388" spans="1:8">
@@ -40014,7 +40014,7 @@
       </c>
       <c r="H1388" s="27" t="str">
         <f>H1386</f>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1389" spans="1:8">
@@ -40042,7 +40042,7 @@
       </c>
       <c r="H1389" s="27" t="str">
         <f t="shared" ref="H1389:H1420" si="192">H1387</f>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1390" spans="1:8">
@@ -40070,7 +40070,7 @@
       </c>
       <c r="H1390" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1391" spans="1:8">
@@ -40098,7 +40098,7 @@
       </c>
       <c r="H1391" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1392" spans="1:8">
@@ -40126,7 +40126,7 @@
       </c>
       <c r="H1392" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1393" spans="1:8">
@@ -40154,7 +40154,7 @@
       </c>
       <c r="H1393" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1394" spans="1:8">
@@ -40182,7 +40182,7 @@
       </c>
       <c r="H1394" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1395" spans="1:8">
@@ -40210,7 +40210,7 @@
       </c>
       <c r="H1395" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1396" spans="1:8">
@@ -40238,7 +40238,7 @@
       </c>
       <c r="H1396" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1397" spans="1:8">
@@ -40266,7 +40266,7 @@
       </c>
       <c r="H1397" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1398" spans="1:8">
@@ -40294,7 +40294,7 @@
       </c>
       <c r="H1398" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1399" spans="1:8">
@@ -40322,7 +40322,7 @@
       </c>
       <c r="H1399" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1400" spans="1:8">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="H1400" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1401" spans="1:8">
@@ -40378,7 +40378,7 @@
       </c>
       <c r="H1401" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1402" spans="1:8">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="H1402" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1403" spans="1:8">
@@ -40434,7 +40434,7 @@
       </c>
       <c r="H1403" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1404" spans="1:8">
@@ -40462,7 +40462,7 @@
       </c>
       <c r="H1404" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1405" spans="1:8">
@@ -40490,7 +40490,7 @@
       </c>
       <c r="H1405" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1406" spans="1:8">
@@ -40518,7 +40518,7 @@
       </c>
       <c r="H1406" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1407" spans="1:8">
@@ -40546,7 +40546,7 @@
       </c>
       <c r="H1407" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1408" spans="1:8">
@@ -40574,7 +40574,7 @@
       </c>
       <c r="H1408" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1409" spans="1:8">
@@ -40602,7 +40602,7 @@
       </c>
       <c r="H1409" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1410" spans="1:8">
@@ -40630,7 +40630,7 @@
       </c>
       <c r="H1410" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1411" spans="1:8">
@@ -40658,7 +40658,7 @@
       </c>
       <c r="H1411" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1412" spans="1:8">
@@ -40686,7 +40686,7 @@
       </c>
       <c r="H1412" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1413" spans="1:8">
@@ -40714,7 +40714,7 @@
       </c>
       <c r="H1413" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1414" spans="1:8">
@@ -40742,7 +40742,7 @@
       </c>
       <c r="H1414" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1415" spans="1:8">
@@ -40770,7 +40770,7 @@
       </c>
       <c r="H1415" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1416" spans="1:8">
@@ -40798,7 +40798,7 @@
       </c>
       <c r="H1416" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1417" spans="1:8">
@@ -40826,7 +40826,7 @@
       </c>
       <c r="H1417" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1418" spans="1:8">
@@ -40854,7 +40854,7 @@
       </c>
       <c r="H1418" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1419" spans="1:8">
@@ -40882,7 +40882,7 @@
       </c>
       <c r="H1419" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1420" spans="1:8">
@@ -40910,7 +40910,7 @@
       </c>
       <c r="H1420" s="27" t="str">
         <f t="shared" si="192"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1421" spans="1:8">
@@ -40938,7 +40938,7 @@
       </c>
       <c r="H1421" s="27" t="str">
         <f t="shared" ref="H1421:H1444" si="198">H1419</f>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1422" spans="1:8">
@@ -40966,7 +40966,7 @@
       </c>
       <c r="H1422" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1423" spans="1:8">
@@ -40994,7 +40994,7 @@
       </c>
       <c r="H1423" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1424" spans="1:8">
@@ -41022,7 +41022,7 @@
       </c>
       <c r="H1424" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1425" spans="1:8">
@@ -41050,7 +41050,7 @@
       </c>
       <c r="H1425" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1426" spans="1:8">
@@ -41078,7 +41078,7 @@
       </c>
       <c r="H1426" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1427" spans="1:8">
@@ -41106,7 +41106,7 @@
       </c>
       <c r="H1427" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1428" spans="1:8">
@@ -41134,7 +41134,7 @@
       </c>
       <c r="H1428" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1429" spans="1:8">
@@ -41162,7 +41162,7 @@
       </c>
       <c r="H1429" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1430" spans="1:8">
@@ -41190,7 +41190,7 @@
       </c>
       <c r="H1430" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1431" spans="1:8">
@@ -41218,7 +41218,7 @@
       </c>
       <c r="H1431" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1432" spans="1:8">
@@ -41246,7 +41246,7 @@
       </c>
       <c r="H1432" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1433" spans="1:8">
@@ -41274,7 +41274,7 @@
       </c>
       <c r="H1433" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1434" spans="1:8">
@@ -41302,7 +41302,7 @@
       </c>
       <c r="H1434" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1435" spans="1:8">
@@ -41330,7 +41330,7 @@
       </c>
       <c r="H1435" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1436" spans="1:8">
@@ -41358,7 +41358,7 @@
       </c>
       <c r="H1436" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1437" spans="1:8">
@@ -41386,7 +41386,7 @@
       </c>
       <c r="H1437" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1438" spans="1:8">
@@ -41414,7 +41414,7 @@
       </c>
       <c r="H1438" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1439" spans="1:8">
@@ -41442,7 +41442,7 @@
       </c>
       <c r="H1439" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1440" spans="1:8">
@@ -41470,7 +41470,7 @@
       </c>
       <c r="H1440" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1441" spans="1:8">
@@ -41498,7 +41498,7 @@
       </c>
       <c r="H1441" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1442" spans="1:8">
@@ -41526,7 +41526,7 @@
       </c>
       <c r="H1442" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1443" spans="1:8">
@@ -41554,7 +41554,7 @@
       </c>
       <c r="H1443" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>25_1024010_2|30_1024001_1|25_1022502_1</v>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1444" spans="1:8">
@@ -41582,7 +41582,7 @@
       </c>
       <c r="H1444" s="27" t="str">
         <f t="shared" si="198"/>
-        <v>26_1024010_2|30_1024001_1|26_1022502_1</v>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1445" spans="1:8">
@@ -41656,7 +41656,7 @@
       </c>
       <c r="H1447" s="32" t="str">
         <f>H1445</f>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1448" spans="1:8">
@@ -41681,7 +41681,7 @@
       </c>
       <c r="H1448" s="32" t="str">
         <f t="shared" ref="H1448:H1456" si="201">H1446</f>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1449" spans="1:8">
@@ -41706,7 +41706,7 @@
       </c>
       <c r="H1449" s="32" t="str">
         <f t="shared" si="201"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1450" spans="1:8">
@@ -41731,7 +41731,7 @@
       </c>
       <c r="H1450" s="32" t="str">
         <f t="shared" si="201"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1451" spans="1:8">
@@ -41756,7 +41756,7 @@
       </c>
       <c r="H1451" s="32" t="str">
         <f t="shared" si="201"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1452" spans="1:8">
@@ -41781,7 +41781,7 @@
       </c>
       <c r="H1452" s="32" t="str">
         <f t="shared" si="201"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1453" spans="1:8">
@@ -41806,7 +41806,7 @@
       </c>
       <c r="H1453" s="32" t="str">
         <f t="shared" si="201"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1454" spans="1:8">
@@ -41831,7 +41831,7 @@
       </c>
       <c r="H1454" s="32" t="str">
         <f t="shared" si="201"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1455" spans="1:8">
@@ -41856,7 +41856,7 @@
       </c>
       <c r="H1455" s="32" t="str">
         <f t="shared" si="201"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1456" spans="1:8">
@@ -41881,7 +41881,7 @@
       </c>
       <c r="H1456" s="32" t="str">
         <f t="shared" si="201"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1457" spans="1:8">
@@ -41906,7 +41906,7 @@
       </c>
       <c r="H1457" s="32" t="str">
         <f t="shared" ref="H1457:H1520" si="202">H1455</f>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1458" spans="1:8">
@@ -41931,7 +41931,7 @@
       </c>
       <c r="H1458" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1459" spans="1:8">
@@ -41956,7 +41956,7 @@
       </c>
       <c r="H1459" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1460" spans="1:8">
@@ -41981,7 +41981,7 @@
       </c>
       <c r="H1460" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1461" spans="1:8">
@@ -42006,7 +42006,7 @@
       </c>
       <c r="H1461" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1462" spans="1:8">
@@ -42031,7 +42031,7 @@
       </c>
       <c r="H1462" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1463" spans="1:8">
@@ -42056,7 +42056,7 @@
       </c>
       <c r="H1463" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1464" spans="1:8">
@@ -42081,7 +42081,7 @@
       </c>
       <c r="H1464" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1465" spans="1:8">
@@ -42106,7 +42106,7 @@
       </c>
       <c r="H1465" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1466" spans="1:8">
@@ -42131,7 +42131,7 @@
       </c>
       <c r="H1466" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1467" spans="1:8">
@@ -42156,7 +42156,7 @@
       </c>
       <c r="H1467" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1468" spans="1:8">
@@ -42181,7 +42181,7 @@
       </c>
       <c r="H1468" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1469" spans="1:8">
@@ -42206,7 +42206,7 @@
       </c>
       <c r="H1469" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1470" spans="1:8">
@@ -42231,7 +42231,7 @@
       </c>
       <c r="H1470" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1471" spans="1:8">
@@ -42256,7 +42256,7 @@
       </c>
       <c r="H1471" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1472" spans="1:8">
@@ -42281,7 +42281,7 @@
       </c>
       <c r="H1472" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1473" spans="1:8">
@@ -42306,7 +42306,7 @@
       </c>
       <c r="H1473" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1474" spans="1:8">
@@ -42331,7 +42331,7 @@
       </c>
       <c r="H1474" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1475" spans="1:8">
@@ -42356,7 +42356,7 @@
       </c>
       <c r="H1475" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1476" spans="1:8">
@@ -42381,7 +42381,7 @@
       </c>
       <c r="H1476" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1477" spans="1:8">
@@ -42406,7 +42406,7 @@
       </c>
       <c r="H1477" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1478" spans="1:8">
@@ -42431,7 +42431,7 @@
       </c>
       <c r="H1478" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1479" spans="1:8">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H1479" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1480" spans="1:8">
@@ -42481,7 +42481,7 @@
       </c>
       <c r="H1480" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1481" spans="1:8">
@@ -42506,7 +42506,7 @@
       </c>
       <c r="H1481" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1482" spans="1:8">
@@ -42531,7 +42531,7 @@
       </c>
       <c r="H1482" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1483" spans="1:8">
@@ -42556,7 +42556,7 @@
       </c>
       <c r="H1483" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1484" spans="1:8">
@@ -42581,7 +42581,7 @@
       </c>
       <c r="H1484" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1485" spans="1:8">
@@ -42606,7 +42606,7 @@
       </c>
       <c r="H1485" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1486" spans="1:8">
@@ -42631,7 +42631,7 @@
       </c>
       <c r="H1486" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1487" spans="1:8">
@@ -42656,7 +42656,7 @@
       </c>
       <c r="H1487" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1488" spans="1:8">
@@ -42681,7 +42681,7 @@
       </c>
       <c r="H1488" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1489" spans="1:8">
@@ -42706,7 +42706,7 @@
       </c>
       <c r="H1489" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1490" spans="1:8">
@@ -42731,7 +42731,7 @@
       </c>
       <c r="H1490" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1491" spans="1:8">
@@ -42756,7 +42756,7 @@
       </c>
       <c r="H1491" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1492" spans="1:8">
@@ -42781,7 +42781,7 @@
       </c>
       <c r="H1492" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1493" spans="1:8">
@@ -42806,7 +42806,7 @@
       </c>
       <c r="H1493" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1494" spans="1:8">
@@ -42831,7 +42831,7 @@
       </c>
       <c r="H1494" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1495" spans="1:8">
@@ -42856,7 +42856,7 @@
       </c>
       <c r="H1495" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1496" spans="1:8">
@@ -42881,7 +42881,7 @@
       </c>
       <c r="H1496" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1497" spans="1:8">
@@ -42906,7 +42906,7 @@
       </c>
       <c r="H1497" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1498" spans="1:8">
@@ -42931,7 +42931,7 @@
       </c>
       <c r="H1498" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1499" spans="1:8">
@@ -42956,7 +42956,7 @@
       </c>
       <c r="H1499" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1500" spans="1:8">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="H1500" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1501" spans="1:8">
@@ -43006,7 +43006,7 @@
       </c>
       <c r="H1501" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1502" spans="1:8">
@@ -43031,7 +43031,7 @@
       </c>
       <c r="H1502" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1503" spans="1:8">
@@ -43056,7 +43056,7 @@
       </c>
       <c r="H1503" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>30_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1504" spans="1:8">
@@ -43081,7 +43081,7 @@
       </c>
       <c r="H1504" s="32" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022505_10|30_1022502_1</v>
+        <v>31_1024008_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1505" spans="1:8">
@@ -43164,7 +43164,7 @@
       </c>
       <c r="H1507" s="28" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1508" spans="1:8">
@@ -43192,7 +43192,7 @@
       </c>
       <c r="H1508" s="28" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1509" spans="1:8">
@@ -43220,7 +43220,7 @@
       </c>
       <c r="H1509" s="28" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1510" spans="1:8">
@@ -43248,7 +43248,7 @@
       </c>
       <c r="H1510" s="28" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1511" spans="1:8">
@@ -43276,7 +43276,7 @@
       </c>
       <c r="H1511" s="28" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1512" spans="1:8">
@@ -43304,7 +43304,7 @@
       </c>
       <c r="H1512" s="28" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1513" spans="1:8">
@@ -43332,7 +43332,7 @@
       </c>
       <c r="H1513" s="28" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1514" spans="1:8">
@@ -43360,7 +43360,7 @@
       </c>
       <c r="H1514" s="28" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1515" spans="1:8">
@@ -43388,7 +43388,7 @@
       </c>
       <c r="H1515" s="28" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1516" spans="1:8">
@@ -43416,7 +43416,7 @@
       </c>
       <c r="H1516" s="28" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1517" spans="1:8">
@@ -43444,7 +43444,7 @@
       </c>
       <c r="H1517" s="28" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1518" spans="1:8">
@@ -43472,7 +43472,7 @@
       </c>
       <c r="H1518" s="28" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1519" spans="1:8">
@@ -43500,7 +43500,7 @@
       </c>
       <c r="H1519" s="28" t="str">
         <f t="shared" si="202"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1520" spans="1:8">
@@ -43528,7 +43528,7 @@
       </c>
       <c r="H1520" s="28" t="str">
         <f t="shared" si="202"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1521" spans="1:8">
@@ -43556,7 +43556,7 @@
       </c>
       <c r="H1521" s="28" t="str">
         <f t="shared" ref="H1521:H1584" si="210">H1519</f>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1522" spans="1:8">
@@ -43584,7 +43584,7 @@
       </c>
       <c r="H1522" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1523" spans="1:8">
@@ -43612,7 +43612,7 @@
       </c>
       <c r="H1523" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1524" spans="1:8">
@@ -43640,7 +43640,7 @@
       </c>
       <c r="H1524" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1525" spans="1:8">
@@ -43668,7 +43668,7 @@
       </c>
       <c r="H1525" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1526" spans="1:8">
@@ -43696,7 +43696,7 @@
       </c>
       <c r="H1526" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1527" spans="1:8">
@@ -43724,7 +43724,7 @@
       </c>
       <c r="H1527" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1528" spans="1:8">
@@ -43752,7 +43752,7 @@
       </c>
       <c r="H1528" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1529" spans="1:8">
@@ -43780,7 +43780,7 @@
       </c>
       <c r="H1529" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1530" spans="1:8">
@@ -43808,7 +43808,7 @@
       </c>
       <c r="H1530" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1531" spans="1:8">
@@ -43836,7 +43836,7 @@
       </c>
       <c r="H1531" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1532" spans="1:8">
@@ -43864,7 +43864,7 @@
       </c>
       <c r="H1532" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1533" spans="1:8">
@@ -43892,7 +43892,7 @@
       </c>
       <c r="H1533" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1534" spans="1:8">
@@ -43920,7 +43920,7 @@
       </c>
       <c r="H1534" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1535" spans="1:8">
@@ -43948,7 +43948,7 @@
       </c>
       <c r="H1535" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1536" spans="1:8">
@@ -43976,7 +43976,7 @@
       </c>
       <c r="H1536" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1537" spans="1:8">
@@ -44004,7 +44004,7 @@
       </c>
       <c r="H1537" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1538" spans="1:8">
@@ -44032,7 +44032,7 @@
       </c>
       <c r="H1538" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1539" spans="1:8">
@@ -44060,7 +44060,7 @@
       </c>
       <c r="H1539" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1540" spans="1:8">
@@ -44088,7 +44088,7 @@
       </c>
       <c r="H1540" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1541" spans="1:8">
@@ -44116,7 +44116,7 @@
       </c>
       <c r="H1541" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1542" spans="1:8">
@@ -44144,7 +44144,7 @@
       </c>
       <c r="H1542" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1543" spans="1:8">
@@ -44172,7 +44172,7 @@
       </c>
       <c r="H1543" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1544" spans="1:8">
@@ -44200,7 +44200,7 @@
       </c>
       <c r="H1544" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1545" spans="1:8">
@@ -44228,7 +44228,7 @@
       </c>
       <c r="H1545" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1546" spans="1:8">
@@ -44256,7 +44256,7 @@
       </c>
       <c r="H1546" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1547" spans="1:8">
@@ -44284,7 +44284,7 @@
       </c>
       <c r="H1547" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1548" spans="1:8">
@@ -44312,7 +44312,7 @@
       </c>
       <c r="H1548" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1549" spans="1:8">
@@ -44340,7 +44340,7 @@
       </c>
       <c r="H1549" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1550" spans="1:8">
@@ -44368,7 +44368,7 @@
       </c>
       <c r="H1550" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1551" spans="1:8">
@@ -44396,7 +44396,7 @@
       </c>
       <c r="H1551" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1552" spans="1:8">
@@ -44424,7 +44424,7 @@
       </c>
       <c r="H1552" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1553" spans="1:8">
@@ -44452,7 +44452,7 @@
       </c>
       <c r="H1553" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1554" spans="1:8">
@@ -44480,7 +44480,7 @@
       </c>
       <c r="H1554" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1555" spans="1:8">
@@ -44508,7 +44508,7 @@
       </c>
       <c r="H1555" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1556" spans="1:8">
@@ -44536,7 +44536,7 @@
       </c>
       <c r="H1556" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1557" spans="1:8">
@@ -44564,7 +44564,7 @@
       </c>
       <c r="H1557" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1558" spans="1:8">
@@ -44592,7 +44592,7 @@
       </c>
       <c r="H1558" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1559" spans="1:8">
@@ -44620,7 +44620,7 @@
       </c>
       <c r="H1559" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1560" spans="1:8">
@@ -44648,7 +44648,7 @@
       </c>
       <c r="H1560" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1561" spans="1:8">
@@ -44676,7 +44676,7 @@
       </c>
       <c r="H1561" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1562" spans="1:8">
@@ -44704,7 +44704,7 @@
       </c>
       <c r="H1562" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1563" spans="1:8">
@@ -44732,7 +44732,7 @@
       </c>
       <c r="H1563" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024008_2|30_1022502_1</v>
+        <v>30_1024008_2</v>
       </c>
     </row>
     <row r="1564" spans="1:8">
@@ -44760,7 +44760,7 @@
       </c>
       <c r="H1564" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024008_2|30_1022502_1</v>
+        <v>31_1024008_2</v>
       </c>
     </row>
     <row r="1565" spans="1:8">
@@ -44843,7 +44843,7 @@
       </c>
       <c r="H1567" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1568" spans="1:8">
@@ -44871,7 +44871,7 @@
       </c>
       <c r="H1568" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1569" spans="1:8">
@@ -44899,7 +44899,7 @@
       </c>
       <c r="H1569" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1570" spans="1:8">
@@ -44927,7 +44927,7 @@
       </c>
       <c r="H1570" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1571" spans="1:8">
@@ -44955,7 +44955,7 @@
       </c>
       <c r="H1571" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1572" spans="1:8">
@@ -44983,7 +44983,7 @@
       </c>
       <c r="H1572" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1573" spans="1:8">
@@ -45011,7 +45011,7 @@
       </c>
       <c r="H1573" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1574" spans="1:8">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H1574" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1575" spans="1:8">
@@ -45067,7 +45067,7 @@
       </c>
       <c r="H1575" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1576" spans="1:8">
@@ -45095,7 +45095,7 @@
       </c>
       <c r="H1576" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1577" spans="1:8">
@@ -45123,7 +45123,7 @@
       </c>
       <c r="H1577" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1578" spans="1:8">
@@ -45151,7 +45151,7 @@
       </c>
       <c r="H1578" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1579" spans="1:8">
@@ -45179,7 +45179,7 @@
       </c>
       <c r="H1579" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1580" spans="1:8">
@@ -45207,7 +45207,7 @@
       </c>
       <c r="H1580" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1581" spans="1:8">
@@ -45235,7 +45235,7 @@
       </c>
       <c r="H1581" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1582" spans="1:8">
@@ -45263,7 +45263,7 @@
       </c>
       <c r="H1582" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1583" spans="1:8">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H1583" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1584" spans="1:8">
@@ -45319,7 +45319,7 @@
       </c>
       <c r="H1584" s="28" t="str">
         <f t="shared" si="210"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1585" spans="1:8">
@@ -45347,7 +45347,7 @@
       </c>
       <c r="H1585" s="28" t="str">
         <f t="shared" ref="H1585:H1648" si="222">H1583</f>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1586" spans="1:8">
@@ -45375,7 +45375,7 @@
       </c>
       <c r="H1586" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1587" spans="1:8">
@@ -45403,7 +45403,7 @@
       </c>
       <c r="H1587" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1588" spans="1:8">
@@ -45431,7 +45431,7 @@
       </c>
       <c r="H1588" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1589" spans="1:8">
@@ -45459,7 +45459,7 @@
       </c>
       <c r="H1589" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1590" spans="1:8">
@@ -45487,7 +45487,7 @@
       </c>
       <c r="H1590" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1591" spans="1:8">
@@ -45515,7 +45515,7 @@
       </c>
       <c r="H1591" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1592" spans="1:8">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H1592" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1593" spans="1:8">
@@ -45571,7 +45571,7 @@
       </c>
       <c r="H1593" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1594" spans="1:8">
@@ -45599,7 +45599,7 @@
       </c>
       <c r="H1594" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1595" spans="1:8">
@@ -45627,7 +45627,7 @@
       </c>
       <c r="H1595" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1596" spans="1:8">
@@ -45655,7 +45655,7 @@
       </c>
       <c r="H1596" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1597" spans="1:8">
@@ -45683,7 +45683,7 @@
       </c>
       <c r="H1597" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1598" spans="1:8">
@@ -45711,7 +45711,7 @@
       </c>
       <c r="H1598" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1599" spans="1:8">
@@ -45739,7 +45739,7 @@
       </c>
       <c r="H1599" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1600" spans="1:8">
@@ -45767,7 +45767,7 @@
       </c>
       <c r="H1600" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1601" spans="1:8">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H1601" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1602" spans="1:8">
@@ -45823,7 +45823,7 @@
       </c>
       <c r="H1602" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1603" spans="1:8">
@@ -45851,7 +45851,7 @@
       </c>
       <c r="H1603" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1604" spans="1:8">
@@ -45879,7 +45879,7 @@
       </c>
       <c r="H1604" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1605" spans="1:8">
@@ -45907,7 +45907,7 @@
       </c>
       <c r="H1605" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1606" spans="1:8">
@@ -45935,7 +45935,7 @@
       </c>
       <c r="H1606" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1607" spans="1:8">
@@ -45963,7 +45963,7 @@
       </c>
       <c r="H1607" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1608" spans="1:8">
@@ -45991,7 +45991,7 @@
       </c>
       <c r="H1608" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1609" spans="1:8">
@@ -46019,7 +46019,7 @@
       </c>
       <c r="H1609" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1610" spans="1:8">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H1610" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1611" spans="1:8">
@@ -46075,7 +46075,7 @@
       </c>
       <c r="H1611" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1612" spans="1:8">
@@ -46103,7 +46103,7 @@
       </c>
       <c r="H1612" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1613" spans="1:8">
@@ -46131,7 +46131,7 @@
       </c>
       <c r="H1613" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1614" spans="1:8">
@@ -46159,7 +46159,7 @@
       </c>
       <c r="H1614" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1615" spans="1:8">
@@ -46187,7 +46187,7 @@
       </c>
       <c r="H1615" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1616" spans="1:8">
@@ -46215,7 +46215,7 @@
       </c>
       <c r="H1616" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1617" spans="1:8">
@@ -46243,7 +46243,7 @@
       </c>
       <c r="H1617" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1618" spans="1:8">
@@ -46271,7 +46271,7 @@
       </c>
       <c r="H1618" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1619" spans="1:8">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H1619" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1620" spans="1:8">
@@ -46327,7 +46327,7 @@
       </c>
       <c r="H1620" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1621" spans="1:8">
@@ -46355,7 +46355,7 @@
       </c>
       <c r="H1621" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1622" spans="1:8">
@@ -46383,7 +46383,7 @@
       </c>
       <c r="H1622" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1623" spans="1:8">
@@ -46411,7 +46411,7 @@
       </c>
       <c r="H1623" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1624" spans="1:8">
@@ -46439,7 +46439,7 @@
       </c>
       <c r="H1624" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1625" spans="1:8">
@@ -46468,7 +46468,7 @@
       </c>
       <c r="H1625" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1626" spans="1:8">
@@ -46496,7 +46496,7 @@
       </c>
       <c r="H1626" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1627" spans="1:8">
@@ -46524,7 +46524,7 @@
       </c>
       <c r="H1627" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1628" spans="1:8">
@@ -46552,7 +46552,7 @@
       </c>
       <c r="H1628" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1629" spans="1:8">
@@ -46580,7 +46580,7 @@
       </c>
       <c r="H1629" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1630" spans="1:8">
@@ -46608,7 +46608,7 @@
       </c>
       <c r="H1630" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1631" spans="1:8">
@@ -46636,7 +46636,7 @@
       </c>
       <c r="H1631" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1632" spans="1:8">
@@ -46664,7 +46664,7 @@
       </c>
       <c r="H1632" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1633" spans="1:8">
@@ -46692,7 +46692,7 @@
       </c>
       <c r="H1633" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1634" spans="1:8">
@@ -46720,7 +46720,7 @@
       </c>
       <c r="H1634" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1635" spans="1:8">
@@ -46748,7 +46748,7 @@
       </c>
       <c r="H1635" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1636" spans="1:8">
@@ -46776,7 +46776,7 @@
       </c>
       <c r="H1636" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1637" spans="1:8">
@@ -46804,7 +46804,7 @@
       </c>
       <c r="H1637" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1638" spans="1:8">
@@ -46832,7 +46832,7 @@
       </c>
       <c r="H1638" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1639" spans="1:8">
@@ -46860,7 +46860,7 @@
       </c>
       <c r="H1639" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1640" spans="1:8">
@@ -46888,7 +46888,7 @@
       </c>
       <c r="H1640" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1641" spans="1:8">
@@ -46916,7 +46916,7 @@
       </c>
       <c r="H1641" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1642" spans="1:8">
@@ -46944,7 +46944,7 @@
       </c>
       <c r="H1642" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1643" spans="1:8">
@@ -46972,7 +46972,7 @@
       </c>
       <c r="H1643" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1644" spans="1:8">
@@ -47000,7 +47000,7 @@
       </c>
       <c r="H1644" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1645" spans="1:8">
@@ -47028,7 +47028,7 @@
       </c>
       <c r="H1645" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1646" spans="1:8">
@@ -47056,7 +47056,7 @@
       </c>
       <c r="H1646" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1647" spans="1:8">
@@ -47084,7 +47084,7 @@
       </c>
       <c r="H1647" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1648" spans="1:8">
@@ -47112,7 +47112,7 @@
       </c>
       <c r="H1648" s="28" t="str">
         <f t="shared" si="222"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1649" spans="1:8">
@@ -47140,7 +47140,7 @@
       </c>
       <c r="H1649" s="28" t="str">
         <f t="shared" ref="H1649:H1712" si="230">H1647</f>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1650" spans="1:8">
@@ -47168,7 +47168,7 @@
       </c>
       <c r="H1650" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1651" spans="1:8">
@@ -47196,7 +47196,7 @@
       </c>
       <c r="H1651" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1652" spans="1:8">
@@ -47224,7 +47224,7 @@
       </c>
       <c r="H1652" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1653" spans="1:8">
@@ -47252,7 +47252,7 @@
       </c>
       <c r="H1653" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1654" spans="1:8">
@@ -47280,7 +47280,7 @@
       </c>
       <c r="H1654" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1655" spans="1:8">
@@ -47308,7 +47308,7 @@
       </c>
       <c r="H1655" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1656" spans="1:8">
@@ -47336,7 +47336,7 @@
       </c>
       <c r="H1656" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1657" spans="1:8">
@@ -47364,7 +47364,7 @@
       </c>
       <c r="H1657" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1658" spans="1:8">
@@ -47392,7 +47392,7 @@
       </c>
       <c r="H1658" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1659" spans="1:8">
@@ -47420,7 +47420,7 @@
       </c>
       <c r="H1659" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1660" spans="1:8">
@@ -47448,7 +47448,7 @@
       </c>
       <c r="H1660" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1661" spans="1:8">
@@ -47476,7 +47476,7 @@
       </c>
       <c r="H1661" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1662" spans="1:8">
@@ -47504,7 +47504,7 @@
       </c>
       <c r="H1662" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1663" spans="1:8">
@@ -47532,7 +47532,7 @@
       </c>
       <c r="H1663" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1664" spans="1:8">
@@ -47560,7 +47560,7 @@
       </c>
       <c r="H1664" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1665" spans="1:8">
@@ -47588,7 +47588,7 @@
       </c>
       <c r="H1665" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1666" spans="1:8">
@@ -47616,7 +47616,7 @@
       </c>
       <c r="H1666" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1667" spans="1:8">
@@ -47644,7 +47644,7 @@
       </c>
       <c r="H1667" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1668" spans="1:8">
@@ -47672,7 +47672,7 @@
       </c>
       <c r="H1668" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1669" spans="1:8">
@@ -47700,7 +47700,7 @@
       </c>
       <c r="H1669" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1670" spans="1:8">
@@ -47728,7 +47728,7 @@
       </c>
       <c r="H1670" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1671" spans="1:8">
@@ -47756,7 +47756,7 @@
       </c>
       <c r="H1671" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1672" spans="1:8">
@@ -47784,7 +47784,7 @@
       </c>
       <c r="H1672" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1673" spans="1:8">
@@ -47812,7 +47812,7 @@
       </c>
       <c r="H1673" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1674" spans="1:8">
@@ -47840,7 +47840,7 @@
       </c>
       <c r="H1674" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1675" spans="1:8">
@@ -47868,7 +47868,7 @@
       </c>
       <c r="H1675" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1676" spans="1:8">
@@ -47896,7 +47896,7 @@
       </c>
       <c r="H1676" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1677" spans="1:8">
@@ -47924,7 +47924,7 @@
       </c>
       <c r="H1677" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1678" spans="1:8">
@@ -47952,7 +47952,7 @@
       </c>
       <c r="H1678" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1679" spans="1:8">
@@ -47980,7 +47980,7 @@
       </c>
       <c r="H1679" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1680" spans="1:8">
@@ -48008,7 +48008,7 @@
       </c>
       <c r="H1680" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1681" spans="1:8">
@@ -48036,7 +48036,7 @@
       </c>
       <c r="H1681" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1682" spans="1:8">
@@ -48064,7 +48064,7 @@
       </c>
       <c r="H1682" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1683" spans="1:8">
@@ -48092,7 +48092,7 @@
       </c>
       <c r="H1683" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024009_2|30_1022502_1</v>
+        <v>30_1024009_2</v>
       </c>
     </row>
     <row r="1684" spans="1:8">
@@ -48120,7 +48120,7 @@
       </c>
       <c r="H1684" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024009_2|30_1022502_1</v>
+        <v>31_1024009_2</v>
       </c>
     </row>
     <row r="1685" spans="1:8">
@@ -48203,7 +48203,7 @@
       </c>
       <c r="H1687" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1688" spans="1:8">
@@ -48231,7 +48231,7 @@
       </c>
       <c r="H1688" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1689" spans="1:8">
@@ -48259,7 +48259,7 @@
       </c>
       <c r="H1689" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1690" spans="1:8">
@@ -48287,7 +48287,7 @@
       </c>
       <c r="H1690" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1691" spans="1:8">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H1691" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1692" spans="1:8">
@@ -48343,7 +48343,7 @@
       </c>
       <c r="H1692" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1693" spans="1:8">
@@ -48371,7 +48371,7 @@
       </c>
       <c r="H1693" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1694" spans="1:8">
@@ -48399,7 +48399,7 @@
       </c>
       <c r="H1694" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1695" spans="1:8">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="H1695" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1696" spans="1:8">
@@ -48455,7 +48455,7 @@
       </c>
       <c r="H1696" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1697" spans="1:8">
@@ -48483,7 +48483,7 @@
       </c>
       <c r="H1697" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1698" spans="1:8">
@@ -48511,7 +48511,7 @@
       </c>
       <c r="H1698" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1699" spans="1:8">
@@ -48539,7 +48539,7 @@
       </c>
       <c r="H1699" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1700" spans="1:8">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H1700" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1701" spans="1:8">
@@ -48595,7 +48595,7 @@
       </c>
       <c r="H1701" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1702" spans="1:8">
@@ -48623,7 +48623,7 @@
       </c>
       <c r="H1702" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1703" spans="1:8">
@@ -48651,7 +48651,7 @@
       </c>
       <c r="H1703" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1704" spans="1:8">
@@ -48679,7 +48679,7 @@
       </c>
       <c r="H1704" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1705" spans="1:8">
@@ -48707,7 +48707,7 @@
       </c>
       <c r="H1705" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1706" spans="1:8">
@@ -48735,7 +48735,7 @@
       </c>
       <c r="H1706" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1707" spans="1:8">
@@ -48763,7 +48763,7 @@
       </c>
       <c r="H1707" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1708" spans="1:8">
@@ -48791,7 +48791,7 @@
       </c>
       <c r="H1708" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1709" spans="1:8">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H1709" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1710" spans="1:8">
@@ -48847,7 +48847,7 @@
       </c>
       <c r="H1710" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1711" spans="1:8">
@@ -48875,7 +48875,7 @@
       </c>
       <c r="H1711" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1712" spans="1:8">
@@ -48903,7 +48903,7 @@
       </c>
       <c r="H1712" s="28" t="str">
         <f t="shared" si="230"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1713" spans="1:8">
@@ -48931,7 +48931,7 @@
       </c>
       <c r="H1713" s="28" t="str">
         <f t="shared" ref="H1713:H1776" si="238">H1711</f>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1714" spans="1:8">
@@ -48959,7 +48959,7 @@
       </c>
       <c r="H1714" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1715" spans="1:8">
@@ -48987,7 +48987,7 @@
       </c>
       <c r="H1715" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1716" spans="1:8">
@@ -49015,7 +49015,7 @@
       </c>
       <c r="H1716" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1717" spans="1:8">
@@ -49043,7 +49043,7 @@
       </c>
       <c r="H1717" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1718" spans="1:8">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H1718" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1719" spans="1:8">
@@ -49099,7 +49099,7 @@
       </c>
       <c r="H1719" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1720" spans="1:8">
@@ -49127,7 +49127,7 @@
       </c>
       <c r="H1720" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1721" spans="1:8">
@@ -49155,7 +49155,7 @@
       </c>
       <c r="H1721" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1722" spans="1:8">
@@ -49183,7 +49183,7 @@
       </c>
       <c r="H1722" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1723" spans="1:8">
@@ -49211,7 +49211,7 @@
       </c>
       <c r="H1723" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1724" spans="1:8">
@@ -49239,7 +49239,7 @@
       </c>
       <c r="H1724" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1725" spans="1:8">
@@ -49267,7 +49267,7 @@
       </c>
       <c r="H1725" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1726" spans="1:8">
@@ -49295,7 +49295,7 @@
       </c>
       <c r="H1726" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1727" spans="1:8">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H1727" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1728" spans="1:8">
@@ -49351,7 +49351,7 @@
       </c>
       <c r="H1728" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1729" spans="1:8">
@@ -49379,7 +49379,7 @@
       </c>
       <c r="H1729" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1730" spans="1:8">
@@ -49407,7 +49407,7 @@
       </c>
       <c r="H1730" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1731" spans="1:8">
@@ -49435,7 +49435,7 @@
       </c>
       <c r="H1731" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1732" spans="1:8">
@@ -49463,7 +49463,7 @@
       </c>
       <c r="H1732" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1733" spans="1:8">
@@ -49491,7 +49491,7 @@
       </c>
       <c r="H1733" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1734" spans="1:8">
@@ -49519,7 +49519,7 @@
       </c>
       <c r="H1734" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1735" spans="1:8">
@@ -49547,7 +49547,7 @@
       </c>
       <c r="H1735" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1736" spans="1:8">
@@ -49575,7 +49575,7 @@
       </c>
       <c r="H1736" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1737" spans="1:8">
@@ -49603,7 +49603,7 @@
       </c>
       <c r="H1737" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1738" spans="1:8">
@@ -49631,7 +49631,7 @@
       </c>
       <c r="H1738" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1739" spans="1:8">
@@ -49659,7 +49659,7 @@
       </c>
       <c r="H1739" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1740" spans="1:8">
@@ -49687,7 +49687,7 @@
       </c>
       <c r="H1740" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1741" spans="1:8">
@@ -49715,7 +49715,7 @@
       </c>
       <c r="H1741" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1742" spans="1:8">
@@ -49743,7 +49743,7 @@
       </c>
       <c r="H1742" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1743" spans="1:8">
@@ -49771,7 +49771,7 @@
       </c>
       <c r="H1743" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1744" spans="1:8">
@@ -49799,7 +49799,7 @@
       </c>
       <c r="H1744" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1745" spans="1:8">
@@ -49828,7 +49828,7 @@
       </c>
       <c r="H1745" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1746" spans="1:8">
@@ -49856,7 +49856,7 @@
       </c>
       <c r="H1746" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1747" spans="1:8">
@@ -49884,7 +49884,7 @@
       </c>
       <c r="H1747" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1748" spans="1:8">
@@ -49912,7 +49912,7 @@
       </c>
       <c r="H1748" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1749" spans="1:8">
@@ -49940,7 +49940,7 @@
       </c>
       <c r="H1749" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1750" spans="1:8">
@@ -49968,7 +49968,7 @@
       </c>
       <c r="H1750" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1751" spans="1:8">
@@ -49996,7 +49996,7 @@
       </c>
       <c r="H1751" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1752" spans="1:8">
@@ -50024,7 +50024,7 @@
       </c>
       <c r="H1752" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1753" spans="1:8">
@@ -50052,7 +50052,7 @@
       </c>
       <c r="H1753" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1754" spans="1:8">
@@ -50080,7 +50080,7 @@
       </c>
       <c r="H1754" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1755" spans="1:8">
@@ -50108,7 +50108,7 @@
       </c>
       <c r="H1755" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1756" spans="1:8">
@@ -50136,7 +50136,7 @@
       </c>
       <c r="H1756" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1757" spans="1:8">
@@ -50164,7 +50164,7 @@
       </c>
       <c r="H1757" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1758" spans="1:8">
@@ -50192,7 +50192,7 @@
       </c>
       <c r="H1758" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1759" spans="1:8">
@@ -50220,7 +50220,7 @@
       </c>
       <c r="H1759" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1760" spans="1:8">
@@ -50248,7 +50248,7 @@
       </c>
       <c r="H1760" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1761" spans="1:8">
@@ -50276,7 +50276,7 @@
       </c>
       <c r="H1761" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1762" spans="1:8">
@@ -50304,7 +50304,7 @@
       </c>
       <c r="H1762" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1763" spans="1:8">
@@ -50332,7 +50332,7 @@
       </c>
       <c r="H1763" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1764" spans="1:8">
@@ -50360,7 +50360,7 @@
       </c>
       <c r="H1764" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1765" spans="1:8">
@@ -50388,7 +50388,7 @@
       </c>
       <c r="H1765" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1766" spans="1:8">
@@ -50416,7 +50416,7 @@
       </c>
       <c r="H1766" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1767" spans="1:8">
@@ -50444,7 +50444,7 @@
       </c>
       <c r="H1767" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1768" spans="1:8">
@@ -50472,7 +50472,7 @@
       </c>
       <c r="H1768" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1769" spans="1:8">
@@ -50500,7 +50500,7 @@
       </c>
       <c r="H1769" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1770" spans="1:8">
@@ -50528,7 +50528,7 @@
       </c>
       <c r="H1770" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1771" spans="1:8">
@@ -50556,7 +50556,7 @@
       </c>
       <c r="H1771" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1772" spans="1:8">
@@ -50584,7 +50584,7 @@
       </c>
       <c r="H1772" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1773" spans="1:8">
@@ -50612,7 +50612,7 @@
       </c>
       <c r="H1773" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1774" spans="1:8">
@@ -50640,7 +50640,7 @@
       </c>
       <c r="H1774" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1775" spans="1:8">
@@ -50668,7 +50668,7 @@
       </c>
       <c r="H1775" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1776" spans="1:8">
@@ -50696,7 +50696,7 @@
       </c>
       <c r="H1776" s="28" t="str">
         <f t="shared" si="238"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1777" spans="1:8">
@@ -50724,7 +50724,7 @@
       </c>
       <c r="H1777" s="28" t="str">
         <f t="shared" ref="H1777:H1805" si="246">H1775</f>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1778" spans="1:8">
@@ -50752,7 +50752,7 @@
       </c>
       <c r="H1778" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1779" spans="1:8">
@@ -50780,7 +50780,7 @@
       </c>
       <c r="H1779" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1780" spans="1:8">
@@ -50808,7 +50808,7 @@
       </c>
       <c r="H1780" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1781" spans="1:8">
@@ -50836,7 +50836,7 @@
       </c>
       <c r="H1781" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1782" spans="1:8">
@@ -50864,7 +50864,7 @@
       </c>
       <c r="H1782" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1783" spans="1:8">
@@ -50892,7 +50892,7 @@
       </c>
       <c r="H1783" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1784" spans="1:8">
@@ -50920,7 +50920,7 @@
       </c>
       <c r="H1784" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1785" spans="1:8">
@@ -50948,7 +50948,7 @@
       </c>
       <c r="H1785" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1786" spans="1:8">
@@ -50976,7 +50976,7 @@
       </c>
       <c r="H1786" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1787" spans="1:8">
@@ -51004,7 +51004,7 @@
       </c>
       <c r="H1787" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1788" spans="1:8">
@@ -51032,7 +51032,7 @@
       </c>
       <c r="H1788" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1789" spans="1:8">
@@ -51060,7 +51060,7 @@
       </c>
       <c r="H1789" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1790" spans="1:8">
@@ -51088,7 +51088,7 @@
       </c>
       <c r="H1790" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1791" spans="1:8">
@@ -51116,7 +51116,7 @@
       </c>
       <c r="H1791" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1792" spans="1:8">
@@ -51144,7 +51144,7 @@
       </c>
       <c r="H1792" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1793" spans="1:8">
@@ -51172,7 +51172,7 @@
       </c>
       <c r="H1793" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1794" spans="1:8">
@@ -51200,7 +51200,7 @@
       </c>
       <c r="H1794" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1795" spans="1:8">
@@ -51228,7 +51228,7 @@
       </c>
       <c r="H1795" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1796" spans="1:8">
@@ -51256,7 +51256,7 @@
       </c>
       <c r="H1796" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1797" spans="1:8">
@@ -51284,7 +51284,7 @@
       </c>
       <c r="H1797" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1798" spans="1:8">
@@ -51312,7 +51312,7 @@
       </c>
       <c r="H1798" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1799" spans="1:8">
@@ -51340,7 +51340,7 @@
       </c>
       <c r="H1799" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1800" spans="1:8">
@@ -51368,7 +51368,7 @@
       </c>
       <c r="H1800" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1801" spans="1:8">
@@ -51396,7 +51396,7 @@
       </c>
       <c r="H1801" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1802" spans="1:8">
@@ -51424,7 +51424,7 @@
       </c>
       <c r="H1802" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1803" spans="1:8">
@@ -51452,7 +51452,7 @@
       </c>
       <c r="H1803" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>30_1024010_2|30_1022502_1</v>
+        <v>30_1024010_2</v>
       </c>
     </row>
     <row r="1804" spans="1:8">
@@ -51480,7 +51480,7 @@
       </c>
       <c r="H1804" s="28" t="str">
         <f t="shared" si="246"/>
-        <v>31_1024010_2|30_1022502_1</v>
+        <v>31_1024010_2</v>
       </c>
     </row>
     <row r="1805" spans="1:8">

--- a/hall/resources/sample/VisitorLevel.xlsx
+++ b/hall/resources/sample/VisitorLevel.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="VisitorLevel" sheetId="9" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2069" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2069" uniqueCount="294">
   <si>
     <t>ID</t>
   </si>
@@ -924,19 +924,13 @@
     <t>摸金校尉</t>
   </si>
   <si>
-    <t>30_1024008_2</t>
-  </si>
-  <si>
-    <t>31_1024008_2</t>
+    <t>25_1024009_2|30_1024001_1</t>
   </si>
   <si>
     <t>氪金大佬</t>
   </si>
   <si>
-    <t>30_1024009_2</t>
-  </si>
-  <si>
-    <t>31_1024009_2</t>
+    <t>30_1024009_2|30_1022505_10</t>
   </si>
   <si>
     <t>穿搭博主</t>
@@ -945,10 +939,7 @@
     <t>美妆新秀</t>
   </si>
   <si>
-    <t>30_1024010_2</t>
-  </si>
-  <si>
-    <t>31_1024010_2</t>
+    <t>30_1024010_2|30_1022505_10</t>
   </si>
   <si>
     <t>高定女王</t>
@@ -1707,7 +1698,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1788,9 +1779,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -39261,7 +39249,7 @@
       <c r="G1445" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="H1445" s="27" t="s">
+      <c r="H1445" s="24" t="s">
         <v>236</v>
       </c>
     </row>
@@ -39285,7 +39273,7 @@
       <c r="G1446" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="H1446" s="27" t="s">
+      <c r="H1446" s="24" t="s">
         <v>237</v>
       </c>
     </row>
@@ -39309,7 +39297,7 @@
       <c r="G1447" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="H1447" s="27" t="str">
+      <c r="H1447" s="24" t="str">
         <f>H1445</f>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -39334,7 +39322,7 @@
       <c r="G1448" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="H1448" s="27" t="str">
+      <c r="H1448" s="24" t="str">
         <f t="shared" ref="H1448:H1456" si="159">H1446</f>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -39359,7 +39347,7 @@
       <c r="G1449" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="H1449" s="27" t="str">
+      <c r="H1449" s="24" t="str">
         <f t="shared" si="159"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -39384,7 +39372,7 @@
       <c r="G1450" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="H1450" s="27" t="str">
+      <c r="H1450" s="24" t="str">
         <f t="shared" si="159"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -39409,7 +39397,7 @@
       <c r="G1451" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="H1451" s="27" t="str">
+      <c r="H1451" s="24" t="str">
         <f t="shared" si="159"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -39434,7 +39422,7 @@
       <c r="G1452" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="H1452" s="27" t="str">
+      <c r="H1452" s="24" t="str">
         <f t="shared" si="159"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -39459,7 +39447,7 @@
       <c r="G1453" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="H1453" s="27" t="str">
+      <c r="H1453" s="24" t="str">
         <f t="shared" si="159"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -39484,7 +39472,7 @@
       <c r="G1454" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="H1454" s="27" t="str">
+      <c r="H1454" s="24" t="str">
         <f t="shared" si="159"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -39509,7 +39497,7 @@
       <c r="G1455" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="H1455" s="27" t="str">
+      <c r="H1455" s="24" t="str">
         <f t="shared" si="159"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -39534,7 +39522,7 @@
       <c r="G1456" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="H1456" s="27" t="str">
+      <c r="H1456" s="24" t="str">
         <f t="shared" si="159"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -39559,7 +39547,7 @@
       <c r="G1457" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="H1457" s="27" t="str">
+      <c r="H1457" s="24" t="str">
         <f t="shared" ref="H1457:H1520" si="160">H1455</f>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -39584,7 +39572,7 @@
       <c r="G1458" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="H1458" s="27" t="str">
+      <c r="H1458" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -39609,7 +39597,7 @@
       <c r="G1459" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="H1459" s="27" t="str">
+      <c r="H1459" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -39634,7 +39622,7 @@
       <c r="G1460" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="H1460" s="27" t="str">
+      <c r="H1460" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -39659,7 +39647,7 @@
       <c r="G1461" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="H1461" s="27" t="str">
+      <c r="H1461" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -39684,7 +39672,7 @@
       <c r="G1462" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="H1462" s="27" t="str">
+      <c r="H1462" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -39709,7 +39697,7 @@
       <c r="G1463" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="H1463" s="27" t="str">
+      <c r="H1463" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -39734,7 +39722,7 @@
       <c r="G1464" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="H1464" s="27" t="str">
+      <c r="H1464" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -39759,7 +39747,7 @@
       <c r="G1465" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="H1465" s="27" t="str">
+      <c r="H1465" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -39784,7 +39772,7 @@
       <c r="G1466" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="H1466" s="27" t="str">
+      <c r="H1466" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -39809,7 +39797,7 @@
       <c r="G1467" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="H1467" s="27" t="str">
+      <c r="H1467" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -39834,7 +39822,7 @@
       <c r="G1468" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="H1468" s="27" t="str">
+      <c r="H1468" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -39859,7 +39847,7 @@
       <c r="G1469" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="H1469" s="27" t="str">
+      <c r="H1469" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -39884,7 +39872,7 @@
       <c r="G1470" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="H1470" s="27" t="str">
+      <c r="H1470" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -39909,7 +39897,7 @@
       <c r="G1471" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="H1471" s="27" t="str">
+      <c r="H1471" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -39934,7 +39922,7 @@
       <c r="G1472" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="H1472" s="27" t="str">
+      <c r="H1472" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -39959,7 +39947,7 @@
       <c r="G1473" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="H1473" s="27" t="str">
+      <c r="H1473" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -39984,7 +39972,7 @@
       <c r="G1474" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="H1474" s="27" t="str">
+      <c r="H1474" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -40009,7 +39997,7 @@
       <c r="G1475" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="H1475" s="27" t="str">
+      <c r="H1475" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -40034,7 +40022,7 @@
       <c r="G1476" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="H1476" s="27" t="str">
+      <c r="H1476" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -40059,7 +40047,7 @@
       <c r="G1477" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H1477" s="27" t="str">
+      <c r="H1477" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -40084,7 +40072,7 @@
       <c r="G1478" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="H1478" s="27" t="str">
+      <c r="H1478" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -40109,7 +40097,7 @@
       <c r="G1479" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="H1479" s="27" t="str">
+      <c r="H1479" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -40134,7 +40122,7 @@
       <c r="G1480" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H1480" s="27" t="str">
+      <c r="H1480" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -40159,7 +40147,7 @@
       <c r="G1481" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="H1481" s="27" t="str">
+      <c r="H1481" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -40184,7 +40172,7 @@
       <c r="G1482" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="H1482" s="27" t="str">
+      <c r="H1482" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -40209,7 +40197,7 @@
       <c r="G1483" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="H1483" s="27" t="str">
+      <c r="H1483" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -40234,7 +40222,7 @@
       <c r="G1484" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="H1484" s="27" t="str">
+      <c r="H1484" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -40259,7 +40247,7 @@
       <c r="G1485" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="H1485" s="27" t="str">
+      <c r="H1485" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -40284,7 +40272,7 @@
       <c r="G1486" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="H1486" s="27" t="str">
+      <c r="H1486" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -40309,7 +40297,7 @@
       <c r="G1487" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="H1487" s="27" t="str">
+      <c r="H1487" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -40334,7 +40322,7 @@
       <c r="G1488" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="H1488" s="27" t="str">
+      <c r="H1488" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -40359,7 +40347,7 @@
       <c r="G1489" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="H1489" s="27" t="str">
+      <c r="H1489" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -40384,7 +40372,7 @@
       <c r="G1490" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="H1490" s="27" t="str">
+      <c r="H1490" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -40409,7 +40397,7 @@
       <c r="G1491" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="H1491" s="27" t="str">
+      <c r="H1491" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -40434,7 +40422,7 @@
       <c r="G1492" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="H1492" s="27" t="str">
+      <c r="H1492" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -40459,7 +40447,7 @@
       <c r="G1493" s="26" t="s">
         <v>223</v>
       </c>
-      <c r="H1493" s="27" t="str">
+      <c r="H1493" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -40484,7 +40472,7 @@
       <c r="G1494" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="H1494" s="27" t="str">
+      <c r="H1494" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -40509,7 +40497,7 @@
       <c r="G1495" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="H1495" s="27" t="str">
+      <c r="H1495" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -40534,7 +40522,7 @@
       <c r="G1496" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="H1496" s="27" t="str">
+      <c r="H1496" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -40559,7 +40547,7 @@
       <c r="G1497" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="H1497" s="27" t="str">
+      <c r="H1497" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -40584,7 +40572,7 @@
       <c r="G1498" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="H1498" s="27" t="str">
+      <c r="H1498" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -40609,7 +40597,7 @@
       <c r="G1499" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="H1499" s="27" t="str">
+      <c r="H1499" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -40634,7 +40622,7 @@
       <c r="G1500" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="H1500" s="27" t="str">
+      <c r="H1500" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -40659,7 +40647,7 @@
       <c r="G1501" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="H1501" s="27" t="str">
+      <c r="H1501" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -40684,7 +40672,7 @@
       <c r="G1502" s="26" t="s">
         <v>273</v>
       </c>
-      <c r="H1502" s="27" t="str">
+      <c r="H1502" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -40709,7 +40697,7 @@
       <c r="G1503" s="26" t="s">
         <v>274</v>
       </c>
-      <c r="H1503" s="27" t="str">
+      <c r="H1503" s="24" t="str">
         <f t="shared" si="160"/>
         <v>30_1024008_2|30_1022505_10</v>
       </c>
@@ -40734,7 +40722,7 @@
       <c r="G1504" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="H1504" s="27" t="str">
+      <c r="H1504" s="24" t="str">
         <f t="shared" si="160"/>
         <v>31_1024008_2|30_1022505_10</v>
       </c>
@@ -40761,7 +40749,7 @@
       <c r="G1505" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="H1505" s="24" t="s">
+      <c r="H1505" s="2" t="s">
         <v>277</v>
       </c>
     </row>
@@ -40786,8 +40774,9 @@
       <c r="G1506" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="H1506" s="24" t="s">
-        <v>278</v>
+      <c r="H1506" s="24" t="str">
+        <f>H1505</f>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1507" spans="1:8">
@@ -40813,7 +40802,7 @@
       </c>
       <c r="H1507" s="24" t="str">
         <f t="shared" si="160"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1508" spans="1:8">
@@ -40839,7 +40828,7 @@
       </c>
       <c r="H1508" s="24" t="str">
         <f t="shared" si="160"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1509" spans="1:8">
@@ -40865,7 +40854,7 @@
       </c>
       <c r="H1509" s="24" t="str">
         <f t="shared" si="160"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1510" spans="1:8">
@@ -40891,7 +40880,7 @@
       </c>
       <c r="H1510" s="24" t="str">
         <f t="shared" si="160"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1511" spans="1:8">
@@ -40917,7 +40906,7 @@
       </c>
       <c r="H1511" s="24" t="str">
         <f t="shared" si="160"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1512" spans="1:8">
@@ -40943,7 +40932,7 @@
       </c>
       <c r="H1512" s="24" t="str">
         <f t="shared" si="160"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1513" spans="1:8">
@@ -40969,7 +40958,7 @@
       </c>
       <c r="H1513" s="24" t="str">
         <f t="shared" si="160"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1514" spans="1:8">
@@ -40995,7 +40984,7 @@
       </c>
       <c r="H1514" s="24" t="str">
         <f t="shared" si="160"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1515" spans="1:8">
@@ -41021,7 +41010,7 @@
       </c>
       <c r="H1515" s="24" t="str">
         <f t="shared" si="160"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1516" spans="1:8">
@@ -41047,7 +41036,7 @@
       </c>
       <c r="H1516" s="24" t="str">
         <f t="shared" si="160"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1517" spans="1:8">
@@ -41073,7 +41062,7 @@
       </c>
       <c r="H1517" s="24" t="str">
         <f t="shared" si="160"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1518" spans="1:8">
@@ -41099,7 +41088,7 @@
       </c>
       <c r="H1518" s="24" t="str">
         <f t="shared" si="160"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1519" spans="1:8">
@@ -41125,7 +41114,7 @@
       </c>
       <c r="H1519" s="24" t="str">
         <f t="shared" si="160"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1520" spans="1:8">
@@ -41151,7 +41140,7 @@
       </c>
       <c r="H1520" s="24" t="str">
         <f t="shared" si="160"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1521" spans="1:8">
@@ -41177,7 +41166,7 @@
       </c>
       <c r="H1521" s="24" t="str">
         <f t="shared" ref="H1521:H1584" si="166">H1519</f>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1522" spans="1:8">
@@ -41203,7 +41192,7 @@
       </c>
       <c r="H1522" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1523" spans="1:8">
@@ -41229,7 +41218,7 @@
       </c>
       <c r="H1523" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1524" spans="1:8">
@@ -41255,7 +41244,7 @@
       </c>
       <c r="H1524" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1525" spans="1:8">
@@ -41281,7 +41270,7 @@
       </c>
       <c r="H1525" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1526" spans="1:8">
@@ -41307,7 +41296,7 @@
       </c>
       <c r="H1526" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1527" spans="1:8">
@@ -41333,7 +41322,7 @@
       </c>
       <c r="H1527" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1528" spans="1:8">
@@ -41359,7 +41348,7 @@
       </c>
       <c r="H1528" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1529" spans="1:8">
@@ -41385,7 +41374,7 @@
       </c>
       <c r="H1529" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1530" spans="1:8">
@@ -41411,7 +41400,7 @@
       </c>
       <c r="H1530" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1531" spans="1:8">
@@ -41437,7 +41426,7 @@
       </c>
       <c r="H1531" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1532" spans="1:8">
@@ -41463,7 +41452,7 @@
       </c>
       <c r="H1532" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1533" spans="1:8">
@@ -41489,7 +41478,7 @@
       </c>
       <c r="H1533" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1534" spans="1:8">
@@ -41515,7 +41504,7 @@
       </c>
       <c r="H1534" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1535" spans="1:8">
@@ -41541,7 +41530,7 @@
       </c>
       <c r="H1535" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1536" spans="1:8">
@@ -41567,7 +41556,7 @@
       </c>
       <c r="H1536" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1537" spans="1:8">
@@ -41593,7 +41582,7 @@
       </c>
       <c r="H1537" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1538" spans="1:8">
@@ -41619,7 +41608,7 @@
       </c>
       <c r="H1538" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1539" spans="1:8">
@@ -41645,7 +41634,7 @@
       </c>
       <c r="H1539" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1540" spans="1:8">
@@ -41671,7 +41660,7 @@
       </c>
       <c r="H1540" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1541" spans="1:8">
@@ -41697,7 +41686,7 @@
       </c>
       <c r="H1541" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1542" spans="1:8">
@@ -41723,7 +41712,7 @@
       </c>
       <c r="H1542" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1543" spans="1:8">
@@ -41749,7 +41738,7 @@
       </c>
       <c r="H1543" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1544" spans="1:8">
@@ -41775,7 +41764,7 @@
       </c>
       <c r="H1544" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1545" spans="1:8">
@@ -41801,7 +41790,7 @@
       </c>
       <c r="H1545" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1546" spans="1:8">
@@ -41827,7 +41816,7 @@
       </c>
       <c r="H1546" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1547" spans="1:8">
@@ -41853,7 +41842,7 @@
       </c>
       <c r="H1547" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1548" spans="1:8">
@@ -41879,7 +41868,7 @@
       </c>
       <c r="H1548" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1549" spans="1:8">
@@ -41905,7 +41894,7 @@
       </c>
       <c r="H1549" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1550" spans="1:8">
@@ -41931,7 +41920,7 @@
       </c>
       <c r="H1550" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1551" spans="1:8">
@@ -41957,7 +41946,7 @@
       </c>
       <c r="H1551" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1552" spans="1:8">
@@ -41983,7 +41972,7 @@
       </c>
       <c r="H1552" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1553" spans="1:8">
@@ -42009,7 +41998,7 @@
       </c>
       <c r="H1553" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1554" spans="1:8">
@@ -42035,7 +42024,7 @@
       </c>
       <c r="H1554" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1555" spans="1:8">
@@ -42061,7 +42050,7 @@
       </c>
       <c r="H1555" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1556" spans="1:8">
@@ -42087,7 +42076,7 @@
       </c>
       <c r="H1556" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1557" spans="1:8">
@@ -42113,7 +42102,7 @@
       </c>
       <c r="H1557" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1558" spans="1:8">
@@ -42139,7 +42128,7 @@
       </c>
       <c r="H1558" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1559" spans="1:8">
@@ -42165,7 +42154,7 @@
       </c>
       <c r="H1559" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1560" spans="1:8">
@@ -42191,7 +42180,7 @@
       </c>
       <c r="H1560" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1561" spans="1:8">
@@ -42217,7 +42206,7 @@
       </c>
       <c r="H1561" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1562" spans="1:8">
@@ -42243,7 +42232,7 @@
       </c>
       <c r="H1562" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1563" spans="1:8">
@@ -42269,7 +42258,7 @@
       </c>
       <c r="H1563" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1564" spans="1:8">
@@ -42295,7 +42284,7 @@
       </c>
       <c r="H1564" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024008_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1565" spans="1:8">
@@ -42311,7 +42300,7 @@
         <v>1</v>
       </c>
       <c r="D1565" s="25" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E1565" s="24">
         <v>50</v>
@@ -42321,7 +42310,7 @@
         <v>50</v>
       </c>
       <c r="H1565" s="24" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="1566" spans="1:8">
@@ -42345,8 +42334,9 @@
       <c r="G1566" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="H1566" s="24" t="s">
-        <v>281</v>
+      <c r="H1566" s="24" t="str">
+        <f>H1565</f>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1567" spans="1:8">
@@ -42372,7 +42362,7 @@
       </c>
       <c r="H1567" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1568" spans="1:8">
@@ -42398,7 +42388,7 @@
       </c>
       <c r="H1568" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1569" spans="1:8">
@@ -42424,7 +42414,7 @@
       </c>
       <c r="H1569" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1570" spans="1:8">
@@ -42450,7 +42440,7 @@
       </c>
       <c r="H1570" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1571" spans="1:8">
@@ -42476,7 +42466,7 @@
       </c>
       <c r="H1571" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1572" spans="1:8">
@@ -42502,7 +42492,7 @@
       </c>
       <c r="H1572" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1573" spans="1:8">
@@ -42528,7 +42518,7 @@
       </c>
       <c r="H1573" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1574" spans="1:8">
@@ -42554,7 +42544,7 @@
       </c>
       <c r="H1574" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1575" spans="1:8">
@@ -42580,7 +42570,7 @@
       </c>
       <c r="H1575" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1576" spans="1:8">
@@ -42606,7 +42596,7 @@
       </c>
       <c r="H1576" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1577" spans="1:8">
@@ -42632,7 +42622,7 @@
       </c>
       <c r="H1577" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1578" spans="1:8">
@@ -42658,7 +42648,7 @@
       </c>
       <c r="H1578" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1579" spans="1:8">
@@ -42684,7 +42674,7 @@
       </c>
       <c r="H1579" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1580" spans="1:8">
@@ -42710,7 +42700,7 @@
       </c>
       <c r="H1580" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1581" spans="1:8">
@@ -42736,7 +42726,7 @@
       </c>
       <c r="H1581" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1582" spans="1:8">
@@ -42762,7 +42752,7 @@
       </c>
       <c r="H1582" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1583" spans="1:8">
@@ -42788,7 +42778,7 @@
       </c>
       <c r="H1583" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1584" spans="1:8">
@@ -42814,7 +42804,7 @@
       </c>
       <c r="H1584" s="24" t="str">
         <f t="shared" si="166"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1585" spans="1:8">
@@ -42840,7 +42830,7 @@
       </c>
       <c r="H1585" s="24" t="str">
         <f t="shared" ref="H1585:H1648" si="174">H1583</f>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1586" spans="1:8">
@@ -42866,7 +42856,7 @@
       </c>
       <c r="H1586" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1587" spans="1:8">
@@ -42892,7 +42882,7 @@
       </c>
       <c r="H1587" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1588" spans="1:8">
@@ -42918,7 +42908,7 @@
       </c>
       <c r="H1588" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1589" spans="1:8">
@@ -42944,7 +42934,7 @@
       </c>
       <c r="H1589" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1590" spans="1:8">
@@ -42970,7 +42960,7 @@
       </c>
       <c r="H1590" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1591" spans="1:8">
@@ -42996,7 +42986,7 @@
       </c>
       <c r="H1591" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1592" spans="1:8">
@@ -43022,7 +43012,7 @@
       </c>
       <c r="H1592" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1593" spans="1:8">
@@ -43048,7 +43038,7 @@
       </c>
       <c r="H1593" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1594" spans="1:8">
@@ -43074,7 +43064,7 @@
       </c>
       <c r="H1594" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1595" spans="1:8">
@@ -43100,7 +43090,7 @@
       </c>
       <c r="H1595" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1596" spans="1:8">
@@ -43126,7 +43116,7 @@
       </c>
       <c r="H1596" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1597" spans="1:8">
@@ -43152,7 +43142,7 @@
       </c>
       <c r="H1597" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1598" spans="1:8">
@@ -43178,7 +43168,7 @@
       </c>
       <c r="H1598" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1599" spans="1:8">
@@ -43204,7 +43194,7 @@
       </c>
       <c r="H1599" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1600" spans="1:8">
@@ -43230,7 +43220,7 @@
       </c>
       <c r="H1600" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1601" spans="1:8">
@@ -43256,7 +43246,7 @@
       </c>
       <c r="H1601" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1602" spans="1:8">
@@ -43282,7 +43272,7 @@
       </c>
       <c r="H1602" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1603" spans="1:8">
@@ -43308,7 +43298,7 @@
       </c>
       <c r="H1603" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1604" spans="1:8">
@@ -43334,7 +43324,7 @@
       </c>
       <c r="H1604" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1605" spans="1:8">
@@ -43360,7 +43350,7 @@
       </c>
       <c r="H1605" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1606" spans="1:8">
@@ -43386,7 +43376,7 @@
       </c>
       <c r="H1606" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1607" spans="1:8">
@@ -43412,7 +43402,7 @@
       </c>
       <c r="H1607" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1608" spans="1:8">
@@ -43438,7 +43428,7 @@
       </c>
       <c r="H1608" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1609" spans="1:8">
@@ -43464,7 +43454,7 @@
       </c>
       <c r="H1609" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1610" spans="1:8">
@@ -43490,7 +43480,7 @@
       </c>
       <c r="H1610" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1611" spans="1:8">
@@ -43516,7 +43506,7 @@
       </c>
       <c r="H1611" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1612" spans="1:8">
@@ -43542,7 +43532,7 @@
       </c>
       <c r="H1612" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1613" spans="1:8">
@@ -43568,7 +43558,7 @@
       </c>
       <c r="H1613" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1614" spans="1:8">
@@ -43594,7 +43584,7 @@
       </c>
       <c r="H1614" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1615" spans="1:8">
@@ -43620,7 +43610,7 @@
       </c>
       <c r="H1615" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1616" spans="1:8">
@@ -43646,7 +43636,7 @@
       </c>
       <c r="H1616" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1617" spans="1:8">
@@ -43672,7 +43662,7 @@
       </c>
       <c r="H1617" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1618" spans="1:8">
@@ -43698,7 +43688,7 @@
       </c>
       <c r="H1618" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1619" spans="1:8">
@@ -43724,7 +43714,7 @@
       </c>
       <c r="H1619" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1620" spans="1:8">
@@ -43750,7 +43740,7 @@
       </c>
       <c r="H1620" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1621" spans="1:8">
@@ -43776,7 +43766,7 @@
       </c>
       <c r="H1621" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1622" spans="1:8">
@@ -43802,7 +43792,7 @@
       </c>
       <c r="H1622" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1623" spans="1:8">
@@ -43828,7 +43818,7 @@
       </c>
       <c r="H1623" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1624" spans="1:8">
@@ -43854,7 +43844,7 @@
       </c>
       <c r="H1624" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>30_1024009_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1625" spans="1:8">
@@ -43870,7 +43860,7 @@
         <v>1</v>
       </c>
       <c r="D1625" s="25" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E1625" s="24">
         <v>50</v>
@@ -43879,9 +43869,8 @@
       <c r="G1625" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="H1625" s="24" t="str">
-        <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+      <c r="H1625" s="2" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="1626" spans="1:8">
@@ -43906,8 +43895,8 @@
         <v>50</v>
       </c>
       <c r="H1626" s="24" t="str">
-        <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <f>H1625</f>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1627" spans="1:8">
@@ -43933,7 +43922,7 @@
       </c>
       <c r="H1627" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1628" spans="1:8">
@@ -43959,7 +43948,7 @@
       </c>
       <c r="H1628" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1629" spans="1:8">
@@ -43985,7 +43974,7 @@
       </c>
       <c r="H1629" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1630" spans="1:8">
@@ -44011,7 +44000,7 @@
       </c>
       <c r="H1630" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1631" spans="1:8">
@@ -44037,7 +44026,7 @@
       </c>
       <c r="H1631" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1632" spans="1:8">
@@ -44063,7 +44052,7 @@
       </c>
       <c r="H1632" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1633" spans="1:8">
@@ -44089,7 +44078,7 @@
       </c>
       <c r="H1633" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1634" spans="1:8">
@@ -44115,7 +44104,7 @@
       </c>
       <c r="H1634" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1635" spans="1:8">
@@ -44141,7 +44130,7 @@
       </c>
       <c r="H1635" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1636" spans="1:8">
@@ -44167,7 +44156,7 @@
       </c>
       <c r="H1636" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1637" spans="1:8">
@@ -44193,7 +44182,7 @@
       </c>
       <c r="H1637" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1638" spans="1:8">
@@ -44219,7 +44208,7 @@
       </c>
       <c r="H1638" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1639" spans="1:8">
@@ -44245,7 +44234,7 @@
       </c>
       <c r="H1639" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1640" spans="1:8">
@@ -44271,7 +44260,7 @@
       </c>
       <c r="H1640" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1641" spans="1:8">
@@ -44297,7 +44286,7 @@
       </c>
       <c r="H1641" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1642" spans="1:8">
@@ -44323,7 +44312,7 @@
       </c>
       <c r="H1642" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1643" spans="1:8">
@@ -44349,7 +44338,7 @@
       </c>
       <c r="H1643" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1644" spans="1:8">
@@ -44375,7 +44364,7 @@
       </c>
       <c r="H1644" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1645" spans="1:8">
@@ -44401,7 +44390,7 @@
       </c>
       <c r="H1645" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1646" spans="1:8">
@@ -44427,7 +44416,7 @@
       </c>
       <c r="H1646" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1647" spans="1:8">
@@ -44453,7 +44442,7 @@
       </c>
       <c r="H1647" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1648" spans="1:8">
@@ -44479,7 +44468,7 @@
       </c>
       <c r="H1648" s="24" t="str">
         <f t="shared" si="174"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1649" spans="1:8">
@@ -44505,7 +44494,7 @@
       </c>
       <c r="H1649" s="24" t="str">
         <f t="shared" ref="H1649:H1712" si="180">H1647</f>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1650" spans="1:8">
@@ -44531,7 +44520,7 @@
       </c>
       <c r="H1650" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1651" spans="1:8">
@@ -44557,7 +44546,7 @@
       </c>
       <c r="H1651" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1652" spans="1:8">
@@ -44583,7 +44572,7 @@
       </c>
       <c r="H1652" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1653" spans="1:8">
@@ -44609,7 +44598,7 @@
       </c>
       <c r="H1653" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1654" spans="1:8">
@@ -44635,7 +44624,7 @@
       </c>
       <c r="H1654" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1655" spans="1:8">
@@ -44661,7 +44650,7 @@
       </c>
       <c r="H1655" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1656" spans="1:8">
@@ -44687,7 +44676,7 @@
       </c>
       <c r="H1656" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1657" spans="1:8">
@@ -44713,7 +44702,7 @@
       </c>
       <c r="H1657" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1658" spans="1:8">
@@ -44739,7 +44728,7 @@
       </c>
       <c r="H1658" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1659" spans="1:8">
@@ -44765,7 +44754,7 @@
       </c>
       <c r="H1659" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1660" spans="1:8">
@@ -44791,7 +44780,7 @@
       </c>
       <c r="H1660" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1661" spans="1:8">
@@ -44817,7 +44806,7 @@
       </c>
       <c r="H1661" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1662" spans="1:8">
@@ -44843,7 +44832,7 @@
       </c>
       <c r="H1662" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1663" spans="1:8">
@@ -44869,7 +44858,7 @@
       </c>
       <c r="H1663" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1664" spans="1:8">
@@ -44895,7 +44884,7 @@
       </c>
       <c r="H1664" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1665" spans="1:8">
@@ -44921,7 +44910,7 @@
       </c>
       <c r="H1665" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1666" spans="1:8">
@@ -44947,7 +44936,7 @@
       </c>
       <c r="H1666" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1667" spans="1:8">
@@ -44973,7 +44962,7 @@
       </c>
       <c r="H1667" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1668" spans="1:8">
@@ -44999,7 +44988,7 @@
       </c>
       <c r="H1668" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1669" spans="1:8">
@@ -45025,7 +45014,7 @@
       </c>
       <c r="H1669" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1670" spans="1:8">
@@ -45051,7 +45040,7 @@
       </c>
       <c r="H1670" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1671" spans="1:8">
@@ -45077,7 +45066,7 @@
       </c>
       <c r="H1671" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1672" spans="1:8">
@@ -45103,7 +45092,7 @@
       </c>
       <c r="H1672" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1673" spans="1:8">
@@ -45129,7 +45118,7 @@
       </c>
       <c r="H1673" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1674" spans="1:8">
@@ -45155,7 +45144,7 @@
       </c>
       <c r="H1674" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1675" spans="1:8">
@@ -45181,7 +45170,7 @@
       </c>
       <c r="H1675" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1676" spans="1:8">
@@ -45207,7 +45196,7 @@
       </c>
       <c r="H1676" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1677" spans="1:8">
@@ -45233,7 +45222,7 @@
       </c>
       <c r="H1677" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1678" spans="1:8">
@@ -45259,7 +45248,7 @@
       </c>
       <c r="H1678" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1679" spans="1:8">
@@ -45285,7 +45274,7 @@
       </c>
       <c r="H1679" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1680" spans="1:8">
@@ -45311,7 +45300,7 @@
       </c>
       <c r="H1680" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1681" spans="1:8">
@@ -45337,7 +45326,7 @@
       </c>
       <c r="H1681" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1682" spans="1:8">
@@ -45363,7 +45352,7 @@
       </c>
       <c r="H1682" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1683" spans="1:8">
@@ -45389,7 +45378,7 @@
       </c>
       <c r="H1683" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1684" spans="1:8">
@@ -45415,7 +45404,7 @@
       </c>
       <c r="H1684" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024009_2</v>
+        <v>25_1024009_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1685" spans="1:8">
@@ -45431,7 +45420,7 @@
         <v>1</v>
       </c>
       <c r="D1685" s="25" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E1685" s="24">
         <v>50</v>
@@ -45441,7 +45430,7 @@
         <v>50</v>
       </c>
       <c r="H1685" s="24" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1686" spans="1:8">
@@ -45465,8 +45454,9 @@
       <c r="G1686" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="H1686" s="24" t="s">
-        <v>285</v>
+      <c r="H1686" s="24" t="str">
+        <f>H1685</f>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1687" spans="1:8">
@@ -45492,7 +45482,7 @@
       </c>
       <c r="H1687" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1688" spans="1:8">
@@ -45518,7 +45508,7 @@
       </c>
       <c r="H1688" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1689" spans="1:8">
@@ -45544,7 +45534,7 @@
       </c>
       <c r="H1689" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1690" spans="1:8">
@@ -45570,7 +45560,7 @@
       </c>
       <c r="H1690" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1691" spans="1:8">
@@ -45596,7 +45586,7 @@
       </c>
       <c r="H1691" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1692" spans="1:8">
@@ -45622,7 +45612,7 @@
       </c>
       <c r="H1692" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1693" spans="1:8">
@@ -45648,7 +45638,7 @@
       </c>
       <c r="H1693" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1694" spans="1:8">
@@ -45674,7 +45664,7 @@
       </c>
       <c r="H1694" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1695" spans="1:8">
@@ -45700,7 +45690,7 @@
       </c>
       <c r="H1695" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1696" spans="1:8">
@@ -45726,7 +45716,7 @@
       </c>
       <c r="H1696" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1697" spans="1:8">
@@ -45752,7 +45742,7 @@
       </c>
       <c r="H1697" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1698" spans="1:8">
@@ -45778,7 +45768,7 @@
       </c>
       <c r="H1698" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1699" spans="1:8">
@@ -45804,7 +45794,7 @@
       </c>
       <c r="H1699" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1700" spans="1:8">
@@ -45830,7 +45820,7 @@
       </c>
       <c r="H1700" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1701" spans="1:8">
@@ -45856,7 +45846,7 @@
       </c>
       <c r="H1701" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1702" spans="1:8">
@@ -45882,7 +45872,7 @@
       </c>
       <c r="H1702" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1703" spans="1:8">
@@ -45908,7 +45898,7 @@
       </c>
       <c r="H1703" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1704" spans="1:8">
@@ -45934,7 +45924,7 @@
       </c>
       <c r="H1704" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1705" spans="1:8">
@@ -45960,7 +45950,7 @@
       </c>
       <c r="H1705" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1706" spans="1:8">
@@ -45986,7 +45976,7 @@
       </c>
       <c r="H1706" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1707" spans="1:8">
@@ -46012,7 +46002,7 @@
       </c>
       <c r="H1707" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1708" spans="1:8">
@@ -46038,7 +46028,7 @@
       </c>
       <c r="H1708" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1709" spans="1:8">
@@ -46064,7 +46054,7 @@
       </c>
       <c r="H1709" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1710" spans="1:8">
@@ -46090,7 +46080,7 @@
       </c>
       <c r="H1710" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1711" spans="1:8">
@@ -46116,7 +46106,7 @@
       </c>
       <c r="H1711" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1712" spans="1:8">
@@ -46142,7 +46132,7 @@
       </c>
       <c r="H1712" s="24" t="str">
         <f t="shared" si="180"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1713" spans="1:8">
@@ -46168,7 +46158,7 @@
       </c>
       <c r="H1713" s="24" t="str">
         <f t="shared" ref="H1713:H1776" si="186">H1711</f>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1714" spans="1:8">
@@ -46194,7 +46184,7 @@
       </c>
       <c r="H1714" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1715" spans="1:8">
@@ -46220,7 +46210,7 @@
       </c>
       <c r="H1715" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1716" spans="1:8">
@@ -46246,7 +46236,7 @@
       </c>
       <c r="H1716" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1717" spans="1:8">
@@ -46272,7 +46262,7 @@
       </c>
       <c r="H1717" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1718" spans="1:8">
@@ -46298,7 +46288,7 @@
       </c>
       <c r="H1718" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1719" spans="1:8">
@@ -46324,7 +46314,7 @@
       </c>
       <c r="H1719" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1720" spans="1:8">
@@ -46350,7 +46340,7 @@
       </c>
       <c r="H1720" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1721" spans="1:8">
@@ -46376,7 +46366,7 @@
       </c>
       <c r="H1721" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1722" spans="1:8">
@@ -46402,7 +46392,7 @@
       </c>
       <c r="H1722" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1723" spans="1:8">
@@ -46428,7 +46418,7 @@
       </c>
       <c r="H1723" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1724" spans="1:8">
@@ -46454,7 +46444,7 @@
       </c>
       <c r="H1724" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1725" spans="1:8">
@@ -46480,7 +46470,7 @@
       </c>
       <c r="H1725" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1726" spans="1:8">
@@ -46506,7 +46496,7 @@
       </c>
       <c r="H1726" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1727" spans="1:8">
@@ -46532,7 +46522,7 @@
       </c>
       <c r="H1727" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1728" spans="1:8">
@@ -46558,7 +46548,7 @@
       </c>
       <c r="H1728" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1729" spans="1:8">
@@ -46584,7 +46574,7 @@
       </c>
       <c r="H1729" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1730" spans="1:8">
@@ -46610,7 +46600,7 @@
       </c>
       <c r="H1730" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1731" spans="1:8">
@@ -46636,7 +46626,7 @@
       </c>
       <c r="H1731" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1732" spans="1:8">
@@ -46662,7 +46652,7 @@
       </c>
       <c r="H1732" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1733" spans="1:8">
@@ -46688,7 +46678,7 @@
       </c>
       <c r="H1733" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1734" spans="1:8">
@@ -46714,7 +46704,7 @@
       </c>
       <c r="H1734" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1735" spans="1:8">
@@ -46740,7 +46730,7 @@
       </c>
       <c r="H1735" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1736" spans="1:8">
@@ -46766,7 +46756,7 @@
       </c>
       <c r="H1736" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1737" spans="1:8">
@@ -46792,7 +46782,7 @@
       </c>
       <c r="H1737" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1738" spans="1:8">
@@ -46818,7 +46808,7 @@
       </c>
       <c r="H1738" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1739" spans="1:8">
@@ -46844,7 +46834,7 @@
       </c>
       <c r="H1739" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1740" spans="1:8">
@@ -46870,7 +46860,7 @@
       </c>
       <c r="H1740" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1741" spans="1:8">
@@ -46896,7 +46886,7 @@
       </c>
       <c r="H1741" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1742" spans="1:8">
@@ -46922,7 +46912,7 @@
       </c>
       <c r="H1742" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1743" spans="1:8">
@@ -46948,7 +46938,7 @@
       </c>
       <c r="H1743" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1744" spans="1:8">
@@ -46974,7 +46964,7 @@
       </c>
       <c r="H1744" s="24" t="str">
         <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+        <v>30_1024010_2|30_1022505_10</v>
       </c>
     </row>
     <row r="1745" spans="1:8">
@@ -46990,7 +46980,7 @@
         <v>1</v>
       </c>
       <c r="D1745" s="25" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E1745" s="24">
         <v>50</v>
@@ -46999,9 +46989,8 @@
       <c r="G1745" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="H1745" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+      <c r="H1745" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="1746" spans="1:8">
@@ -47025,9 +47014,8 @@
       <c r="G1746" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="H1746" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+      <c r="H1746" s="2" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="1747" spans="1:8">
@@ -47051,9 +47039,9 @@
       <c r="G1747" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="H1747" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+      <c r="H1747" s="2" t="str">
+        <f t="shared" ref="H1747:H1804" si="191">H1745</f>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1748" spans="1:8">
@@ -47077,9 +47065,9 @@
       <c r="G1748" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="H1748" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+      <c r="H1748" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1749" spans="1:8">
@@ -47103,9 +47091,9 @@
       <c r="G1749" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="H1749" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+      <c r="H1749" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1750" spans="1:8">
@@ -47129,9 +47117,9 @@
       <c r="G1750" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="H1750" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+      <c r="H1750" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1751" spans="1:8">
@@ -47155,9 +47143,9 @@
       <c r="G1751" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="H1751" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+      <c r="H1751" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1752" spans="1:8">
@@ -47181,9 +47169,9 @@
       <c r="G1752" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="H1752" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+      <c r="H1752" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1753" spans="1:8">
@@ -47207,9 +47195,9 @@
       <c r="G1753" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="H1753" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+      <c r="H1753" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1754" spans="1:8">
@@ -47233,9 +47221,9 @@
       <c r="G1754" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="H1754" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+      <c r="H1754" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1755" spans="1:8">
@@ -47259,9 +47247,9 @@
       <c r="G1755" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="H1755" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+      <c r="H1755" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1756" spans="1:8">
@@ -47285,9 +47273,9 @@
       <c r="G1756" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="H1756" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+      <c r="H1756" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1757" spans="1:8">
@@ -47311,9 +47299,9 @@
       <c r="G1757" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="H1757" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+      <c r="H1757" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1758" spans="1:8">
@@ -47337,9 +47325,9 @@
       <c r="G1758" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="H1758" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+      <c r="H1758" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1759" spans="1:8">
@@ -47363,9 +47351,9 @@
       <c r="G1759" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="H1759" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+      <c r="H1759" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1760" spans="1:8">
@@ -47389,9 +47377,9 @@
       <c r="G1760" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="H1760" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+      <c r="H1760" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1761" spans="1:8">
@@ -47415,9 +47403,9 @@
       <c r="G1761" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="H1761" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+      <c r="H1761" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1762" spans="1:8">
@@ -47441,9 +47429,9 @@
       <c r="G1762" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="H1762" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+      <c r="H1762" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1763" spans="1:8">
@@ -47467,9 +47455,9 @@
       <c r="G1763" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="H1763" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+      <c r="H1763" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1764" spans="1:8">
@@ -47482,7 +47470,7 @@
         <v>5006</v>
       </c>
       <c r="C1764" s="25">
-        <f t="shared" ref="C1764:C1809" si="191">C1704</f>
+        <f t="shared" ref="C1764:C1809" si="192">C1704</f>
         <v>20</v>
       </c>
       <c r="D1764" s="26"/>
@@ -47493,9 +47481,9 @@
       <c r="G1764" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="H1764" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+      <c r="H1764" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1765" spans="1:8">
@@ -47508,7 +47496,7 @@
         <v>5006</v>
       </c>
       <c r="C1765" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>21</v>
       </c>
       <c r="D1765" s="26"/>
@@ -47519,9 +47507,9 @@
       <c r="G1765" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="H1765" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+      <c r="H1765" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1766" spans="1:8">
@@ -47534,7 +47522,7 @@
         <v>5006</v>
       </c>
       <c r="C1766" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>22</v>
       </c>
       <c r="D1766" s="26"/>
@@ -47545,9 +47533,9 @@
       <c r="G1766" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="H1766" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+      <c r="H1766" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1767" spans="1:8">
@@ -47560,7 +47548,7 @@
         <v>5006</v>
       </c>
       <c r="C1767" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>23</v>
       </c>
       <c r="D1767" s="26"/>
@@ -47571,9 +47559,9 @@
       <c r="G1767" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="H1767" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+      <c r="H1767" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1768" spans="1:8">
@@ -47586,7 +47574,7 @@
         <v>5006</v>
       </c>
       <c r="C1768" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>24</v>
       </c>
       <c r="D1768" s="26"/>
@@ -47597,9 +47585,9 @@
       <c r="G1768" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="H1768" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+      <c r="H1768" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1769" spans="1:8">
@@ -47612,7 +47600,7 @@
         <v>5006</v>
       </c>
       <c r="C1769" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>25</v>
       </c>
       <c r="D1769" s="26"/>
@@ -47623,9 +47611,9 @@
       <c r="G1769" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="H1769" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+      <c r="H1769" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1770" spans="1:8">
@@ -47638,7 +47626,7 @@
         <v>5006</v>
       </c>
       <c r="C1770" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>26</v>
       </c>
       <c r="D1770" s="26"/>
@@ -47649,9 +47637,9 @@
       <c r="G1770" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="H1770" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+      <c r="H1770" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1771" spans="1:8">
@@ -47664,7 +47652,7 @@
         <v>5006</v>
       </c>
       <c r="C1771" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>27</v>
       </c>
       <c r="D1771" s="26"/>
@@ -47675,9 +47663,9 @@
       <c r="G1771" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="H1771" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+      <c r="H1771" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1772" spans="1:8">
@@ -47690,7 +47678,7 @@
         <v>5006</v>
       </c>
       <c r="C1772" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>28</v>
       </c>
       <c r="D1772" s="26"/>
@@ -47701,9 +47689,9 @@
       <c r="G1772" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="H1772" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+      <c r="H1772" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1773" spans="1:8">
@@ -47716,7 +47704,7 @@
         <v>5006</v>
       </c>
       <c r="C1773" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>29</v>
       </c>
       <c r="D1773" s="26"/>
@@ -47727,9 +47715,9 @@
       <c r="G1773" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="H1773" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+      <c r="H1773" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1774" spans="1:8">
@@ -47742,7 +47730,7 @@
         <v>5006</v>
       </c>
       <c r="C1774" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>30</v>
       </c>
       <c r="D1774" s="26"/>
@@ -47753,9 +47741,9 @@
       <c r="G1774" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="H1774" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+      <c r="H1774" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1775" spans="1:8">
@@ -47768,7 +47756,7 @@
         <v>5006</v>
       </c>
       <c r="C1775" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>31</v>
       </c>
       <c r="D1775" s="26"/>
@@ -47779,9 +47767,9 @@
       <c r="G1775" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="H1775" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>30_1024010_2</v>
+      <c r="H1775" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1776" spans="1:8">
@@ -47794,7 +47782,7 @@
         <v>5006</v>
       </c>
       <c r="C1776" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>32</v>
       </c>
       <c r="D1776" s="26"/>
@@ -47805,9 +47793,9 @@
       <c r="G1776" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="H1776" s="24" t="str">
-        <f t="shared" si="186"/>
-        <v>31_1024010_2</v>
+      <c r="H1776" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1777" spans="1:8">
@@ -47820,7 +47808,7 @@
         <v>5006</v>
       </c>
       <c r="C1777" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>33</v>
       </c>
       <c r="D1777" s="26"/>
@@ -47831,9 +47819,9 @@
       <c r="G1777" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H1777" s="24" t="str">
-        <f t="shared" ref="H1777:H1805" si="192">H1775</f>
-        <v>30_1024010_2</v>
+      <c r="H1777" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1778" spans="1:8">
@@ -47846,7 +47834,7 @@
         <v>5006</v>
       </c>
       <c r="C1778" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>34</v>
       </c>
       <c r="D1778" s="26"/>
@@ -47857,9 +47845,9 @@
       <c r="G1778" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="H1778" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>31_1024010_2</v>
+      <c r="H1778" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1779" spans="1:8">
@@ -47872,7 +47860,7 @@
         <v>5006</v>
       </c>
       <c r="C1779" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>35</v>
       </c>
       <c r="D1779" s="26"/>
@@ -47883,9 +47871,9 @@
       <c r="G1779" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="H1779" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>30_1024010_2</v>
+      <c r="H1779" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1780" spans="1:8">
@@ -47898,7 +47886,7 @@
         <v>5006</v>
       </c>
       <c r="C1780" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>36</v>
       </c>
       <c r="D1780" s="26"/>
@@ -47909,9 +47897,9 @@
       <c r="G1780" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H1780" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>31_1024010_2</v>
+      <c r="H1780" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1781" spans="1:8">
@@ -47924,7 +47912,7 @@
         <v>5006</v>
       </c>
       <c r="C1781" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>37</v>
       </c>
       <c r="D1781" s="26"/>
@@ -47935,9 +47923,9 @@
       <c r="G1781" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="H1781" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>30_1024010_2</v>
+      <c r="H1781" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1782" spans="1:8">
@@ -47950,7 +47938,7 @@
         <v>5006</v>
       </c>
       <c r="C1782" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>38</v>
       </c>
       <c r="D1782" s="26"/>
@@ -47961,9 +47949,9 @@
       <c r="G1782" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="H1782" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>31_1024010_2</v>
+      <c r="H1782" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1783" spans="1:8">
@@ -47976,7 +47964,7 @@
         <v>5006</v>
       </c>
       <c r="C1783" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>39</v>
       </c>
       <c r="D1783" s="26"/>
@@ -47987,9 +47975,9 @@
       <c r="G1783" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="H1783" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>30_1024010_2</v>
+      <c r="H1783" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1784" spans="1:8">
@@ -48002,7 +47990,7 @@
         <v>5006</v>
       </c>
       <c r="C1784" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>40</v>
       </c>
       <c r="D1784" s="26"/>
@@ -48013,9 +48001,9 @@
       <c r="G1784" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="H1784" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>31_1024010_2</v>
+      <c r="H1784" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1785" spans="1:8">
@@ -48028,7 +48016,7 @@
         <v>5006</v>
       </c>
       <c r="C1785" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>41</v>
       </c>
       <c r="D1785" s="26"/>
@@ -48039,9 +48027,9 @@
       <c r="G1785" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="H1785" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>30_1024010_2</v>
+      <c r="H1785" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1786" spans="1:8">
@@ -48054,7 +48042,7 @@
         <v>5006</v>
       </c>
       <c r="C1786" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>42</v>
       </c>
       <c r="D1786" s="26"/>
@@ -48065,9 +48053,9 @@
       <c r="G1786" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="H1786" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>31_1024010_2</v>
+      <c r="H1786" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1787" spans="1:8">
@@ -48080,7 +48068,7 @@
         <v>5006</v>
       </c>
       <c r="C1787" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>43</v>
       </c>
       <c r="D1787" s="26"/>
@@ -48091,9 +48079,9 @@
       <c r="G1787" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="H1787" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>30_1024010_2</v>
+      <c r="H1787" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1788" spans="1:8">
@@ -48106,7 +48094,7 @@
         <v>5006</v>
       </c>
       <c r="C1788" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>44</v>
       </c>
       <c r="D1788" s="26"/>
@@ -48117,9 +48105,9 @@
       <c r="G1788" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="H1788" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>31_1024010_2</v>
+      <c r="H1788" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1789" spans="1:8">
@@ -48132,7 +48120,7 @@
         <v>5006</v>
       </c>
       <c r="C1789" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>45</v>
       </c>
       <c r="D1789" s="26"/>
@@ -48143,9 +48131,9 @@
       <c r="G1789" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="H1789" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>30_1024010_2</v>
+      <c r="H1789" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1790" spans="1:8">
@@ -48158,7 +48146,7 @@
         <v>5006</v>
       </c>
       <c r="C1790" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>46</v>
       </c>
       <c r="D1790" s="26"/>
@@ -48169,9 +48157,9 @@
       <c r="G1790" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="H1790" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>31_1024010_2</v>
+      <c r="H1790" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1791" spans="1:8">
@@ -48184,7 +48172,7 @@
         <v>5006</v>
       </c>
       <c r="C1791" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>47</v>
       </c>
       <c r="D1791" s="26"/>
@@ -48195,9 +48183,9 @@
       <c r="G1791" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="H1791" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>30_1024010_2</v>
+      <c r="H1791" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1792" spans="1:8">
@@ -48210,7 +48198,7 @@
         <v>5006</v>
       </c>
       <c r="C1792" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>48</v>
       </c>
       <c r="D1792" s="26"/>
@@ -48221,9 +48209,9 @@
       <c r="G1792" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="H1792" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>31_1024010_2</v>
+      <c r="H1792" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1793" spans="1:8">
@@ -48236,7 +48224,7 @@
         <v>5006</v>
       </c>
       <c r="C1793" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>49</v>
       </c>
       <c r="D1793" s="26"/>
@@ -48247,9 +48235,9 @@
       <c r="G1793" s="26" t="s">
         <v>223</v>
       </c>
-      <c r="H1793" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>30_1024010_2</v>
+      <c r="H1793" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1794" spans="1:8">
@@ -48262,7 +48250,7 @@
         <v>5006</v>
       </c>
       <c r="C1794" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>50</v>
       </c>
       <c r="D1794" s="26"/>
@@ -48273,9 +48261,9 @@
       <c r="G1794" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="H1794" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>31_1024010_2</v>
+      <c r="H1794" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1795" spans="1:8">
@@ -48288,7 +48276,7 @@
         <v>5006</v>
       </c>
       <c r="C1795" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>51</v>
       </c>
       <c r="D1795" s="26"/>
@@ -48299,9 +48287,9 @@
       <c r="G1795" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="H1795" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>30_1024010_2</v>
+      <c r="H1795" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1796" spans="1:8">
@@ -48314,7 +48302,7 @@
         <v>5006</v>
       </c>
       <c r="C1796" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>52</v>
       </c>
       <c r="D1796" s="26"/>
@@ -48325,9 +48313,9 @@
       <c r="G1796" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="H1796" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>31_1024010_2</v>
+      <c r="H1796" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1797" spans="1:8">
@@ -48340,7 +48328,7 @@
         <v>5006</v>
       </c>
       <c r="C1797" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>53</v>
       </c>
       <c r="D1797" s="26"/>
@@ -48351,9 +48339,9 @@
       <c r="G1797" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="H1797" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>30_1024010_2</v>
+      <c r="H1797" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1798" spans="1:8">
@@ -48366,7 +48354,7 @@
         <v>5006</v>
       </c>
       <c r="C1798" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>54</v>
       </c>
       <c r="D1798" s="26"/>
@@ -48377,9 +48365,9 @@
       <c r="G1798" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="H1798" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>31_1024010_2</v>
+      <c r="H1798" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1799" spans="1:8">
@@ -48392,7 +48380,7 @@
         <v>5006</v>
       </c>
       <c r="C1799" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>55</v>
       </c>
       <c r="D1799" s="26"/>
@@ -48403,9 +48391,9 @@
       <c r="G1799" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="H1799" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>30_1024010_2</v>
+      <c r="H1799" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1800" spans="1:8">
@@ -48418,7 +48406,7 @@
         <v>5006</v>
       </c>
       <c r="C1800" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>56</v>
       </c>
       <c r="D1800" s="26"/>
@@ -48429,9 +48417,9 @@
       <c r="G1800" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="H1800" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>31_1024010_2</v>
+      <c r="H1800" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1801" spans="1:8">
@@ -48444,7 +48432,7 @@
         <v>5006</v>
       </c>
       <c r="C1801" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>57</v>
       </c>
       <c r="D1801" s="26"/>
@@ -48455,9 +48443,9 @@
       <c r="G1801" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="H1801" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>30_1024010_2</v>
+      <c r="H1801" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1802" spans="1:8">
@@ -48470,7 +48458,7 @@
         <v>5006</v>
       </c>
       <c r="C1802" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>58</v>
       </c>
       <c r="D1802" s="26"/>
@@ -48481,9 +48469,9 @@
       <c r="G1802" s="26" t="s">
         <v>273</v>
       </c>
-      <c r="H1802" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>31_1024010_2</v>
+      <c r="H1802" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1803" spans="1:8">
@@ -48496,7 +48484,7 @@
         <v>5006</v>
       </c>
       <c r="C1803" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>59</v>
       </c>
       <c r="D1803" s="26"/>
@@ -48507,9 +48495,9 @@
       <c r="G1803" s="26" t="s">
         <v>274</v>
       </c>
-      <c r="H1803" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>30_1024010_2</v>
+      <c r="H1803" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>25_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1804" spans="1:8">
@@ -48522,7 +48510,7 @@
         <v>5006</v>
       </c>
       <c r="C1804" s="25">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>60</v>
       </c>
       <c r="D1804" s="26"/>
@@ -48533,279 +48521,279 @@
       <c r="G1804" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="H1804" s="24" t="str">
-        <f t="shared" si="192"/>
-        <v>31_1024010_2</v>
+      <c r="H1804" s="2" t="str">
+        <f t="shared" si="191"/>
+        <v>26_1024010_2|30_1024001_1</v>
       </c>
     </row>
     <row r="1805" spans="1:8">
-      <c r="A1805" s="28">
+      <c r="A1805" s="27">
         <f t="shared" si="193"/>
         <v>9001001</v>
       </c>
-      <c r="B1805" s="28">
+      <c r="B1805" s="27">
         <v>9001</v>
       </c>
-      <c r="C1805" s="29">
-        <f t="shared" si="191"/>
+      <c r="C1805" s="28">
+        <f t="shared" si="192"/>
         <v>1</v>
       </c>
-      <c r="D1805" s="28" t="s">
-        <v>287</v>
-      </c>
-      <c r="E1805" s="28">
+      <c r="D1805" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="E1805" s="27">
         <v>9999999</v>
       </c>
-      <c r="F1805" s="30"/>
-      <c r="G1805" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="H1805" s="28"/>
+      <c r="F1805" s="29"/>
+      <c r="G1805" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="H1805" s="27"/>
     </row>
     <row r="1806" spans="1:8">
-      <c r="A1806" s="28">
+      <c r="A1806" s="27">
         <f t="shared" si="193"/>
         <v>9002002</v>
       </c>
-      <c r="B1806" s="28">
+      <c r="B1806" s="27">
         <v>9002</v>
       </c>
-      <c r="C1806" s="29">
-        <f t="shared" si="191"/>
+      <c r="C1806" s="28">
+        <f t="shared" si="192"/>
         <v>2</v>
       </c>
-      <c r="D1806" s="28" t="s">
-        <v>289</v>
-      </c>
-      <c r="E1806" s="28">
+      <c r="D1806" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="E1806" s="27">
         <v>9999999</v>
       </c>
-      <c r="F1806" s="30"/>
-      <c r="G1806" s="30" t="s">
-        <v>290</v>
-      </c>
-      <c r="H1806" s="28"/>
+      <c r="F1806" s="29"/>
+      <c r="G1806" s="29" t="s">
+        <v>287</v>
+      </c>
+      <c r="H1806" s="27"/>
     </row>
     <row r="1807" spans="1:8">
-      <c r="A1807" s="28">
+      <c r="A1807" s="27">
         <f t="shared" si="193"/>
         <v>9003003</v>
       </c>
-      <c r="B1807" s="28">
+      <c r="B1807" s="27">
         <v>9003</v>
       </c>
-      <c r="C1807" s="29">
-        <f t="shared" si="191"/>
+      <c r="C1807" s="28">
+        <f t="shared" si="192"/>
         <v>3</v>
       </c>
-      <c r="D1807" s="28" t="s">
-        <v>291</v>
-      </c>
-      <c r="E1807" s="28">
+      <c r="D1807" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="E1807" s="27">
         <v>9999999</v>
       </c>
-      <c r="F1807" s="30"/>
-      <c r="G1807" s="30" t="s">
-        <v>292</v>
-      </c>
-      <c r="H1807" s="28"/>
+      <c r="F1807" s="29"/>
+      <c r="G1807" s="29" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1807" s="27"/>
     </row>
     <row r="1808" spans="1:8">
-      <c r="A1808" s="28">
+      <c r="A1808" s="27">
         <f t="shared" si="193"/>
         <v>9004004</v>
       </c>
-      <c r="B1808" s="28">
+      <c r="B1808" s="27">
         <v>9004</v>
       </c>
-      <c r="C1808" s="29">
-        <f t="shared" si="191"/>
+      <c r="C1808" s="28">
+        <f t="shared" si="192"/>
         <v>4</v>
       </c>
-      <c r="D1808" s="28" t="s">
-        <v>293</v>
-      </c>
-      <c r="E1808" s="28">
+      <c r="D1808" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="E1808" s="27">
         <v>9999999</v>
       </c>
-      <c r="F1808" s="30"/>
-      <c r="G1808" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="H1808" s="28"/>
+      <c r="F1808" s="29"/>
+      <c r="G1808" s="29" t="s">
+        <v>291</v>
+      </c>
+      <c r="H1808" s="27"/>
     </row>
     <row r="1809" spans="1:8">
-      <c r="A1809" s="28">
+      <c r="A1809" s="27">
         <f t="shared" si="193"/>
         <v>9005005</v>
       </c>
-      <c r="B1809" s="28">
+      <c r="B1809" s="27">
         <v>9005</v>
       </c>
-      <c r="C1809" s="29">
-        <f t="shared" si="191"/>
+      <c r="C1809" s="28">
+        <f t="shared" si="192"/>
         <v>5</v>
       </c>
-      <c r="D1809" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="E1809" s="28">
+      <c r="D1809" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="E1809" s="27">
         <v>9999999</v>
       </c>
-      <c r="F1809" s="30"/>
-      <c r="G1809" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="H1809" s="28"/>
+      <c r="F1809" s="29"/>
+      <c r="G1809" s="29" t="s">
+        <v>293</v>
+      </c>
+      <c r="H1809" s="27"/>
     </row>
     <row r="1810" spans="1:8">
-      <c r="H1810" s="31"/>
+      <c r="H1810" s="30"/>
     </row>
     <row r="1811" spans="1:8">
-      <c r="H1811" s="31"/>
+      <c r="H1811" s="30"/>
     </row>
     <row r="1812" spans="1:8">
-      <c r="H1812" s="31"/>
+      <c r="H1812" s="30"/>
     </row>
     <row r="1813" spans="1:8">
-      <c r="H1813" s="31"/>
+      <c r="H1813" s="30"/>
     </row>
     <row r="1814" spans="1:8">
-      <c r="H1814" s="31"/>
+      <c r="H1814" s="30"/>
     </row>
     <row r="1815" spans="1:8">
-      <c r="H1815" s="31"/>
+      <c r="H1815" s="30"/>
     </row>
     <row r="1816" spans="1:8">
-      <c r="H1816" s="31"/>
+      <c r="H1816" s="30"/>
     </row>
     <row r="1817" spans="1:8">
-      <c r="H1817" s="31"/>
+      <c r="H1817" s="30"/>
     </row>
     <row r="1818" spans="1:8">
-      <c r="H1818" s="31"/>
+      <c r="H1818" s="30"/>
     </row>
     <row r="1819" spans="1:8">
-      <c r="H1819" s="31"/>
+      <c r="H1819" s="30"/>
     </row>
     <row r="1820" spans="1:8">
-      <c r="H1820" s="31"/>
+      <c r="H1820" s="30"/>
     </row>
     <row r="1821" spans="1:8">
-      <c r="H1821" s="31"/>
+      <c r="H1821" s="30"/>
     </row>
     <row r="1822" spans="1:8">
-      <c r="H1822" s="31"/>
+      <c r="H1822" s="30"/>
     </row>
     <row r="1823" spans="1:8">
-      <c r="H1823" s="31"/>
+      <c r="H1823" s="30"/>
     </row>
     <row r="1824" spans="1:8">
-      <c r="H1824" s="31"/>
+      <c r="H1824" s="30"/>
     </row>
     <row r="1825" spans="8:8">
-      <c r="H1825" s="31"/>
+      <c r="H1825" s="30"/>
     </row>
     <row r="1826" spans="8:8">
-      <c r="H1826" s="31"/>
+      <c r="H1826" s="30"/>
     </row>
     <row r="1827" spans="8:8">
-      <c r="H1827" s="31"/>
+      <c r="H1827" s="30"/>
     </row>
     <row r="1828" spans="8:8">
-      <c r="H1828" s="31"/>
+      <c r="H1828" s="30"/>
     </row>
     <row r="1829" spans="8:8">
-      <c r="H1829" s="31"/>
+      <c r="H1829" s="30"/>
     </row>
     <row r="1830" spans="8:8">
-      <c r="H1830" s="31"/>
+      <c r="H1830" s="30"/>
     </row>
     <row r="1831" spans="8:8">
-      <c r="H1831" s="31"/>
+      <c r="H1831" s="30"/>
     </row>
     <row r="1832" spans="8:8">
-      <c r="H1832" s="31"/>
+      <c r="H1832" s="30"/>
     </row>
     <row r="1833" spans="8:8">
-      <c r="H1833" s="31"/>
+      <c r="H1833" s="30"/>
     </row>
     <row r="1834" spans="8:8">
-      <c r="H1834" s="31"/>
+      <c r="H1834" s="30"/>
     </row>
     <row r="1835" spans="8:8">
-      <c r="H1835" s="31"/>
+      <c r="H1835" s="30"/>
     </row>
     <row r="1836" spans="8:8">
-      <c r="H1836" s="31"/>
+      <c r="H1836" s="30"/>
     </row>
     <row r="1837" spans="8:8">
-      <c r="H1837" s="31"/>
+      <c r="H1837" s="30"/>
     </row>
     <row r="1838" spans="8:8">
-      <c r="H1838" s="31"/>
+      <c r="H1838" s="30"/>
     </row>
     <row r="1839" spans="8:8">
-      <c r="H1839" s="31"/>
+      <c r="H1839" s="30"/>
     </row>
     <row r="1840" spans="8:8">
-      <c r="H1840" s="31"/>
+      <c r="H1840" s="30"/>
     </row>
     <row r="1841" spans="4:8">
-      <c r="H1841" s="31"/>
+      <c r="H1841" s="30"/>
     </row>
     <row r="1842" spans="4:8">
-      <c r="H1842" s="31"/>
+      <c r="H1842" s="30"/>
     </row>
     <row r="1843" spans="4:8">
-      <c r="H1843" s="31"/>
+      <c r="H1843" s="30"/>
     </row>
     <row r="1844" ht="17.25" spans="4:8">
-      <c r="D1844" s="32"/>
-      <c r="H1844" s="31"/>
+      <c r="D1844" s="31"/>
+      <c r="H1844" s="30"/>
     </row>
     <row r="1845" ht="14.25" spans="4:8">
-      <c r="E1845" s="33"/>
-      <c r="H1845" s="31"/>
+      <c r="E1845" s="32"/>
+      <c r="H1845" s="30"/>
     </row>
     <row r="1846" spans="4:8">
-      <c r="H1846" s="31"/>
+      <c r="H1846" s="30"/>
     </row>
     <row r="1847" spans="4:8">
-      <c r="H1847" s="31"/>
+      <c r="H1847" s="30"/>
     </row>
     <row r="1848" spans="4:8">
-      <c r="H1848" s="31"/>
+      <c r="H1848" s="30"/>
     </row>
     <row r="1849" spans="4:8">
-      <c r="H1849" s="31"/>
+      <c r="H1849" s="30"/>
     </row>
     <row r="1850" spans="4:8">
-      <c r="H1850" s="31"/>
+      <c r="H1850" s="30"/>
     </row>
     <row r="1851" spans="4:8">
-      <c r="H1851" s="31"/>
+      <c r="H1851" s="30"/>
     </row>
     <row r="1852" spans="4:8">
-      <c r="H1852" s="31"/>
+      <c r="H1852" s="30"/>
     </row>
     <row r="1853" spans="4:8">
-      <c r="H1853" s="31"/>
+      <c r="H1853" s="30"/>
     </row>
     <row r="1854" spans="4:8">
-      <c r="H1854" s="31"/>
+      <c r="H1854" s="30"/>
     </row>
     <row r="1855" spans="4:8">
-      <c r="H1855" s="31"/>
+      <c r="H1855" s="30"/>
     </row>
     <row r="1858" ht="14.25" spans="4:5">
-      <c r="D1858" s="33"/>
+      <c r="D1858" s="32"/>
     </row>
     <row r="1861" ht="14.25" spans="4:5">
-      <c r="E1861" s="33"/>
+      <c r="E1861" s="32"/>
     </row>
     <row r="1862" ht="14.25" spans="4:5">
-      <c r="E1862" s="33"/>
+      <c r="E1862" s="32"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:C1862" etc:filterBottomFollowUsedRange="0">
